--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -2322,25 +2322,89 @@
         <v>0</v>
       </c>
       <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
-      <c r="DY3" t="inlineStr"/>
-      <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
-      <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
       <c r="EG3" t="inlineStr"/>
       <c r="EH3" t="inlineStr"/>
       <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31148,26 +31212,78 @@
       <c r="DU64" t="b">
         <v>0</v>
       </c>
-      <c r="DV64" t="inlineStr"/>
-      <c r="DW64" t="inlineStr"/>
-      <c r="DX64" t="inlineStr"/>
-      <c r="DY64" t="inlineStr"/>
-      <c r="DZ64" t="inlineStr"/>
-      <c r="EA64" t="inlineStr"/>
-      <c r="EB64" t="inlineStr"/>
+      <c r="DV64" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="DW64" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="DX64" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="DY64" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="DZ64" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EA64" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="EB64" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
       <c r="EC64" t="inlineStr"/>
-      <c r="ED64" t="inlineStr"/>
+      <c r="ED64" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
       <c r="EE64" t="inlineStr"/>
-      <c r="EF64" t="inlineStr"/>
-      <c r="EG64" t="inlineStr"/>
-      <c r="EH64" t="inlineStr"/>
-      <c r="EI64" t="inlineStr"/>
+      <c r="EF64" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EG64" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EH64" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
       <c r="EJ64" t="inlineStr"/>
       <c r="EK64" t="inlineStr"/>
       <c r="EL64" t="inlineStr"/>
       <c r="EM64" t="inlineStr"/>
-      <c r="EN64" t="inlineStr"/>
-      <c r="EO64" t="inlineStr"/>
+      <c r="EN64" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO64" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP113" headerRowCount="1">
-  <autoFilter ref="A1:EP113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP114" headerRowCount="1">
+  <autoFilter ref="A1:EP114"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP113"/>
+  <dimension ref="A1:EP114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6105,7 +6105,7 @@
         <v>1.43</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE12" t="n">
         <v>0.29</v>
@@ -11897,7 +11897,7 @@
         <v>2.13</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -12374,7 +12374,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE24" t="n">
         <v>1.5</v>
@@ -17146,7 +17146,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -22917,7 +22917,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -23386,7 +23386,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE47" t="n">
         <v>1.57</v>
@@ -28625,7 +28625,7 @@
         <v>1.57</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -33378,7 +33378,7 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE68" t="n">
         <v>1.63</v>
@@ -37197,7 +37197,7 @@
         <v>1.71</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -40050,7 +40050,7 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE82" t="n">
         <v>0.43</v>
@@ -46209,7 +46209,7 @@
         <v>0.75</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -47626,7 +47626,7 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE98" t="n">
         <v>1</v>
@@ -51421,7 +51421,7 @@
         <v>0.43</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -54848,6 +54848,486 @@
       <c r="EP113" t="inlineStr">
         <is>
           <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>15</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>45982.82291666666</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" t="n">
+        <v>8</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>8</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" t="n">
+        <v>13</v>
+      </c>
+      <c r="T114" t="n">
+        <v>4</v>
+      </c>
+      <c r="U114" t="n">
+        <v>21</v>
+      </c>
+      <c r="V114" t="n">
+        <v>6</v>
+      </c>
+      <c r="W114" t="n">
+        <v>13</v>
+      </c>
+      <c r="X114" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>156</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF114" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG114" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH114" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI114" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ114" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK114" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL114" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM114" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN114" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO114" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW114" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DX114" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DY114" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="DZ114" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA114" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EB114" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="ED114" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EH114" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK114" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr"/>
+      <c r="EM114" t="inlineStr"/>
+      <c r="EN114" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EO114" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EP114" t="inlineStr">
+        <is>
+          <t>2.42</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP114" headerRowCount="1">
-  <autoFilter ref="A1:EP114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
+  <autoFilter ref="A1:EP121"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP114"/>
+  <dimension ref="A1:EP121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE2" t="n">
         <v>1.88</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2285,7 +2285,7 @@
         <v>0.43</v>
       </c>
       <c r="DE3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>1.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE5" t="n">
         <v>0.86</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4206,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE8" t="n">
         <v>1.5</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE11" t="n">
         <v>1.25</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6577,7 +6577,7 @@
         <v>1.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE14" t="n">
         <v>0.43</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8033,7 +8033,7 @@
         <v>0.75</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9001,7 +9001,7 @@
         <v>1.57</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>2</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10446,10 +10446,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11406,10 +11406,10 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12862,7 +12862,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13342,7 +13342,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE26" t="n">
         <v>1.5</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15237,7 +15237,7 @@
         <v>0.43</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17149,7 +17149,7 @@
         <v>1.5</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17621,7 +17621,7 @@
         <v>1.43</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18098,10 +18098,10 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18586,7 +18586,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE37" t="n">
         <v>1.88</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19557,7 +19557,7 @@
         <v>0.75</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE41" t="n">
         <v>0.43</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20997,7 +20997,7 @@
         <v>1.57</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21954,7 +21954,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE44" t="n">
         <v>0.86</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22429,7 +22429,7 @@
         <v>3</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22914,7 +22914,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE46" t="n">
         <v>1.25</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23389,7 +23389,7 @@
         <v>1.5</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24810,7 +24810,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE50" t="n">
         <v>1.63</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25274,7 +25274,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE51" t="n">
         <v>1</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25749,7 +25749,7 @@
         <v>0.75</v>
       </c>
       <c r="DE52" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27178,10 +27178,10 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE55" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>2</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28134,7 +28134,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE57" t="n">
         <v>0.71</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29582,7 +29582,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE60" t="n">
         <v>1.88</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30054,7 +30054,7 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE61" t="n">
         <v>0.86</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30534,10 +30534,10 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31009,7 +31009,7 @@
         <v>1.43</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31942,7 +31942,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE65" t="n">
         <v>0.71</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32414,10 +32414,10 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35277,7 +35277,7 @@
         <v>1.57</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36237,7 +36237,7 @@
         <v>2</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36717,7 +36717,7 @@
         <v>1.43</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37194,7 +37194,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE76" t="n">
         <v>1.25</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38634,10 +38634,10 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39090,7 +39090,7 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE80" t="n">
         <v>1.88</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39578,7 +39578,7 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE81" t="n">
         <v>1</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40510,7 +40510,7 @@
         <v>70</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE83" t="n">
         <v>0.71</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40982,7 +40982,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE84" t="n">
         <v>1.63</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41457,7 +41457,7 @@
         <v>3</v>
       </c>
       <c r="DE85" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42401,7 +42401,7 @@
         <v>0.43</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF87" t="n">
         <v>0.4</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42865,7 +42865,7 @@
         <v>2</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF88" t="n">
         <v>1.8</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43825,7 +43825,7 @@
         <v>1.57</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44310,10 +44310,10 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45726,7 +45726,7 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE94" t="n">
         <v>1.63</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46678,7 +46678,7 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE96" t="n">
         <v>0.71</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>3</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47629,7 +47629,7 @@
         <v>1.5</v>
       </c>
       <c r="DE98" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48586,10 +48586,10 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49069,7 +49069,7 @@
         <v>2.13</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49538,7 +49538,7 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE102" t="n">
         <v>1.5</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50002,7 +50002,7 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE103" t="n">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50954,10 +50954,10 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE105" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52834,7 +52834,7 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE109" t="n">
         <v>0.71</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55328,6 +55328,3318 @@
       <c r="EP114" t="inlineStr">
         <is>
           <t>2.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>15</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>45983.625</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2</v>
+      </c>
+      <c r="J115" t="n">
+        <v>7</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4</v>
+      </c>
+      <c r="L115" t="n">
+        <v>11</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>4</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>6</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>11</v>
+      </c>
+      <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>17</v>
+      </c>
+      <c r="V115" t="n">
+        <v>8</v>
+      </c>
+      <c r="W115" t="n">
+        <v>17</v>
+      </c>
+      <c r="X115" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="DO115" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW115" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DX115" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH115" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr"/>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO115" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EP115" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>15</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>45983.71875</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>9</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
+        <v>11</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>3</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="n">
+        <v>7</v>
+      </c>
+      <c r="U116" t="n">
+        <v>20</v>
+      </c>
+      <c r="V116" t="n">
+        <v>10</v>
+      </c>
+      <c r="W116" t="n">
+        <v>10</v>
+      </c>
+      <c r="X116" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="DX116" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ116" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr"/>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EJ116" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EO116" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP116" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>15</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>45983.82291666666</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" t="n">
+        <v>11</v>
+      </c>
+      <c r="L117" t="n">
+        <v>17</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>5</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>12</v>
+      </c>
+      <c r="T117" t="n">
+        <v>10</v>
+      </c>
+      <c r="U117" t="n">
+        <v>17</v>
+      </c>
+      <c r="V117" t="n">
+        <v>10</v>
+      </c>
+      <c r="W117" t="n">
+        <v>5</v>
+      </c>
+      <c r="X117" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>45</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW117" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="DX117" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EB117" t="inlineStr">
+        <is>
+          <t>5.23</t>
+        </is>
+      </c>
+      <c r="EC117" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="ED117" t="inlineStr"/>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr"/>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EM117" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EN117" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO117" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EP117" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>15</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>45984.52083333334</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3</v>
+      </c>
+      <c r="L118" t="n">
+        <v>9</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>6</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6</v>
+      </c>
+      <c r="S118" t="n">
+        <v>14</v>
+      </c>
+      <c r="T118" t="n">
+        <v>5</v>
+      </c>
+      <c r="U118" t="n">
+        <v>20</v>
+      </c>
+      <c r="V118" t="n">
+        <v>11</v>
+      </c>
+      <c r="W118" t="n">
+        <v>5</v>
+      </c>
+      <c r="X118" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>156</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>60</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>55</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX118" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr"/>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr"/>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EL118" t="inlineStr"/>
+      <c r="EM118" t="inlineStr"/>
+      <c r="EN118" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EO118" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EP118" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>15</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45984.625</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" t="n">
+        <v>8</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>6</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2</v>
+      </c>
+      <c r="S119" t="n">
+        <v>9</v>
+      </c>
+      <c r="T119" t="n">
+        <v>7</v>
+      </c>
+      <c r="U119" t="n">
+        <v>15</v>
+      </c>
+      <c r="V119" t="n">
+        <v>9</v>
+      </c>
+      <c r="W119" t="n">
+        <v>15</v>
+      </c>
+      <c r="X119" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>669388</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW119" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DX119" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr"/>
+      <c r="EE119" t="inlineStr"/>
+      <c r="EF119" t="inlineStr"/>
+      <c r="EG119" t="inlineStr"/>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL119" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EO119" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EP119" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>15</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>45984.72916666666</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>7</v>
+      </c>
+      <c r="L120" t="n">
+        <v>12</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>3</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>4</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7</v>
+      </c>
+      <c r="S120" t="n">
+        <v>6</v>
+      </c>
+      <c r="T120" t="n">
+        <v>13</v>
+      </c>
+      <c r="U120" t="n">
+        <v>10</v>
+      </c>
+      <c r="V120" t="n">
+        <v>20</v>
+      </c>
+      <c r="W120" t="n">
+        <v>14</v>
+      </c>
+      <c r="X120" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>61</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU120" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV120" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX120" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY120" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ120" t="n">
+        <v>16</v>
+      </c>
+      <c r="DA120" t="n">
+        <v>56</v>
+      </c>
+      <c r="DB120" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC120" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG120" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH120" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI120" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DJ120" t="n">
+        <v>85</v>
+      </c>
+      <c r="DK120" t="n">
+        <v>44</v>
+      </c>
+      <c r="DL120" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM120" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN120" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO120" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW120" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DX120" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="DY120" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="DZ120" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA120" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EB120" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="ED120" t="inlineStr"/>
+      <c r="EE120" t="inlineStr"/>
+      <c r="EF120" t="inlineStr"/>
+      <c r="EG120" t="inlineStr"/>
+      <c r="EH120" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI120" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EJ120" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EK120" t="inlineStr"/>
+      <c r="EL120" t="inlineStr"/>
+      <c r="EM120" t="inlineStr"/>
+      <c r="EN120" t="inlineStr"/>
+      <c r="EO120" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP120" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>15</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>45984.76041666666</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>10</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>11</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3</v>
+      </c>
+      <c r="N121" t="n">
+        <v>2</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>6</v>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="n">
+        <v>13</v>
+      </c>
+      <c r="T121" t="n">
+        <v>4</v>
+      </c>
+      <c r="U121" t="n">
+        <v>19</v>
+      </c>
+      <c r="V121" t="n">
+        <v>8</v>
+      </c>
+      <c r="W121" t="n">
+        <v>15</v>
+      </c>
+      <c r="X121" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW121" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DX121" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF121" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG121" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EH121" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI121" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EJ121" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK121" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL121" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM121" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EN121" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EO121" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EP121" t="inlineStr">
+        <is>
+          <t>2.25</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -57285,13 +57285,13 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R119" t="n">
         <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T119" t="n">
         <v>7</v>
@@ -57472,13 +57472,13 @@
         <v>98</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="CA119" t="n">
         <v>0.99</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
-  <autoFilter ref="A1:EP121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP122" headerRowCount="1">
+  <autoFilter ref="A1:EP122"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP121"/>
+  <dimension ref="A1:EP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3241,7 +3241,7 @@
         <v>1.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -5630,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE10" t="n">
         <v>1.63</v>
@@ -14282,7 +14282,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE28" t="n">
         <v>1</v>
@@ -14757,7 +14757,7 @@
         <v>3</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -20034,7 +20034,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE40" t="n">
         <v>0.71</v>
@@ -21957,7 +21957,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -30057,7 +30057,7 @@
         <v>1.38</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -31006,7 +31006,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE63" t="n">
         <v>0.86</v>
@@ -36714,7 +36714,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE75" t="n">
         <v>1.57</v>
@@ -38165,7 +38165,7 @@
         <v>2.13</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -44774,7 +44774,7 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE92" t="n">
         <v>1</v>
@@ -45257,7 +45257,7 @@
         <v>2</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -53797,7 +53797,7 @@
         <v>2</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -54730,7 +54730,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE113" t="n">
         <v>1.88</v>
@@ -58640,6 +58640,494 @@
       <c r="EP121" t="inlineStr">
         <is>
           <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45989.82291666666</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4</v>
+      </c>
+      <c r="K122" t="n">
+        <v>4</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2</v>
+      </c>
+      <c r="S122" t="n">
+        <v>8</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4</v>
+      </c>
+      <c r="U122" t="n">
+        <v>9</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6</v>
+      </c>
+      <c r="W122" t="n">
+        <v>11</v>
+      </c>
+      <c r="X122" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW122" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="DX122" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="ED122" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EE122" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF122" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK122" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EL122" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM122" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EN122" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EO122" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EP122" t="inlineStr">
+        <is>
+          <t>2.24</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP122" headerRowCount="1">
-  <autoFilter ref="A1:EP122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP129" headerRowCount="1">
+  <autoFilter ref="A1:EP129"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP122"/>
+  <dimension ref="A1:EP129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.38</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE4" t="n">
         <v>1.75</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3726,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE8" t="n">
         <v>1.5</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7062,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8998,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10918,10 +10918,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE23" t="n">
         <v>1.25</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>1.38</v>
       </c>
       <c r="DE25" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13814,7 +13814,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE27" t="n">
         <v>1.63</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE30" t="n">
         <v>1.57</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15701,7 +15701,7 @@
         <v>2</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16186,10 +16186,10 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16677,7 +16677,7 @@
         <v>0.75</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17149,7 +17149,7 @@
         <v>1.5</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17618,10 +17618,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18589,7 +18589,7 @@
         <v>1.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19066,10 +19066,10 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19557,7 +19557,7 @@
         <v>0.75</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20037,7 +20037,7 @@
         <v>1.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20525,7 +20525,7 @@
         <v>1.38</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20994,7 +20994,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE42" t="n">
         <v>0.63</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21482,7 +21482,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE43" t="n">
         <v>1.63</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22914,7 +22914,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE46" t="n">
         <v>1.25</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23858,10 +23858,10 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24322,10 +24322,10 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26234,7 +26234,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE53" t="n">
         <v>1.5</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26709,7 +26709,7 @@
         <v>2</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27178,7 +27178,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE55" t="n">
         <v>0.88</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE56" t="n">
         <v>0.63</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28137,7 +28137,7 @@
         <v>1</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28622,7 +28622,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE58" t="n">
         <v>1.25</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29110,10 +29110,10 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29582,10 +29582,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30534,10 +30534,10 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31009,7 +31009,7 @@
         <v>1.25</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE64" t="n">
         <v>1</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31942,10 +31942,10 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32902,10 +32902,10 @@
         <v>63</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33869,7 +33869,7 @@
         <v>3</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35274,7 +35274,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE72" t="n">
         <v>1.75</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35746,10 +35746,10 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36234,7 +36234,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE74" t="n">
         <v>0.88</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36717,7 +36717,7 @@
         <v>1.25</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37685,7 +37685,7 @@
         <v>1.38</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38162,7 +38162,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE78" t="n">
         <v>1.13</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38634,7 +38634,7 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE79" t="n">
         <v>0.63</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39090,10 +39090,10 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39581,7 +39581,7 @@
         <v>1.38</v>
       </c>
       <c r="DE81" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40053,7 +40053,7 @@
         <v>1.5</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF82" t="n">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40513,7 +40513,7 @@
         <v>1.5</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF83" t="n">
         <v>1.6</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42398,7 +42398,7 @@
         <v>30</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE87" t="n">
         <v>1.75</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43350,7 +43350,7 @@
         <v>50</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43822,7 +43822,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE90" t="n">
         <v>1.57</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         <v>1.25</v>
       </c>
       <c r="DE92" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45254,7 +45254,7 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE93" t="n">
         <v>1.13</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46678,10 +46678,10 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>3</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48114,10 +48114,10 @@
         <v>50</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48586,7 +48586,7 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE100" t="n">
         <v>0.63</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49066,7 +49066,7 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE101" t="n">
         <v>1.75</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50469,7 +50469,7 @@
         <v>2</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50957,7 +50957,7 @@
         <v>1.5</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51418,7 +51418,7 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE106" t="n">
         <v>1.25</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51909,7 +51909,7 @@
         <v>0.75</v>
       </c>
       <c r="DE107" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52378,10 +52378,10 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52837,7 +52837,7 @@
         <v>1.38</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53322,7 +53322,7 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE110" t="n">
         <v>1.63</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54266,7 +54266,7 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE112" t="n">
         <v>1.5</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54733,7 +54733,7 @@
         <v>1.25</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55669,7 +55669,7 @@
         <v>3</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56610,7 +56610,7 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="DE117" t="n">
         <v>0.88</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57090,7 +57090,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE118" t="n">
         <v>1.75</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58493,7 +58493,7 @@
         <v>1</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59128,6 +59128,3334 @@
       <c r="EP122" t="inlineStr">
         <is>
           <t>2.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45990.625</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6</v>
+      </c>
+      <c r="M123" t="n">
+        <v>4</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>4</v>
+      </c>
+      <c r="R123" t="n">
+        <v>5</v>
+      </c>
+      <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>14</v>
+      </c>
+      <c r="U123" t="n">
+        <v>8</v>
+      </c>
+      <c r="V123" t="n">
+        <v>19</v>
+      </c>
+      <c r="W123" t="n">
+        <v>16</v>
+      </c>
+      <c r="X123" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>16</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW123" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="DX123" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr"/>
+      <c r="EE123" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EF123" t="inlineStr"/>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr"/>
+      <c r="EM123" t="inlineStr"/>
+      <c r="EN123" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EO123" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EP123" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45990.71875</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>6</v>
+      </c>
+      <c r="K124" t="n">
+        <v>7</v>
+      </c>
+      <c r="L124" t="n">
+        <v>13</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>2</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="n">
+        <v>9</v>
+      </c>
+      <c r="U124" t="n">
+        <v>7</v>
+      </c>
+      <c r="V124" t="n">
+        <v>13</v>
+      </c>
+      <c r="W124" t="n">
+        <v>13</v>
+      </c>
+      <c r="X124" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW124" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="DX124" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr"/>
+      <c r="EE124" t="inlineStr"/>
+      <c r="EF124" t="inlineStr"/>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr"/>
+      <c r="EM124" t="inlineStr"/>
+      <c r="EN124" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EO124" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>16</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45990.82291666666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>11</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>5</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>12</v>
+      </c>
+      <c r="T125" t="n">
+        <v>6</v>
+      </c>
+      <c r="U125" t="n">
+        <v>17</v>
+      </c>
+      <c r="V125" t="n">
+        <v>6</v>
+      </c>
+      <c r="W125" t="n">
+        <v>12</v>
+      </c>
+      <c r="X125" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW125" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="DX125" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM125" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN125" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EO125" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EP125" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>16</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45991.52083333334</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>9</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4</v>
+      </c>
+      <c r="L126" t="n">
+        <v>13</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>6</v>
+      </c>
+      <c r="R126" t="n">
+        <v>5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>21</v>
+      </c>
+      <c r="T126" t="n">
+        <v>7</v>
+      </c>
+      <c r="U126" t="n">
+        <v>27</v>
+      </c>
+      <c r="V126" t="n">
+        <v>12</v>
+      </c>
+      <c r="W126" t="n">
+        <v>11</v>
+      </c>
+      <c r="X126" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>93</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>136</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>22</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>79</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW126" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="DX126" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr"/>
+      <c r="EL126" t="inlineStr"/>
+      <c r="EM126" t="inlineStr"/>
+      <c r="EN126" t="inlineStr"/>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>16</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45991.625</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>10</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" t="n">
+        <v>12</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6</v>
+      </c>
+      <c r="S127" t="n">
+        <v>15</v>
+      </c>
+      <c r="T127" t="n">
+        <v>5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>23</v>
+      </c>
+      <c r="V127" t="n">
+        <v>11</v>
+      </c>
+      <c r="W127" t="n">
+        <v>13</v>
+      </c>
+      <c r="X127" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW127" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="DX127" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr"/>
+      <c r="EM127" t="inlineStr"/>
+      <c r="EN127" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EO127" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EP127" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>16</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45991.72916666666</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>2</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>4</v>
+      </c>
+      <c r="T128" t="n">
+        <v>9</v>
+      </c>
+      <c r="U128" t="n">
+        <v>6</v>
+      </c>
+      <c r="V128" t="n">
+        <v>10</v>
+      </c>
+      <c r="W128" t="n">
+        <v>8</v>
+      </c>
+      <c r="X128" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>61</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>149</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>36</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>44</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW128" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="DX128" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM128" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EN128" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EO128" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EP128" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>16</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>45991.76041666666</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" t="n">
+        <v>6</v>
+      </c>
+      <c r="L129" t="n">
+        <v>11</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>4</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="n">
+        <v>10</v>
+      </c>
+      <c r="U129" t="n">
+        <v>19</v>
+      </c>
+      <c r="V129" t="n">
+        <v>14</v>
+      </c>
+      <c r="W129" t="n">
+        <v>9</v>
+      </c>
+      <c r="X129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW129" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="DX129" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="ED129" t="inlineStr"/>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr"/>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM129" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EN129" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EO129" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EP129" t="inlineStr">
+        <is>
+          <t>2.46</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -59656,7 +59656,7 @@
         <v>2</v>
       </c>
       <c r="R124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -59668,7 +59668,7 @@
         <v>7</v>
       </c>
       <c r="V124" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W124" t="n">
         <v>13</v>
@@ -59843,10 +59843,10 @@
         <v>0.8</v>
       </c>
       <c r="CA124" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="CB124" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="CC124" t="n">
         <v>1</v>
@@ -60117,7 +60117,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -60129,7 +60129,7 @@
         <v>6</v>
       </c>
       <c r="U125" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V125" t="n">
         <v>6</v>
@@ -60304,13 +60304,13 @@
         <v>92</v>
       </c>
       <c r="BZ125" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="CA125" t="n">
         <v>0.67</v>
       </c>
       <c r="CB125" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -60629,10 +60629,10 @@
         <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z126" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -61592,7 +61592,7 @@
         <v>2</v>
       </c>
       <c r="AD128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE128" t="n">
         <v>3.1</v>
@@ -61712,13 +61712,13 @@
         <v>1</v>
       </c>
       <c r="BR128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS128" t="n">
         <v>3</v>
       </c>
       <c r="BT128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU128" t="n">
         <v>1</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP129" headerRowCount="1">
-  <autoFilter ref="A1:EP129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP130" headerRowCount="1">
+  <autoFilter ref="A1:EP130"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP129"/>
+  <dimension ref="A1:EP130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE5" t="n">
         <v>1.13</v>
@@ -6577,7 +6577,7 @@
         <v>1.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>2</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -11406,7 +11406,7 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE22" t="n">
         <v>0.88</v>
@@ -18586,7 +18586,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE37" t="n">
         <v>1.67</v>
@@ -20997,7 +20997,7 @@
         <v>1.5</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -24810,7 +24810,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE50" t="n">
         <v>1.63</v>
@@ -27649,7 +27649,7 @@
         <v>1.75</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -37194,7 +37194,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE76" t="n">
         <v>1.25</v>
@@ -38637,7 +38637,7 @@
         <v>1.38</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -40510,7 +40510,7 @@
         <v>70</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE83" t="n">
         <v>0.75</v>
@@ -44313,7 +44313,7 @@
         <v>1.38</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -48589,7 +48589,7 @@
         <v>2.38</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -50954,7 +50954,7 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE105" t="n">
         <v>0.88</v>
@@ -57565,7 +57565,7 @@
         <v>1.38</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -58034,7 +58034,7 @@
         <v>54</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE120" t="n">
         <v>1.57</v>
@@ -62456,6 +62456,494 @@
       <c r="EP129" t="inlineStr">
         <is>
           <t>2.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>17</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>45996.82291666666</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2</v>
+      </c>
+      <c r="L130" t="n">
+        <v>7</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6</v>
+      </c>
+      <c r="S130" t="n">
+        <v>12</v>
+      </c>
+      <c r="T130" t="n">
+        <v>8</v>
+      </c>
+      <c r="U130" t="n">
+        <v>16</v>
+      </c>
+      <c r="V130" t="n">
+        <v>14</v>
+      </c>
+      <c r="W130" t="n">
+        <v>9</v>
+      </c>
+      <c r="X130" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>669388</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="DX130" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ130" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EN130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO130" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP130" t="inlineStr">
+        <is>
+          <t>1.97</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP130" headerRowCount="1">
-  <autoFilter ref="A1:EP130"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP137" headerRowCount="1">
+  <autoFilter ref="A1:EP137"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP130"/>
+  <dimension ref="A1:EP137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE2" t="n">
         <v>1.67</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>1.33</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4209,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         <v>2.38</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE9" t="n">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5630,10 +5630,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6102,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8030,10 +8030,10 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8518,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0.88</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE18" t="n">
         <v>0.89</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10446,7 +10446,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE20" t="n">
         <v>1.75</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         <v>1.33</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11897,7 +11897,7 @@
         <v>2.22</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12377,7 +12377,7 @@
         <v>1.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12862,7 +12862,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE25" t="n">
         <v>0.88</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         <v>1</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13817,7 +13817,7 @@
         <v>1.38</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14282,7 +14282,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE28" t="n">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14754,10 +14754,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15237,7 +15237,7 @@
         <v>0.5</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15698,7 +15698,7 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE31" t="n">
         <v>0.75</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16674,7 +16674,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE33" t="n">
         <v>0.75</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18098,7 +18098,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE36" t="n">
         <v>1.75</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19554,7 +19554,7 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE39" t="n">
         <v>1.75</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20034,7 +20034,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE40" t="n">
         <v>0.75</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE41" t="n">
         <v>0.75</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21485,7 +21485,7 @@
         <v>1.75</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21957,7 +21957,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22426,10 +22426,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22917,7 +22917,7 @@
         <v>1.38</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24813,7 +24813,7 @@
         <v>1.33</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25274,7 +25274,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE51" t="n">
         <v>1</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25746,10 +25746,10 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26237,7 +26237,7 @@
         <v>2.22</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26706,7 +26706,7 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE54" t="n">
         <v>0.75</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27181,7 +27181,7 @@
         <v>1.38</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28625,7 +28625,7 @@
         <v>1.5</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30054,10 +30054,10 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31006,7 +31006,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE63" t="n">
         <v>0.88</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32417,7 +32417,7 @@
         <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33381,7 +33381,7 @@
         <v>1.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33866,7 +33866,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE69" t="n">
         <v>0.75</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34330,10 +34330,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34802,7 +34802,7 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36237,7 +36237,7 @@
         <v>1.75</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36714,7 +36714,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE75" t="n">
         <v>1.75</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37197,7 +37197,7 @@
         <v>1.33</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37682,7 +37682,7 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE77" t="n">
         <v>0.88</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38165,7 +38165,7 @@
         <v>2.22</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39578,7 +39578,7 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE81" t="n">
         <v>0.88</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40985,7 +40985,7 @@
         <v>1</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF84" t="n">
         <v>1</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41454,10 +41454,10 @@
         <v>88</v>
       </c>
       <c r="DD85" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41934,10 +41934,10 @@
         <v>90</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF86" t="n">
         <v>0.8</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42862,10 +42862,10 @@
         <v>65</v>
       </c>
       <c r="DD88" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF88" t="n">
         <v>1.8</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43825,7 +43825,7 @@
         <v>1.5</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44310,7 +44310,7 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE91" t="n">
         <v>0.89</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44774,7 +44774,7 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE92" t="n">
         <v>0.88</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45257,7 +45257,7 @@
         <v>1.75</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45726,10 +45726,10 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46206,10 +46206,10 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47166,7 +47166,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE97" t="n">
         <v>1.75</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47629,7 +47629,7 @@
         <v>1.5</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49538,10 +49538,10 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50466,7 +50466,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE104" t="n">
         <v>0.75</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51421,7 +51421,7 @@
         <v>0.5</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51906,7 +51906,7 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE107" t="n">
         <v>0.88</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52834,7 +52834,7 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE109" t="n">
         <v>0.75</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53325,7 +53325,7 @@
         <v>2.22</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53794,10 +53794,10 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54269,7 +54269,7 @@
         <v>1.75</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54730,7 +54730,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE113" t="n">
         <v>1.67</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55189,7 +55189,7 @@
         <v>1.5</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55666,7 +55666,7 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE115" t="n">
         <v>0.88</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56138,7 +56138,7 @@
         <v>79</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE116" t="n">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56613,7 +56613,7 @@
         <v>2.38</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF117" t="n">
         <v>2.67</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57562,7 +57562,7 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE119" t="n">
         <v>0.89</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58037,7 +58037,7 @@
         <v>1.33</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58978,10 +58978,10 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60915,7 +60915,7 @@
         <v>2.87</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62523,13 +62523,13 @@
         <v>6</v>
       </c>
       <c r="S130" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T130" t="n">
         <v>8</v>
       </c>
       <c r="U130" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V130" t="n">
         <v>14</v>
@@ -62538,7 +62538,7 @@
         <v>9</v>
       </c>
       <c r="X130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y130" t="n">
         <v>50</v>
@@ -62704,13 +62704,13 @@
         <v>73</v>
       </c>
       <c r="BZ130" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="CA130" t="n">
         <v>1.59</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="CC130" t="n">
         <v>0</v>
@@ -62758,7 +62758,7 @@
         <v>1</v>
       </c>
       <c r="CR130" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CS130" t="n">
         <v>22</v>
@@ -62767,7 +62767,7 @@
         <v>1</v>
       </c>
       <c r="CU130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV130" t="n">
         <v>8</v>
@@ -62868,82 +62868,3398 @@
       </c>
       <c r="EA130" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EB130" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC130" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="ED130" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EE130" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EN130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO130" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP130" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>17</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>45997.625</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>9</v>
+      </c>
+      <c r="K131" t="n">
+        <v>5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>14</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>6</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2</v>
+      </c>
+      <c r="S131" t="n">
+        <v>9</v>
+      </c>
+      <c r="T131" t="n">
+        <v>9</v>
+      </c>
+      <c r="U131" t="n">
+        <v>15</v>
+      </c>
+      <c r="V131" t="n">
+        <v>11</v>
+      </c>
+      <c r="W131" t="n">
+        <v>7</v>
+      </c>
+      <c r="X131" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>51</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW131" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="DX131" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="ED131" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF131" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EF130" t="inlineStr">
+      <c r="EG131" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EH131" t="inlineStr"/>
+      <c r="EI131" t="inlineStr"/>
+      <c r="EJ131" t="inlineStr"/>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM131" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EN131" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EO131" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EP131" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>17</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>45997.71875</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2</v>
+      </c>
+      <c r="J132" t="n">
+        <v>8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>10</v>
+      </c>
+      <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="n">
+        <v>2</v>
+      </c>
+      <c r="U132" t="n">
+        <v>20</v>
+      </c>
+      <c r="V132" t="n">
+        <v>6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>13</v>
+      </c>
+      <c r="X132" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>86</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>148</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW132" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="DX132" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>8.83</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr"/>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr"/>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH132" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr"/>
+      <c r="EM132" t="inlineStr"/>
+      <c r="EN132" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO132" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EP132" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>17</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>45997.82291666666</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>8</v>
+      </c>
+      <c r="K133" t="n">
+        <v>6</v>
+      </c>
+      <c r="L133" t="n">
+        <v>14</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>6</v>
+      </c>
+      <c r="R133" t="n">
+        <v>8</v>
+      </c>
+      <c r="S133" t="n">
+        <v>8</v>
+      </c>
+      <c r="T133" t="n">
+        <v>11</v>
+      </c>
+      <c r="U133" t="n">
+        <v>14</v>
+      </c>
+      <c r="V133" t="n">
+        <v>19</v>
+      </c>
+      <c r="W133" t="n">
+        <v>7</v>
+      </c>
+      <c r="X133" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>13</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>44</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW133" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="DX133" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="ED133" t="inlineStr"/>
+      <c r="EE133" t="inlineStr"/>
+      <c r="EF133" t="inlineStr"/>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM133" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EN133" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EO133" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP133" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>17</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>45998.52083333334</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>4</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>7</v>
+      </c>
+      <c r="T134" t="n">
+        <v>7</v>
+      </c>
+      <c r="U134" t="n">
+        <v>11</v>
+      </c>
+      <c r="V134" t="n">
+        <v>7</v>
+      </c>
+      <c r="W134" t="n">
+        <v>11</v>
+      </c>
+      <c r="X134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>51</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>51</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW134" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="DX134" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr"/>
+      <c r="EE134" t="inlineStr"/>
+      <c r="EF134" t="inlineStr"/>
+      <c r="EG134" t="inlineStr"/>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM134" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EN134" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EO134" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EP134" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>17</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>45998.625</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>9</v>
+      </c>
+      <c r="L135" t="n">
+        <v>14</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>8</v>
+      </c>
+      <c r="R135" t="n">
+        <v>3</v>
+      </c>
+      <c r="S135" t="n">
+        <v>8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>10</v>
+      </c>
+      <c r="U135" t="n">
+        <v>16</v>
+      </c>
+      <c r="V135" t="n">
+        <v>13</v>
+      </c>
+      <c r="W135" t="n">
+        <v>11</v>
+      </c>
+      <c r="X135" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>534</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>14</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>87</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW135" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="DX135" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr"/>
+      <c r="EE135" t="inlineStr"/>
+      <c r="EF135" t="inlineStr"/>
+      <c r="EG135" t="inlineStr"/>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr"/>
+      <c r="EL135" t="inlineStr"/>
+      <c r="EM135" t="inlineStr"/>
+      <c r="EN135" t="inlineStr"/>
+      <c r="EO135" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EP135" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>17</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>45998.72916666666</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>10</v>
+      </c>
+      <c r="L136" t="n">
+        <v>13</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>8</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>10</v>
+      </c>
+      <c r="U136" t="n">
+        <v>11</v>
+      </c>
+      <c r="V136" t="n">
+        <v>18</v>
+      </c>
+      <c r="W136" t="n">
+        <v>12</v>
+      </c>
+      <c r="X136" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW136" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="DX136" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EG130" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="EH130" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EI130" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="EJ130" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EK130" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EL130" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EM130" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EN130" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EO130" t="inlineStr">
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EI136" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EJ136" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EP130" t="inlineStr">
-        <is>
-          <t>1.97</t>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EL136" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM136" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EN136" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO136" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EP136" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>17</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>45998.76041666666</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" t="n">
+        <v>3</v>
+      </c>
+      <c r="L137" t="n">
+        <v>7</v>
+      </c>
+      <c r="M137" t="n">
+        <v>2</v>
+      </c>
+      <c r="N137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>6</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="n">
+        <v>11</v>
+      </c>
+      <c r="T137" t="n">
+        <v>3</v>
+      </c>
+      <c r="U137" t="n">
+        <v>17</v>
+      </c>
+      <c r="V137" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" t="n">
+        <v>18</v>
+      </c>
+      <c r="X137" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW137" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="DX137" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI137" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM137" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EN137" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO137" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EP137" t="inlineStr">
+        <is>
+          <t>2.29</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -63029,10 +63029,10 @@
         <v>16</v>
       </c>
       <c r="Y131" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z131" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
@@ -63977,10 +63977,10 @@
         <v>9</v>
       </c>
       <c r="Y133" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z133" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr"/>
@@ -64661,7 +64661,7 @@
         <v>22</v>
       </c>
       <c r="CS134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
@@ -64895,13 +64895,13 @@
         <v>3</v>
       </c>
       <c r="S135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T135" t="n">
         <v>10</v>
       </c>
       <c r="U135" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V135" t="n">
         <v>13</v>
@@ -65076,13 +65076,13 @@
         <v>107</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="CA135" t="n">
         <v>1.47</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="CC135" t="n">
         <v>1</v>
@@ -65151,7 +65151,7 @@
         <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ135" t="n">
         <v>14</v>
@@ -65369,10 +65369,10 @@
         <v>11</v>
       </c>
       <c r="Y136" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z136" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
@@ -65589,7 +65589,7 @@
         <v>14</v>
       </c>
       <c r="CS136" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CT136" t="n">
         <v>1</v>
@@ -65833,7 +65833,7 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R137" t="n">
         <v>1</v>
@@ -65845,7 +65845,7 @@
         <v>3</v>
       </c>
       <c r="U137" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V137" t="n">
         <v>4</v>
@@ -66020,13 +66020,13 @@
         <v>103</v>
       </c>
       <c r="BZ137" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="CA137" t="n">
         <v>0.71</v>
       </c>
       <c r="CB137" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="CC137" t="n">
         <v>0</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP137" headerRowCount="1">
-  <autoFilter ref="A1:EP137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP145" headerRowCount="1">
+  <autoFilter ref="A1:EP145"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP137"/>
+  <dimension ref="A1:EP145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.56</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE3" t="n">
         <v>0.88</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3726,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         <v>1.44</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE12" t="n">
         <v>0.89</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7062,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE15" t="n">
         <v>1.38</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>2.75</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8998,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10449,7 +10449,7 @@
         <v>1.56</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10918,10 +10918,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE23" t="n">
         <v>1.22</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12374,7 +12374,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE24" t="n">
         <v>1.33</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>1.56</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13814,10 +13814,10 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE30" t="n">
         <v>1.38</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15701,7 +15701,7 @@
         <v>2.11</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16186,10 +16186,10 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16674,10 +16674,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17146,7 +17146,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE34" t="n">
         <v>0.88</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17618,10 +17618,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18101,7 +18101,7 @@
         <v>1.56</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18589,7 +18589,7 @@
         <v>1.33</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19066,10 +19066,10 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19554,10 +19554,10 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20037,7 +20037,7 @@
         <v>1.44</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20525,7 +20525,7 @@
         <v>1.56</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20994,7 +20994,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE42" t="n">
         <v>0.89</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21482,10 +21482,10 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22914,7 +22914,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
         <v>1.22</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23386,10 +23386,10 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23858,10 +23858,10 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24322,10 +24322,10 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24813,7 +24813,7 @@
         <v>1.33</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25746,7 +25746,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE52" t="n">
         <v>0.78</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26234,7 +26234,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE53" t="n">
         <v>1.33</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26709,7 +26709,7 @@
         <v>2.11</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27178,7 +27178,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE55" t="n">
         <v>0.78</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE56" t="n">
         <v>0.89</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28137,7 +28137,7 @@
         <v>1</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28622,7 +28622,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE58" t="n">
         <v>1.22</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29110,10 +29110,10 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29582,10 +29582,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30537,7 +30537,7 @@
         <v>2.38</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE64" t="n">
         <v>1</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31945,7 +31945,7 @@
         <v>2.38</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32902,10 +32902,10 @@
         <v>63</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33378,10 +33378,10 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33869,7 +33869,7 @@
         <v>2.75</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34802,7 +34802,7 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35274,10 +35274,10 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35746,10 +35746,10 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36234,7 +36234,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE74" t="n">
         <v>0.78</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36717,7 +36717,7 @@
         <v>1.44</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38162,7 +38162,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE78" t="n">
         <v>1.33</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38634,7 +38634,7 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE79" t="n">
         <v>0.89</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39093,7 +39093,7 @@
         <v>2.38</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39581,7 +39581,7 @@
         <v>1.56</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40050,10 +40050,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF82" t="n">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40513,7 +40513,7 @@
         <v>1.33</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF83" t="n">
         <v>1.6</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40985,7 +40985,7 @@
         <v>1</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF84" t="n">
         <v>1</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41934,7 +41934,7 @@
         <v>90</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE86" t="n">
         <v>1.33</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42398,10 +42398,10 @@
         <v>30</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF87" t="n">
         <v>0.4</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43350,7 +43350,7 @@
         <v>50</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43822,7 +43822,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE90" t="n">
         <v>1.38</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         <v>1.44</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45254,7 +45254,7 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE93" t="n">
         <v>1.33</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45729,7 +45729,7 @@
         <v>1.56</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46206,7 +46206,7 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE95" t="n">
         <v>1.22</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46678,10 +46678,10 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>2.75</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47626,7 +47626,7 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE98" t="n">
         <v>0.78</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48114,10 +48114,10 @@
         <v>50</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49066,10 +49066,10 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50469,7 +50469,7 @@
         <v>2.11</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51418,7 +51418,7 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE106" t="n">
         <v>1.22</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51906,10 +51906,10 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52378,10 +52378,10 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52837,7 +52837,7 @@
         <v>1.56</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53322,10 +53322,10 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54266,7 +54266,7 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE112" t="n">
         <v>1.33</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54733,7 +54733,7 @@
         <v>1.44</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55186,7 +55186,7 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE114" t="n">
         <v>1.22</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57090,10 +57090,10 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58493,7 +58493,7 @@
         <v>1</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59458,10 +59458,10 @@
         <v>50</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59930,7 +59930,7 @@
         <v>57</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE124" t="n">
         <v>0.88</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60394,10 +60394,10 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60885,7 +60885,7 @@
         <v>2.38</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF126" t="n">
         <v>2.71</v>
@@ -60915,7 +60915,7 @@
         <v>2.87</v>
       </c>
       <c r="DO126" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61346,10 +61346,10 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE127" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF127" t="n">
         <v>1.14</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61826,10 +61826,10 @@
         <v>50</v>
       </c>
       <c r="DD128" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF128" t="n">
         <v>2.13</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62314,10 +62314,10 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62827,7 +62827,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -63282,7 +63282,7 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE131" t="n">
         <v>1.33</v>
@@ -63315,7 +63315,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63791,7 +63791,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -64225,7 +64225,7 @@
         <v>2.11</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -64255,7 +64255,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64727,7 +64727,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65199,7 +65199,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65655,7 +65655,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66143,7 +66143,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66260,6 +66260,3830 @@
       <c r="EP137" t="inlineStr">
         <is>
           <t>2.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>18</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46003.82291666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>5</v>
+      </c>
+      <c r="K138" t="n">
+        <v>4</v>
+      </c>
+      <c r="L138" t="n">
+        <v>9</v>
+      </c>
+      <c r="M138" t="n">
+        <v>2</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>9</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6</v>
+      </c>
+      <c r="T138" t="n">
+        <v>9</v>
+      </c>
+      <c r="U138" t="n">
+        <v>9</v>
+      </c>
+      <c r="V138" t="n">
+        <v>18</v>
+      </c>
+      <c r="W138" t="n">
+        <v>13</v>
+      </c>
+      <c r="X138" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>690</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="DX138" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF138" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EH138" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI138" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EM138" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EN138" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EO138" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EP138" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>18</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46004.625</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="n">
+        <v>5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" t="n">
+        <v>9</v>
+      </c>
+      <c r="L139" t="n">
+        <v>15</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>7</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="n">
+        <v>6</v>
+      </c>
+      <c r="U139" t="n">
+        <v>17</v>
+      </c>
+      <c r="V139" t="n">
+        <v>12</v>
+      </c>
+      <c r="W139" t="n">
+        <v>12</v>
+      </c>
+      <c r="X139" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>76</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW139" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="DX139" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>5.16</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr"/>
+      <c r="EE139" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EF139" t="inlineStr"/>
+      <c r="EG139" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EL139" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EM139" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EN139" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EO139" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EP139" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>18</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46004.71875</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>4</v>
+      </c>
+      <c r="J140" t="n">
+        <v>3</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2</v>
+      </c>
+      <c r="L140" t="n">
+        <v>5</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" t="n">
+        <v>4</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="n">
+        <v>4</v>
+      </c>
+      <c r="U140" t="n">
+        <v>9</v>
+      </c>
+      <c r="V140" t="n">
+        <v>8</v>
+      </c>
+      <c r="W140" t="n">
+        <v>12</v>
+      </c>
+      <c r="X140" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>138</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="DX140" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr"/>
+      <c r="EE140" t="inlineStr"/>
+      <c r="EF140" t="inlineStr"/>
+      <c r="EG140" t="inlineStr"/>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM140" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EN140" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EO140" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP140" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>18</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46004.82291666666</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>6</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2</v>
+      </c>
+      <c r="L141" t="n">
+        <v>8</v>
+      </c>
+      <c r="M141" t="n">
+        <v>4</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>9</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2</v>
+      </c>
+      <c r="S141" t="n">
+        <v>13</v>
+      </c>
+      <c r="T141" t="n">
+        <v>6</v>
+      </c>
+      <c r="U141" t="n">
+        <v>22</v>
+      </c>
+      <c r="V141" t="n">
+        <v>8</v>
+      </c>
+      <c r="W141" t="n">
+        <v>11</v>
+      </c>
+      <c r="X141" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>61</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW141" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="DX141" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="ED141" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EE141" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF141" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EG141" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EH141" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI141" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL141" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM141" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EN141" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EO141" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EP141" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>18</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46005.52083333334</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2</v>
+      </c>
+      <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>2</v>
+      </c>
+      <c r="R142" t="n">
+        <v>5</v>
+      </c>
+      <c r="S142" t="n">
+        <v>12</v>
+      </c>
+      <c r="T142" t="n">
+        <v>8</v>
+      </c>
+      <c r="U142" t="n">
+        <v>14</v>
+      </c>
+      <c r="V142" t="n">
+        <v>13</v>
+      </c>
+      <c r="W142" t="n">
+        <v>7</v>
+      </c>
+      <c r="X142" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>125</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="DX142" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EC142" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr"/>
+      <c r="EE142" t="inlineStr"/>
+      <c r="EF142" t="inlineStr"/>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EI142" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EJ142" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EK142" t="inlineStr"/>
+      <c r="EL142" t="inlineStr"/>
+      <c r="EM142" t="inlineStr"/>
+      <c r="EN142" t="inlineStr"/>
+      <c r="EO142" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EP142" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>18</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>46005.625</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>5</v>
+      </c>
+      <c r="I143" t="n">
+        <v>6</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" t="n">
+        <v>3</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>9</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>13</v>
+      </c>
+      <c r="U143" t="n">
+        <v>6</v>
+      </c>
+      <c r="V143" t="n">
+        <v>22</v>
+      </c>
+      <c r="W143" t="n">
+        <v>6</v>
+      </c>
+      <c r="X143" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>47</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>11</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>53</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW143" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="DX143" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EC143" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr"/>
+      <c r="EE143" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF143" t="inlineStr"/>
+      <c r="EG143" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EH143" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI143" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL143" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EM143" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EN143" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO143" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EP143" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>18</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>46005.72916666666</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>4</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>9</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5</v>
+      </c>
+      <c r="R144" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="n">
+        <v>12</v>
+      </c>
+      <c r="U144" t="n">
+        <v>10</v>
+      </c>
+      <c r="V144" t="n">
+        <v>13</v>
+      </c>
+      <c r="W144" t="n">
+        <v>8</v>
+      </c>
+      <c r="X144" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV144" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW144" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK144" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL144" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM144" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN144" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DO144" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW144" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="DX144" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC144" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EH144" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL144" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EM144" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EN144" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EO144" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EP144" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>18</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>46005.76041666666</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>9</v>
+      </c>
+      <c r="K145" t="n">
+        <v>7</v>
+      </c>
+      <c r="L145" t="n">
+        <v>16</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>6</v>
+      </c>
+      <c r="R145" t="n">
+        <v>3</v>
+      </c>
+      <c r="S145" t="n">
+        <v>16</v>
+      </c>
+      <c r="T145" t="n">
+        <v>7</v>
+      </c>
+      <c r="U145" t="n">
+        <v>22</v>
+      </c>
+      <c r="V145" t="n">
+        <v>10</v>
+      </c>
+      <c r="W145" t="n">
+        <v>13</v>
+      </c>
+      <c r="X145" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS145" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU145" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV145" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX145" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY145" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ145" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA145" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB145" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC145" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE145" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF145" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG145" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH145" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI145" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ145" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK145" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL145" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM145" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN145" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="DO145" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW145" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="DX145" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DY145" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ145" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="EA145" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EB145" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EC145" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="ED145" t="inlineStr"/>
+      <c r="EE145" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EF145" t="inlineStr"/>
+      <c r="EG145" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH145" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI145" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EJ145" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EK145" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL145" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EM145" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EN145" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO145" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EP145" t="inlineStr">
+        <is>
+          <t>2.40</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -67313,10 +67313,10 @@
         <v>13</v>
       </c>
       <c r="Y140" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z140" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
@@ -67767,13 +67767,13 @@
         <v>2</v>
       </c>
       <c r="S141" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T141" t="n">
         <v>6</v>
       </c>
       <c r="U141" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V141" t="n">
         <v>8</v>
@@ -67785,10 +67785,10 @@
         <v>18</v>
       </c>
       <c r="Y141" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z141" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
@@ -67948,13 +67948,13 @@
         <v>70</v>
       </c>
       <c r="BZ141" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="CA141" t="n">
         <v>0.98</v>
       </c>
       <c r="CB141" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="CC141" t="n">
         <v>0</v>
@@ -68249,7 +68249,7 @@
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R142" t="n">
         <v>5</v>
@@ -68261,7 +68261,7 @@
         <v>8</v>
       </c>
       <c r="U142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V142" t="n">
         <v>13</v>
@@ -68436,13 +68436,13 @@
         <v>87</v>
       </c>
       <c r="BZ142" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="CA142" t="n">
         <v>1.34</v>
       </c>
       <c r="CB142" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="CC142" t="n">
         <v>0</v>
@@ -68714,13 +68714,13 @@
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U143" t="n">
         <v>6</v>
       </c>
       <c r="V143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W143" t="n">
         <v>6</v>
@@ -68887,10 +68887,10 @@
         <v>0.68</v>
       </c>
       <c r="CA143" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="CB143" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="CC143" t="n">
         <v>0</v>
@@ -68938,7 +68938,7 @@
         <v>1</v>
       </c>
       <c r="CR143" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CS143" t="n">
         <v>16</v>
@@ -68956,7 +68956,7 @@
         <v>1</v>
       </c>
       <c r="CX143" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CY143" t="n">
         <v>6</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP145" headerRowCount="1">
-  <autoFilter ref="A1:EP145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP150" headerRowCount="1">
+  <autoFilter ref="A1:EP150"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP145"/>
+  <dimension ref="A1:EP150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE3" t="n">
         <v>0.88</v>
@@ -3241,7 +3241,7 @@
         <v>1.33</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5161,7 +5161,7 @@
         <v>2.11</v>
       </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -6102,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7065,7 +7065,7 @@
         <v>1.56</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8518,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE16" t="n">
         <v>1.11</v>
@@ -8998,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE17" t="n">
         <v>1.56</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE19" t="n">
         <v>0.88</v>
@@ -10446,7 +10446,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE20" t="n">
         <v>1.89</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11897,7 +11897,7 @@
         <v>2.3</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -12377,7 +12377,7 @@
         <v>1.33</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         <v>1</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14285,7 +14285,7 @@
         <v>1.44</v>
       </c>
       <c r="DE28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -14754,10 +14754,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE30" t="n">
         <v>1.38</v>
@@ -15701,7 +15701,7 @@
         <v>2.11</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -16186,7 +16186,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19066,7 +19066,7 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE38" t="n">
         <v>1.11</v>
@@ -20037,7 +20037,7 @@
         <v>1.44</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -20994,7 +20994,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE42" t="n">
         <v>0.89</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21957,7 +21957,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -22426,7 +22426,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE45" t="n">
         <v>1.38</v>
@@ -22917,7 +22917,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -24322,7 +24322,7 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE49" t="n">
         <v>1.6</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25277,7 +25277,7 @@
         <v>1.56</v>
       </c>
       <c r="DE51" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -26237,7 +26237,7 @@
         <v>2.3</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28137,7 +28137,7 @@
         <v>1</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -28622,10 +28622,10 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30054,10 +30054,10 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30534,7 +30534,7 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE62" t="n">
         <v>1.56</v>
@@ -31481,7 +31481,7 @@
         <v>2.3</v>
       </c>
       <c r="DE64" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF64" t="n">
         <v>1.25</v>
@@ -31942,7 +31942,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE65" t="n">
         <v>0.78</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33866,7 +33866,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE69" t="n">
         <v>0.78</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34333,7 +34333,7 @@
         <v>2.11</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -34805,7 +34805,7 @@
         <v>0.6</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -35274,7 +35274,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE72" t="n">
         <v>1.89</v>
@@ -35746,10 +35746,10 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -37197,7 +37197,7 @@
         <v>1.33</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -38165,7 +38165,7 @@
         <v>2.3</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39090,7 +39090,7 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE80" t="n">
         <v>1.6</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39578,7 +39578,7 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE81" t="n">
         <v>1.11</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -41454,7 +41454,7 @@
         <v>88</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE85" t="n">
         <v>0.78</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41937,7 +41937,7 @@
         <v>0.6</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF86" t="n">
         <v>0.8</v>
@@ -42398,7 +42398,7 @@
         <v>30</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE87" t="n">
         <v>1.89</v>
@@ -43353,7 +43353,7 @@
         <v>1.33</v>
       </c>
       <c r="DE89" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF89" t="n">
         <v>1.4</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43822,7 +43822,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE90" t="n">
         <v>1.38</v>
@@ -44310,7 +44310,7 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE91" t="n">
         <v>0.89</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -45257,7 +45257,7 @@
         <v>1.56</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46209,7 +46209,7 @@
         <v>0.6</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -46681,7 +46681,7 @@
         <v>1.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47166,7 +47166,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE97" t="n">
         <v>1.56</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48586,7 +48586,7 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE100" t="n">
         <v>0.89</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49538,10 +49538,10 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50005,7 +50005,7 @@
         <v>1</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF103" t="n">
         <v>0.83</v>
@@ -51418,10 +51418,10 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -52378,7 +52378,7 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE108" t="n">
         <v>0.78</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52837,7 +52837,7 @@
         <v>1.56</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -53797,7 +53797,7 @@
         <v>2.11</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -54269,7 +54269,7 @@
         <v>1.56</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -55189,7 +55189,7 @@
         <v>1.33</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55666,7 +55666,7 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE115" t="n">
         <v>0.88</v>
@@ -56138,10 +56138,10 @@
         <v>79</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE116" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF116" t="n">
         <v>1.43</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56610,7 +56610,7 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE117" t="n">
         <v>0.78</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -58981,7 +58981,7 @@
         <v>1.44</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -59458,7 +59458,7 @@
         <v>50</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE123" t="n">
         <v>0.78</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -60394,10 +60394,10 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60882,7 +60882,7 @@
         <v>64</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE126" t="n">
         <v>1</v>
@@ -62827,7 +62827,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -63285,7 +63285,7 @@
         <v>0.6</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF131" t="n">
         <v>0.75</v>
@@ -63758,10 +63758,10 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE132" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF132" t="n">
         <v>3</v>
@@ -63791,7 +63791,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -65166,7 +65166,7 @@
         <v>59</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE135" t="n">
         <v>1.38</v>
@@ -65625,7 +65625,7 @@
         <v>1.56</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF136" t="n">
         <v>1.38</v>
@@ -66113,7 +66113,7 @@
         <v>1</v>
       </c>
       <c r="DE137" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -67569,7 +67569,7 @@
         <v>1.33</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -67599,7 +67599,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -68974,7 +68974,7 @@
         <v>53</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE143" t="n">
         <v>1.6</v>
@@ -69007,7 +69007,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69454,7 +69454,7 @@
         <v>66</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE144" t="n">
         <v>1.6</v>
@@ -69487,7 +69487,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -69975,7 +69975,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70084,6 +70084,2406 @@
       <c r="EP145" t="inlineStr">
         <is>
           <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>19</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46010.82291666666</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>4</v>
+      </c>
+      <c r="J146" t="n">
+        <v>8</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>9</v>
+      </c>
+      <c r="M146" t="n">
+        <v>2</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>6</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6</v>
+      </c>
+      <c r="S146" t="n">
+        <v>11</v>
+      </c>
+      <c r="T146" t="n">
+        <v>3</v>
+      </c>
+      <c r="U146" t="n">
+        <v>17</v>
+      </c>
+      <c r="V146" t="n">
+        <v>9</v>
+      </c>
+      <c r="W146" t="n">
+        <v>13</v>
+      </c>
+      <c r="X146" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV146" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW146" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX146" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY146" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ146" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA146" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CB146" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR146" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS146" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU146" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV146" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX146" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY146" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ146" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA146" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB146" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC146" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD146" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF146" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH146" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DI146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ146" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK146" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL146" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM146" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DN146" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DO146" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW146" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="DX146" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="DY146" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ146" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA146" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EB146" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EC146" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="ED146" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EE146" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF146" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EG146" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EH146" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI146" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EJ146" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EK146" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EL146" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EM146" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EN146" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EO146" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP146" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>19</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46011.625</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>4</v>
+      </c>
+      <c r="L147" t="n">
+        <v>9</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>4</v>
+      </c>
+      <c r="R147" t="n">
+        <v>4</v>
+      </c>
+      <c r="S147" t="n">
+        <v>6</v>
+      </c>
+      <c r="T147" t="n">
+        <v>4</v>
+      </c>
+      <c r="U147" t="n">
+        <v>10</v>
+      </c>
+      <c r="V147" t="n">
+        <v>8</v>
+      </c>
+      <c r="W147" t="n">
+        <v>17</v>
+      </c>
+      <c r="X147" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV147" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW147" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX147" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY147" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ147" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB147" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR147" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS147" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU147" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV147" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX147" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY147" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ147" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA147" t="n">
+        <v>56</v>
+      </c>
+      <c r="DB147" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC147" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD147" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF147" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DG147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH147" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ147" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK147" t="n">
+        <v>44</v>
+      </c>
+      <c r="DL147" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM147" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN147" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DO147" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW147" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="DX147" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="DY147" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="DZ147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA147" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EB147" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EC147" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="ED147" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EE147" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF147" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG147" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EH147" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI147" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="EJ147" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EK147" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL147" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM147" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EN147" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO147" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EP147" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>19</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>46011.71875</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>9</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>4</v>
+      </c>
+      <c r="R148" t="n">
+        <v>3</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="n">
+        <v>11</v>
+      </c>
+      <c r="U148" t="n">
+        <v>14</v>
+      </c>
+      <c r="V148" t="n">
+        <v>14</v>
+      </c>
+      <c r="W148" t="n">
+        <v>10</v>
+      </c>
+      <c r="X148" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>534</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV148" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW148" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX148" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY148" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ148" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB148" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM148" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR148" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS148" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU148" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV148" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX148" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY148" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ148" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA148" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB148" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC148" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DE148" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF148" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG148" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI148" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ148" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK148" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL148" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM148" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN148" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DO148" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW148" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="DX148" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="DY148" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ148" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA148" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EB148" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="EC148" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="ED148" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EE148" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF148" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EG148" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EH148" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI148" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EJ148" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK148" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EL148" t="inlineStr"/>
+      <c r="EM148" t="inlineStr"/>
+      <c r="EN148" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO148" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EP148" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>19</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46011.82291666666</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>3</v>
+      </c>
+      <c r="L149" t="n">
+        <v>8</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>5</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3</v>
+      </c>
+      <c r="T149" t="n">
+        <v>9</v>
+      </c>
+      <c r="U149" t="n">
+        <v>8</v>
+      </c>
+      <c r="V149" t="n">
+        <v>9</v>
+      </c>
+      <c r="W149" t="n">
+        <v>10</v>
+      </c>
+      <c r="X149" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV149" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW149" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX149" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY149" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ149" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA149" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB149" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR149" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS149" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU149" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV149" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX149" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY149" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ149" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA149" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB149" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC149" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD149" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE149" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DF149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH149" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DI149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DJ149" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK149" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL149" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DM149" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN149" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DO149" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW149" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="DX149" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DY149" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ149" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA149" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EB149" t="inlineStr">
+        <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="EC149" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="ED149" t="inlineStr"/>
+      <c r="EE149" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EF149" t="inlineStr"/>
+      <c r="EG149" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH149" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI149" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EJ149" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EK149" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EL149" t="inlineStr"/>
+      <c r="EM149" t="inlineStr"/>
+      <c r="EN149" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EO149" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EP149" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>19</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>46012.52083333334</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>10</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" t="n">
+        <v>12</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>3</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2</v>
+      </c>
+      <c r="S150" t="n">
+        <v>19</v>
+      </c>
+      <c r="T150" t="n">
+        <v>4</v>
+      </c>
+      <c r="U150" t="n">
+        <v>22</v>
+      </c>
+      <c r="V150" t="n">
+        <v>6</v>
+      </c>
+      <c r="W150" t="n">
+        <v>9</v>
+      </c>
+      <c r="X150" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV150" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW150" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX150" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY150" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ150" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CA150" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB150" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR150" t="n">
+        <v>37</v>
+      </c>
+      <c r="CS150" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU150" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV150" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX150" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY150" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ150" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA150" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB150" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC150" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD150" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DE150" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF150" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DG150" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH150" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DJ150" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK150" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL150" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DM150" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN150" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DO150" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW150" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="DX150" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="DY150" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="DZ150" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA150" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EB150" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="EC150" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="ED150" t="inlineStr"/>
+      <c r="EE150" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EF150" t="inlineStr"/>
+      <c r="EG150" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EH150" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EI150" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ150" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK150" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL150" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM150" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EN150" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO150" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EP150" t="inlineStr">
+        <is>
+          <t>2.28</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP150" headerRowCount="1">
-  <autoFilter ref="A1:EP150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP153" headerRowCount="1">
+  <autoFilter ref="A1:EP153"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP150"/>
+  <dimension ref="A1:EP153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.6</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2285,7 +2285,7 @@
         <v>0.4</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>1.33</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE7" t="n">
         <v>0.78</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE9" t="n">
         <v>0.9</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8033,7 +8033,7 @@
         <v>0.6</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE18" t="n">
         <v>0.89</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9969,7 +9969,7 @@
         <v>2.44</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10449,7 +10449,7 @@
         <v>1.7</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12862,7 +12862,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
         <v>1.11</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13342,7 +13342,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE26" t="n">
         <v>1.3</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15237,7 +15237,7 @@
         <v>0.4</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15698,7 +15698,7 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE31" t="n">
         <v>0.7</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17149,7 +17149,7 @@
         <v>1.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18098,10 +18098,10 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21954,7 +21954,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE44" t="n">
         <v>1.5</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22429,7 +22429,7 @@
         <v>2.78</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23389,7 +23389,7 @@
         <v>1.33</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -25274,7 +25274,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE51" t="n">
         <v>0.9</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26706,7 +26706,7 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE54" t="n">
         <v>0.78</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -28134,7 +28134,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE57" t="n">
         <v>0.7</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31009,7 +31009,7 @@
         <v>1.44</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32414,10 +32414,10 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -34330,7 +34330,7 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE70" t="n">
         <v>1.3</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35277,7 +35277,7 @@
         <v>1.4</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37682,10 +37682,10 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40982,7 +40982,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE84" t="n">
         <v>1.6</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42401,7 +42401,7 @@
         <v>0.4</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF87" t="n">
         <v>0.4</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42862,10 +42862,10 @@
         <v>65</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF88" t="n">
         <v>1.8</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43825,7 +43825,7 @@
         <v>1.4</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45726,7 +45726,7 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE94" t="n">
         <v>1.6</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -49069,7 +49069,7 @@
         <v>2.3</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -50002,7 +50002,7 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE103" t="n">
         <v>0.9</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50466,7 +50466,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE104" t="n">
         <v>1</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50957,7 +50957,7 @@
         <v>1.33</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52834,7 +52834,7 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE109" t="n">
         <v>0.7</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53794,7 +53794,7 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE111" t="n">
         <v>1.5</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55669,7 +55669,7 @@
         <v>2.78</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -57093,7 +57093,7 @@
         <v>1.33</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57562,7 +57562,7 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE119" t="n">
         <v>0.89</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58037,7 +58037,7 @@
         <v>1.33</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58490,7 +58490,7 @@
         <v>62</v>
       </c>
       <c r="DD121" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE121" t="n">
         <v>1.56</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59933,7 +59933,7 @@
         <v>1.33</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF124" t="n">
         <v>1.43</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60915,7 +60915,7 @@
         <v>2.87</v>
       </c>
       <c r="DO126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -63315,7 +63315,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -64222,7 +64222,7 @@
         <v>69</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE133" t="n">
         <v>1.6</v>
@@ -64255,7 +64255,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64727,7 +64727,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65169,7 +65169,7 @@
         <v>1.7</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -65199,7 +65199,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65622,7 +65622,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE136" t="n">
         <v>1.3</v>
@@ -65655,7 +65655,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66110,7 +66110,7 @@
         <v>69</v>
       </c>
       <c r="DD137" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE137" t="n">
         <v>1.1</v>
@@ -66143,7 +66143,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66631,7 +66631,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67089,7 +67089,7 @@
         <v>0.6</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF139" t="n">
         <v>0.67</v>
@@ -67119,7 +67119,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -68071,7 +68071,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -68559,7 +68559,7 @@
         <v>2.67</v>
       </c>
       <c r="DO142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -70148,13 +70148,13 @@
         <v>6</v>
       </c>
       <c r="R146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S146" t="n">
         <v>11</v>
       </c>
       <c r="T146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U146" t="n">
         <v>17</v>
@@ -70335,10 +70335,10 @@
         <v>1.8</v>
       </c>
       <c r="CA146" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="CB146" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="CC146" t="n">
         <v>0</v>
@@ -71137,10 +71137,10 @@
         <v>5</v>
       </c>
       <c r="Y148" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z148" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
@@ -72416,29 +72416,29 @@
       </c>
       <c r="EA150" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr"/>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr"/>
       <c r="EG150" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EH150" t="inlineStr">
@@ -72448,17 +72448,17 @@
       </c>
       <c r="EI150" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL150" t="inlineStr">
@@ -72473,17 +72473,1441 @@
       </c>
       <c r="EN150" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EO150" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP150" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>19</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46012.625</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8</v>
+      </c>
+      <c r="M151" t="n">
+        <v>2</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>5</v>
+      </c>
+      <c r="R151" t="n">
+        <v>2</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="n">
+        <v>8</v>
+      </c>
+      <c r="U151" t="n">
+        <v>9</v>
+      </c>
+      <c r="V151" t="n">
+        <v>10</v>
+      </c>
+      <c r="W151" t="n">
+        <v>12</v>
+      </c>
+      <c r="X151" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY151" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ151" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA151" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB151" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ151" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK151" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL151" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DM151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN151" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO151" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW151" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DX151" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="DY151" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ151" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA151" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EB151" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="EC151" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr"/>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr"/>
+      <c r="EG151" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EH151" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EI151" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EJ151" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK151" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EL151" t="inlineStr"/>
+      <c r="EM151" t="inlineStr"/>
+      <c r="EN151" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EO151" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EP151" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>19</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>46012.72916666666</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2</v>
+      </c>
+      <c r="I152" t="n">
+        <v>4</v>
+      </c>
+      <c r="J152" t="n">
+        <v>6</v>
+      </c>
+      <c r="K152" t="n">
+        <v>5</v>
+      </c>
+      <c r="L152" t="n">
+        <v>11</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>3</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>9</v>
+      </c>
+      <c r="R152" t="n">
+        <v>3</v>
+      </c>
+      <c r="S152" t="n">
+        <v>14</v>
+      </c>
+      <c r="T152" t="n">
+        <v>9</v>
+      </c>
+      <c r="U152" t="n">
+        <v>23</v>
+      </c>
+      <c r="V152" t="n">
+        <v>12</v>
+      </c>
+      <c r="W152" t="n">
+        <v>12</v>
+      </c>
+      <c r="X152" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV152" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW152" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX152" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY152" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ152" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CA152" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB152" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR152" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS152" t="n">
+        <v>36</v>
+      </c>
+      <c r="CT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU152" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV152" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX152" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY152" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ152" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA152" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB152" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC152" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE152" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH152" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DI152" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DJ152" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK152" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL152" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM152" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN152" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO152" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW152" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="DX152" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="DY152" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="DZ152" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA152" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EB152" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EC152" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED152" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EE152" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EG152" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EH152" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI152" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EJ152" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK152" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL152" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EM152" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EN152" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO152" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP152" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>19</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>46012.76041666666</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" t="n">
+        <v>7</v>
+      </c>
+      <c r="L153" t="n">
+        <v>15</v>
+      </c>
+      <c r="M153" t="n">
+        <v>5</v>
+      </c>
+      <c r="N153" t="n">
+        <v>5</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>3</v>
+      </c>
+      <c r="S153" t="n">
+        <v>14</v>
+      </c>
+      <c r="T153" t="n">
+        <v>8</v>
+      </c>
+      <c r="U153" t="n">
+        <v>18</v>
+      </c>
+      <c r="V153" t="n">
+        <v>11</v>
+      </c>
+      <c r="W153" t="n">
+        <v>21</v>
+      </c>
+      <c r="X153" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>2567</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY153" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA153" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB153" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR153" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS153" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU153" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV153" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX153" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY153" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ153" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA153" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB153" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC153" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD153" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DE153" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF153" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG153" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH153" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI153" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="DJ153" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK153" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL153" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM153" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN153" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO153" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW153" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="DX153" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="DY153" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA153" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EB153" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EC153" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="ED153" t="inlineStr"/>
+      <c r="EE153" t="inlineStr"/>
+      <c r="EF153" t="inlineStr"/>
+      <c r="EG153" t="inlineStr"/>
+      <c r="EH153" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EI153" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EJ153" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EK153" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EL153" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM153" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN153" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EO153" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EP153" t="inlineStr">
+        <is>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -72089,10 +72089,10 @@
         <v>12</v>
       </c>
       <c r="Y150" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Z150" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP153" headerRowCount="1">
-  <autoFilter ref="A1:EP153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP161" headerRowCount="1">
+  <autoFilter ref="A1:EP161"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP153"/>
+  <dimension ref="A1:EP161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1802,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE5" t="n">
         <v>1.5</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3726,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4209,7 +4209,7 @@
         <v>0.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5630,10 +5630,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         <v>1.7</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6574,10 +6574,10 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE13" t="n">
         <v>0.7</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE15" t="n">
         <v>1.33</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>2.78</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9001,7 +9001,7 @@
         <v>1.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>2.2</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10918,10 +10918,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11406,10 +11406,10 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11894,10 +11894,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12374,7 +12374,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE24" t="n">
         <v>1.3</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12862,10 +12862,10 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13817,7 +13817,7 @@
         <v>1.33</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14282,7 +14282,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE28" t="n">
         <v>0.9</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16674,10 +16674,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17146,7 +17146,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE34" t="n">
         <v>1.11</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17621,7 +17621,7 @@
         <v>1.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18098,7 +18098,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE36" t="n">
         <v>1.7</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18586,10 +18586,10 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19069,7 +19069,7 @@
         <v>0.4</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19554,10 +19554,10 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20034,7 +20034,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE40" t="n">
         <v>0.7</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20997,7 +20997,7 @@
         <v>1.4</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21482,10 +21482,10 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22914,10 +22914,10 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23386,7 +23386,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE47" t="n">
         <v>1.7</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23861,7 +23861,7 @@
         <v>1.33</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24325,7 +24325,7 @@
         <v>0.4</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24810,10 +24810,10 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25274,7 +25274,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE51" t="n">
         <v>0.9</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25746,10 +25746,10 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26234,7 +26234,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE53" t="n">
         <v>1.3</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26709,7 +26709,7 @@
         <v>2.2</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27178,10 +27178,10 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27646,10 +27646,10 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28625,7 +28625,7 @@
         <v>1.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29110,7 +29110,7 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE59" t="n">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29582,10 +29582,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30537,7 +30537,7 @@
         <v>2.44</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31006,7 +31006,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE63" t="n">
         <v>1.11</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE64" t="n">
         <v>0.9</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31945,7 +31945,7 @@
         <v>2.44</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33378,10 +33378,10 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33869,7 +33869,7 @@
         <v>2.78</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34802,7 +34802,7 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE71" t="n">
         <v>0.9</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36234,10 +36234,10 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36714,10 +36714,10 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37194,10 +37194,10 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37682,7 +37682,7 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE77" t="n">
         <v>1.11</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38162,7 +38162,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE78" t="n">
         <v>1.5</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38634,10 +38634,10 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39093,7 +39093,7 @@
         <v>2.44</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39581,7 +39581,7 @@
         <v>1.7</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40050,7 +40050,7 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE82" t="n">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40510,10 +40510,10 @@
         <v>70</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF83" t="n">
         <v>1.6</v>
@@ -40543,7 +40543,7 @@
         <v>2.79</v>
       </c>
       <c r="DO83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40985,7 +40985,7 @@
         <v>0.9</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF84" t="n">
         <v>1</v>
@@ -41015,7 +41015,7 @@
         <v>3.36</v>
       </c>
       <c r="DO84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41457,7 +41457,7 @@
         <v>2.78</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41487,7 +41487,7 @@
         <v>3.64</v>
       </c>
       <c r="DO85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41934,7 +41934,7 @@
         <v>90</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE86" t="n">
         <v>1.3</v>
@@ -41967,7 +41967,7 @@
         <v>3.48</v>
       </c>
       <c r="DO86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42431,7 +42431,7 @@
         <v>2.27</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42895,7 +42895,7 @@
         <v>2.97</v>
       </c>
       <c r="DO88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43383,7 +43383,7 @@
         <v>2.85</v>
       </c>
       <c r="DO89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44313,7 +44313,7 @@
         <v>1.7</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44774,10 +44774,10 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45254,7 +45254,7 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE93" t="n">
         <v>1.5</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45726,10 +45726,10 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46206,10 +46206,10 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46678,7 +46678,7 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE96" t="n">
         <v>0.7</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>2.78</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47626,10 +47626,10 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48117,7 +48117,7 @@
         <v>1.33</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48589,7 +48589,7 @@
         <v>2.44</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49066,7 +49066,7 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE101" t="n">
         <v>1.7</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50499,7 +50499,7 @@
         <v>2.71</v>
       </c>
       <c r="DO104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50954,7 +50954,7 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE105" t="n">
         <v>1.11</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51421,7 +51421,7 @@
         <v>0.4</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51906,10 +51906,10 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52381,7 +52381,7 @@
         <v>1.4</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52834,7 +52834,7 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE109" t="n">
         <v>0.7</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53322,10 +53322,10 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54266,7 +54266,7 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE112" t="n">
         <v>1.3</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54730,10 +54730,10 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55186,10 +55186,10 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56613,7 +56613,7 @@
         <v>2.44</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF117" t="n">
         <v>2.67</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57090,7 +57090,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE118" t="n">
         <v>1.7</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57562,10 +57562,10 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58034,7 +58034,7 @@
         <v>54</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE120" t="n">
         <v>1.33</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58493,7 +58493,7 @@
         <v>0.9</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58978,7 +58978,7 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE122" t="n">
         <v>1.5</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59461,7 +59461,7 @@
         <v>0.4</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60915,7 +60915,7 @@
         <v>2.87</v>
       </c>
       <c r="DO126" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61346,10 +61346,10 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF127" t="n">
         <v>1.14</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61826,10 +61826,10 @@
         <v>50</v>
       </c>
       <c r="DD128" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF128" t="n">
         <v>2.13</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62314,10 +62314,10 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62794,10 +62794,10 @@
         <v>63</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF130" t="n">
         <v>1.5</v>
@@ -62827,7 +62827,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -63282,7 +63282,7 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE131" t="n">
         <v>1.5</v>
@@ -63315,7 +63315,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63791,7 +63791,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -64225,7 +64225,7 @@
         <v>2.2</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -64255,7 +64255,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64694,10 +64694,10 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE134" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF134" t="n">
         <v>1.25</v>
@@ -64727,7 +64727,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65199,7 +65199,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65622,7 +65622,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE136" t="n">
         <v>1.3</v>
@@ -65655,7 +65655,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66113,7 +66113,7 @@
         <v>0.9</v>
       </c>
       <c r="DE137" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -66143,7 +66143,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66598,10 +66598,10 @@
         <v>63</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF138" t="n">
         <v>1.5</v>
@@ -66631,7 +66631,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67086,7 +67086,7 @@
         <v>88</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DE139" t="n">
         <v>1.7</v>
@@ -67119,7 +67119,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67599,7 +67599,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -68038,10 +68038,10 @@
         <v>66</v>
       </c>
       <c r="DD141" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DE141" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF141" t="n">
         <v>2.22</v>
@@ -68071,7 +68071,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -68526,7 +68526,7 @@
         <v>69</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE142" t="n">
         <v>1</v>
@@ -68559,7 +68559,7 @@
         <v>2.67</v>
       </c>
       <c r="DO142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -68977,7 +68977,7 @@
         <v>0.4</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF143" t="n">
         <v>0.5</v>
@@ -69007,7 +69007,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69457,7 +69457,7 @@
         <v>1.4</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF144" t="n">
         <v>1.5</v>
@@ -69487,7 +69487,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -69942,10 +69942,10 @@
         <v>82</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF145" t="n">
         <v>1.38</v>
@@ -69975,7 +69975,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70455,7 +70455,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70935,7 +70935,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -71423,7 +71423,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71873,7 +71873,7 @@
         <v>2.78</v>
       </c>
       <c r="DE149" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF149" t="n">
         <v>2.75</v>
@@ -71903,7 +71903,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -72375,7 +72375,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -72847,7 +72847,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -73286,7 +73286,7 @@
         <v>64</v>
       </c>
       <c r="DD152" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE152" t="n">
         <v>1.33</v>
@@ -73319,7 +73319,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73807,7 +73807,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -73908,6 +73908,3854 @@
       <c r="EP153" t="inlineStr">
         <is>
           <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>20</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46017.52083333334</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5</v>
+      </c>
+      <c r="I154" t="n">
+        <v>8</v>
+      </c>
+      <c r="J154" t="n">
+        <v>9</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
+      <c r="L154" t="n">
+        <v>11</v>
+      </c>
+      <c r="M154" t="n">
+        <v>3</v>
+      </c>
+      <c r="N154" t="n">
+        <v>3</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>7</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6</v>
+      </c>
+      <c r="S154" t="n">
+        <v>15</v>
+      </c>
+      <c r="T154" t="n">
+        <v>2</v>
+      </c>
+      <c r="U154" t="n">
+        <v>22</v>
+      </c>
+      <c r="V154" t="n">
+        <v>8</v>
+      </c>
+      <c r="W154" t="n">
+        <v>13</v>
+      </c>
+      <c r="X154" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW154" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DX154" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC154" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="ED154" t="inlineStr"/>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr"/>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EN154" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EO154" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EP154" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>20</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46017.625</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" t="n">
+        <v>4</v>
+      </c>
+      <c r="K155" t="n">
+        <v>4</v>
+      </c>
+      <c r="L155" t="n">
+        <v>8</v>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
+        <v>3</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>5</v>
+      </c>
+      <c r="R155" t="n">
+        <v>8</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" t="n">
+        <v>13</v>
+      </c>
+      <c r="U155" t="n">
+        <v>9</v>
+      </c>
+      <c r="V155" t="n">
+        <v>21</v>
+      </c>
+      <c r="W155" t="n">
+        <v>11</v>
+      </c>
+      <c r="X155" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW155" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DX155" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="EA155" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="EB155" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC155" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="ED155" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EM155" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EN155" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO155" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EP155" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>20</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>46017.72916666666</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="n">
+        <v>5</v>
+      </c>
+      <c r="L156" t="n">
+        <v>6</v>
+      </c>
+      <c r="M156" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="n">
+        <v>1</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>2</v>
+      </c>
+      <c r="R156" t="n">
+        <v>3</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3</v>
+      </c>
+      <c r="T156" t="n">
+        <v>13</v>
+      </c>
+      <c r="U156" t="n">
+        <v>5</v>
+      </c>
+      <c r="V156" t="n">
+        <v>16</v>
+      </c>
+      <c r="W156" t="n">
+        <v>7</v>
+      </c>
+      <c r="X156" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV156" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW156" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX156" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY156" t="n">
+        <v>129</v>
+      </c>
+      <c r="BZ156" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CA156" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CB156" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR156" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS156" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU156" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV156" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX156" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY156" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ156" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA156" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB156" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC156" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD156" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DF156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DI156" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DJ156" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK156" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL156" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM156" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN156" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO156" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW156" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DX156" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="DY156" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ156" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="EA156" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EB156" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EC156" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED156" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EE156" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF156" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EG156" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EH156" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI156" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EJ156" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EK156" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL156" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EM156" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EN156" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EO156" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP156" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>20</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>46017.82291666666</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>8</v>
+      </c>
+      <c r="K157" t="n">
+        <v>3</v>
+      </c>
+      <c r="L157" t="n">
+        <v>11</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>4</v>
+      </c>
+      <c r="R157" t="n">
+        <v>5</v>
+      </c>
+      <c r="S157" t="n">
+        <v>13</v>
+      </c>
+      <c r="T157" t="n">
+        <v>8</v>
+      </c>
+      <c r="U157" t="n">
+        <v>17</v>
+      </c>
+      <c r="V157" t="n">
+        <v>13</v>
+      </c>
+      <c r="W157" t="n">
+        <v>7</v>
+      </c>
+      <c r="X157" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>529</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV157" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>136</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA157" t="n">
+        <v>53</v>
+      </c>
+      <c r="DB157" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC157" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD157" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DE157" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF157" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DG157" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH157" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DI157" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DJ157" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK157" t="n">
+        <v>47</v>
+      </c>
+      <c r="DL157" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN157" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO157" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW157" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DX157" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="DY157" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="DZ157" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA157" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EB157" t="inlineStr">
+        <is>
+          <t>5.16</t>
+        </is>
+      </c>
+      <c r="EC157" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="ED157" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG157" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EJ157" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EK157" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EL157" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM157" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EN157" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EO157" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP157" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>20</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>46018.52083333334</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="n">
+        <v>3</v>
+      </c>
+      <c r="J158" t="n">
+        <v>5</v>
+      </c>
+      <c r="K158" t="n">
+        <v>7</v>
+      </c>
+      <c r="L158" t="n">
+        <v>12</v>
+      </c>
+      <c r="M158" t="n">
+        <v>3</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>3</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6</v>
+      </c>
+      <c r="S158" t="n">
+        <v>4</v>
+      </c>
+      <c r="T158" t="n">
+        <v>10</v>
+      </c>
+      <c r="U158" t="n">
+        <v>7</v>
+      </c>
+      <c r="V158" t="n">
+        <v>16</v>
+      </c>
+      <c r="W158" t="n">
+        <v>19</v>
+      </c>
+      <c r="X158" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV158" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW158" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY158" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ158" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR158" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS158" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU158" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV158" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX158" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY158" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ158" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA158" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB158" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC158" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD158" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE158" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG158" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH158" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DI158" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ158" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK158" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL158" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DM158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN158" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO158" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW158" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="DX158" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DY158" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="DZ158" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA158" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EB158" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="EC158" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="ED158" t="inlineStr"/>
+      <c r="EE158" t="inlineStr"/>
+      <c r="EF158" t="inlineStr"/>
+      <c r="EG158" t="inlineStr"/>
+      <c r="EH158" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI158" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EJ158" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK158" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL158" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EM158" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EN158" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EO158" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EP158" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>20</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>46018.625</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>13</v>
+      </c>
+      <c r="K159" t="n">
+        <v>5</v>
+      </c>
+      <c r="L159" t="n">
+        <v>18</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>7</v>
+      </c>
+      <c r="R159" t="n">
+        <v>3</v>
+      </c>
+      <c r="S159" t="n">
+        <v>8</v>
+      </c>
+      <c r="T159" t="n">
+        <v>8</v>
+      </c>
+      <c r="U159" t="n">
+        <v>15</v>
+      </c>
+      <c r="V159" t="n">
+        <v>11</v>
+      </c>
+      <c r="W159" t="n">
+        <v>7</v>
+      </c>
+      <c r="X159" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV159" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW159" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX159" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY159" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ159" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN159" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR159" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS159" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU159" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV159" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX159" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY159" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ159" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA159" t="n">
+        <v>56</v>
+      </c>
+      <c r="DB159" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC159" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE159" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DF159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG159" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH159" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI159" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ159" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK159" t="n">
+        <v>45</v>
+      </c>
+      <c r="DL159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM159" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN159" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO159" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW159" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="DX159" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="DY159" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ159" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA159" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EB159" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EC159" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="ED159" t="inlineStr"/>
+      <c r="EE159" t="inlineStr"/>
+      <c r="EF159" t="inlineStr"/>
+      <c r="EG159" t="inlineStr"/>
+      <c r="EH159" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI159" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EJ159" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EK159" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL159" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EM159" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EN159" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EO159" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EP159" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>20</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>46018.71875</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2</v>
+      </c>
+      <c r="J160" t="n">
+        <v>5</v>
+      </c>
+      <c r="K160" t="n">
+        <v>6</v>
+      </c>
+      <c r="L160" t="n">
+        <v>11</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2</v>
+      </c>
+      <c r="N160" t="n">
+        <v>4</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>6</v>
+      </c>
+      <c r="R160" t="n">
+        <v>9</v>
+      </c>
+      <c r="S160" t="n">
+        <v>8</v>
+      </c>
+      <c r="T160" t="n">
+        <v>8</v>
+      </c>
+      <c r="U160" t="n">
+        <v>14</v>
+      </c>
+      <c r="V160" t="n">
+        <v>17</v>
+      </c>
+      <c r="W160" t="n">
+        <v>13</v>
+      </c>
+      <c r="X160" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV160" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW160" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX160" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY160" t="n">
+        <v>115</v>
+      </c>
+      <c r="BZ160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CB160" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR160" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS160" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU160" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV160" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX160" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY160" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ160" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA160" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB160" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC160" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG160" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DH160" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DI160" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DJ160" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK160" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL160" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM160" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN160" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DO160" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW160" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="DX160" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="DY160" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ160" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA160" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EB160" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EC160" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="ED160" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EE160" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF160" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG160" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EH160" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI160" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EJ160" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EK160" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL160" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM160" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EN160" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EO160" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EP160" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>20</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46018.82291666666</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2</v>
+      </c>
+      <c r="J161" t="n">
+        <v>4</v>
+      </c>
+      <c r="K161" t="n">
+        <v>3</v>
+      </c>
+      <c r="L161" t="n">
+        <v>7</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>5</v>
+      </c>
+      <c r="R161" t="n">
+        <v>5</v>
+      </c>
+      <c r="S161" t="n">
+        <v>13</v>
+      </c>
+      <c r="T161" t="n">
+        <v>9</v>
+      </c>
+      <c r="U161" t="n">
+        <v>18</v>
+      </c>
+      <c r="V161" t="n">
+        <v>14</v>
+      </c>
+      <c r="W161" t="n">
+        <v>17</v>
+      </c>
+      <c r="X161" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV161" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW161" t="n">
+        <v>82</v>
+      </c>
+      <c r="BX161" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY161" t="n">
+        <v>135</v>
+      </c>
+      <c r="BZ161" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA161" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CB161" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR161" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS161" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU161" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV161" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX161" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY161" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ161" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA161" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB161" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC161" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DE161" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF161" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG161" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH161" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI161" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DJ161" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK161" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL161" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM161" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN161" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="DO161" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW161" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DX161" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="DY161" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ161" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA161" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EB161" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EC161" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="ED161" t="inlineStr"/>
+      <c r="EE161" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF161" t="inlineStr"/>
+      <c r="EG161" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EH161" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI161" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ161" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK161" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EL161" t="inlineStr"/>
+      <c r="EM161" t="inlineStr"/>
+      <c r="EN161" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EO161" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP161" t="inlineStr">
+        <is>
+          <t>2.74</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -74473,10 +74473,10 @@
         <v>15</v>
       </c>
       <c r="Y155" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z155" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
@@ -77351,13 +77351,13 @@
         <v>5</v>
       </c>
       <c r="S161" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T161" t="n">
         <v>9</v>
       </c>
       <c r="U161" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V161" t="n">
         <v>14</v>
@@ -77532,13 +77532,13 @@
         <v>135</v>
       </c>
       <c r="BZ161" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="CA161" t="n">
         <v>1.83</v>
       </c>
       <c r="CB161" t="n">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -77607,7 +77607,7 @@
         <v>12</v>
       </c>
       <c r="CY161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ161" t="n">
         <v>56</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -39731,146 +39731,146 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45947.78125</v>
+        <v>45948.58333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
         <v>4</v>
       </c>
-      <c r="K82" t="n">
-        <v>5</v>
-      </c>
-      <c r="L82" t="n">
-        <v>9</v>
-      </c>
       <c r="M82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>7</v>
       </c>
       <c r="T82" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>7</v>
+      </c>
+      <c r="W82" t="n">
         <v>11</v>
       </c>
-      <c r="V82" t="n">
-        <v>16</v>
-      </c>
-      <c r="W82" t="n">
-        <v>19</v>
-      </c>
       <c r="X82" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y82" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Z82" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Stade Maurice Dufrasne</t>
+          <t>Stade du Tivoli</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS82" t="n">
         <v>3</v>
       </c>
-      <c r="AE82" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AT82" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AU82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
         <v>0</v>
@@ -39885,16 +39885,16 @@
         <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>527</v>
+        <v>-1</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39909,64 +39909,64 @@
         <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BN82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU82" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BV82" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW82" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BX82" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="BY82" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="BZ82" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -39993,16 +39993,16 @@
         <v>1</v>
       </c>
       <c r="CK82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL82" t="n">
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO82" t="n">
         <v>0</v>
@@ -40014,79 +40014,79 @@
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CS82" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CV82" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY82" t="n">
         <v>12</v>
       </c>
-      <c r="CY82" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ82" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="DA82" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="DB82" t="n">
         <v>40</v>
       </c>
       <c r="DC82" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ82" t="n">
         <v>60</v>
       </c>
-      <c r="DD82" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DE82" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF82" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG82" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DH82" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DI82" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DJ82" t="n">
-        <v>70</v>
-      </c>
       <c r="DK82" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="DM82" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="DO82" t="n">
         <v>20</v>
       </c>
       <c r="DP82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ82" t="b">
         <v>0</v>
@@ -40107,71 +40107,83 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>12.33</v>
+        <v>14.39</v>
       </c>
       <c r="DX82" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="ED82" t="inlineStr"/>
-      <c r="EE82" t="inlineStr"/>
-      <c r="EF82" t="inlineStr"/>
-      <c r="EG82" t="inlineStr"/>
-      <c r="EH82" t="inlineStr"/>
-      <c r="EI82" t="inlineStr"/>
-      <c r="EJ82" t="inlineStr"/>
-      <c r="EK82" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EL82" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EN82" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr"/>
+      <c r="EL82" t="inlineStr"/>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr"/>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.42</t>
         </is>
       </c>
     </row>
@@ -40191,143 +40203,143 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45948.58333333334</v>
+        <v>45948.67708333334</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L83" t="n">
+        <v>15</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T83" t="n">
         <v>7</v>
       </c>
       <c r="U83" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="V83" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W83" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="X83" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y83" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Z83" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Stade du Tivoli</t>
+          <t>King Power at Den Dreef Stadion</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD83" t="n">
         <v>1</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.57</v>
+        <v>5.3</v>
       </c>
       <c r="AF83" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AG83" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AJ83" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AL83" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AM83" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AN83" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AO83" t="n">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.3</v>
       </c>
       <c r="AR83" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AS83" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AT83" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV83" t="n">
         <v>0</v>
@@ -40339,22 +40351,22 @@
         <v>0</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA83" t="n">
         <v>0</v>
       </c>
       <c r="BB83" t="n">
-        <v>-1</v>
+        <v>95</v>
       </c>
       <c r="BC83" t="n">
         <v>0</v>
       </c>
       <c r="BD83" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="BE83" t="n">
         <v>0</v>
@@ -40369,100 +40381,100 @@
         <v>1</v>
       </c>
       <c r="BI83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BK83" t="n">
         <v>1</v>
       </c>
       <c r="BL83" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM83" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BN83" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>43</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
         <v>3</v>
       </c>
-      <c r="BO83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BV83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI83" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ83" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM83" t="n">
-        <v>1</v>
-      </c>
       <c r="CN83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO83" t="n">
         <v>0</v>
@@ -40474,19 +40486,19 @@
         <v>1</v>
       </c>
       <c r="CR83" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CS83" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="CT83" t="n">
         <v>1</v>
       </c>
       <c r="CU83" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV83" t="n">
         <v>15</v>
-      </c>
-      <c r="CV83" t="n">
-        <v>11</v>
       </c>
       <c r="CW83" t="n">
         <v>1</v>
@@ -40495,58 +40507,58 @@
         <v>9</v>
       </c>
       <c r="CY83" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CZ83" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA83" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC83" t="n">
         <v>60</v>
       </c>
-      <c r="DB83" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC83" t="n">
-        <v>70</v>
-      </c>
       <c r="DD83" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="DF83" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="DG83" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH83" t="n">
         <v>0.8</v>
       </c>
-      <c r="DH83" t="n">
-        <v>1.2</v>
-      </c>
       <c r="DI83" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="DJ83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DK83" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="DL83" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="DM83" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="DN83" t="n">
-        <v>2.79</v>
+        <v>3.36</v>
       </c>
       <c r="DO83" t="n">
         <v>20</v>
       </c>
       <c r="DP83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ83" t="b">
         <v>0</v>
@@ -40567,14 +40579,14 @@
         <v>0</v>
       </c>
       <c r="DW83" t="n">
-        <v>14.39</v>
+        <v>14.2</v>
       </c>
       <c r="DX83" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="DY83" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ83" t="inlineStr">
@@ -40584,66 +40596,66 @@
       </c>
       <c r="EA83" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EB83" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EC83" t="inlineStr">
         <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="ED83" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr"/>
       <c r="EE83" t="inlineStr">
         <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF83" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr"/>
       <c r="EG83" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH83" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EI83" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EJ83" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EK83" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
       <c r="EL83" t="inlineStr"/>
       <c r="EM83" t="inlineStr"/>
-      <c r="EN83" t="inlineStr"/>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EO83" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EP83" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.22</t>
         </is>
       </c>
     </row>
@@ -40663,40 +40675,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45948.67708333334</v>
+        <v>45948.78125</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -40705,128 +40717,128 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S84" t="n">
         <v>12</v>
       </c>
       <c r="T84" t="n">
+        <v>6</v>
+      </c>
+      <c r="U84" t="n">
+        <v>15</v>
+      </c>
+      <c r="V84" t="n">
+        <v>9</v>
+      </c>
+      <c r="W84" t="n">
+        <v>13</v>
+      </c>
+      <c r="X84" t="n">
         <v>7</v>
       </c>
-      <c r="U84" t="n">
-        <v>17</v>
-      </c>
-      <c r="V84" t="n">
-        <v>11</v>
-      </c>
-      <c r="W84" t="n">
-        <v>17</v>
-      </c>
-      <c r="X84" t="n">
-        <v>12</v>
-      </c>
       <c r="Y84" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Z84" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>King Power at Den Dreef Stadion</t>
+          <t>Stade Joseph Mariën</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE84" t="n">
-        <v>5.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF84" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AK84" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AL84" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AM84" t="n">
         <v>1.42</v>
       </c>
       <c r="AN84" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AO84" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.3</v>
       </c>
       <c r="AR84" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AS84" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AU84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB84" t="n">
-        <v>95</v>
+        <v>2572</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40841,121 +40853,121 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
         <v>8</v>
-      </c>
-      <c r="BN84" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ84" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT84" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV84" t="n">
-        <v>31</v>
-      </c>
-      <c r="BW84" t="n">
-        <v>38</v>
-      </c>
-      <c r="BX84" t="n">
-        <v>43</v>
-      </c>
-      <c r="BY84" t="n">
-        <v>67</v>
-      </c>
-      <c r="BZ84" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CA84" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CB84" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM84" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS84" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU84" t="n">
-        <v>12</v>
       </c>
       <c r="CV84" t="n">
         <v>15</v>
@@ -40964,55 +40976,55 @@
         <v>1</v>
       </c>
       <c r="CX84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CY84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ84" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="DA84" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DB84" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DC84" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>0.9</v>
+        <v>2.78</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.73</v>
+        <v>1</v>
       </c>
       <c r="DF84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DG84" t="n">
         <v>1.4</v>
       </c>
       <c r="DH84" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="DI84" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="DJ84" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DK84" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="DN84" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="DO84" t="n">
         <v>20</v>
@@ -41021,13 +41033,13 @@
         <v>1</v>
       </c>
       <c r="DQ84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT84" t="b">
         <v>0</v>
@@ -41036,86 +41048,94 @@
         <v>0</v>
       </c>
       <c r="DV84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW84" t="n">
-        <v>14.2</v>
+        <v>14.25</v>
       </c>
       <c r="DX84" t="n">
         <v>4.27</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="EC84" t="inlineStr">
         <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="ED84" t="inlineStr"/>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EF84" t="inlineStr"/>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH84" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EI84" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EJ84" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EK84" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL84" t="inlineStr"/>
       <c r="EM84" t="inlineStr"/>
       <c r="EN84" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EO84" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EP84" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -41135,140 +41155,140 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45948.78125</v>
+        <v>45949.47916666666</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
         <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L85" t="n">
+        <v>8</v>
+      </c>
+      <c r="M85" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
       <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>7</v>
+      </c>
+      <c r="R85" t="n">
+        <v>5</v>
+      </c>
+      <c r="S85" t="n">
+        <v>11</v>
+      </c>
+      <c r="T85" t="n">
+        <v>11</v>
+      </c>
+      <c r="U85" t="n">
+        <v>18</v>
+      </c>
+      <c r="V85" t="n">
+        <v>16</v>
+      </c>
+      <c r="W85" t="n">
+        <v>10</v>
+      </c>
+      <c r="X85" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
         <v>3</v>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>3</v>
-      </c>
-      <c r="R85" t="n">
-        <v>3</v>
-      </c>
-      <c r="S85" t="n">
-        <v>12</v>
-      </c>
-      <c r="T85" t="n">
-        <v>6</v>
-      </c>
-      <c r="U85" t="n">
-        <v>15</v>
-      </c>
-      <c r="V85" t="n">
-        <v>9</v>
-      </c>
-      <c r="W85" t="n">
-        <v>13</v>
-      </c>
-      <c r="X85" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Stade Joseph Mariën</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
-        </is>
-      </c>
-      <c r="AC85" t="n">
-        <v>0</v>
-      </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.33</v>
+        <v>3.24</v>
       </c>
       <c r="AF85" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AG85" t="n">
-        <v>7.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AJ85" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.78</v>
+        <v>2.64</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AN85" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AO85" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AS85" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AU85" t="n">
         <v>4</v>
@@ -41280,10 +41300,10 @@
         <v>1</v>
       </c>
       <c r="AX85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ85" t="n">
         <v>2</v>
@@ -41292,13 +41312,13 @@
         <v>2</v>
       </c>
       <c r="BB85" t="n">
-        <v>2572</v>
+        <v>-1</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -41313,31 +41333,31 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ85" t="n">
         <v>1</v>
       </c>
       <c r="BK85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR85" t="n">
         <v>1</v>
@@ -41346,40 +41366,40 @@
         <v>2</v>
       </c>
       <c r="BT85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="BW85" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BX85" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="BY85" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.51</v>
+        <v>3.06</v>
       </c>
       <c r="CC85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD85" t="n">
         <v>0</v>
       </c>
       <c r="CE85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF85" t="n">
         <v>0</v>
@@ -41403,10 +41423,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO85" t="n">
         <v>0</v>
@@ -41418,10 +41438,10 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CS85" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
@@ -41430,61 +41450,61 @@
         <v>8</v>
       </c>
       <c r="CV85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW85" t="n">
         <v>1</v>
       </c>
       <c r="CX85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY85" t="n">
         <v>6</v>
       </c>
       <c r="CZ85" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="DA85" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DB85" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="DC85" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.78</v>
+        <v>0.64</v>
       </c>
       <c r="DE85" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="DF85" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="DG85" t="n">
         <v>1.4</v>
       </c>
       <c r="DH85" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="DI85" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ85" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="DK85" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL85" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="DN85" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="DO85" t="n">
         <v>20</v>
@@ -41511,91 +41531,83 @@
         <v>1</v>
       </c>
       <c r="DW85" t="n">
-        <v>14.25</v>
+        <v>14.39</v>
       </c>
       <c r="DX85" t="n">
-        <v>4.27</v>
+        <v>8.57</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr">
         <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="EE85" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EF85" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EG85" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr"/>
+      <c r="EE85" t="inlineStr"/>
+      <c r="EF85" t="inlineStr"/>
+      <c r="EG85" t="inlineStr"/>
       <c r="EH85" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI85" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="EJ85" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EK85" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EL85" t="inlineStr"/>
-      <c r="EM85" t="inlineStr"/>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EN85" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EO85" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EP85" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -41615,22 +41627,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45949.47916666666</v>
+        <v>45949.58333333334</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
         <v>4</v>
@@ -41645,10 +41657,10 @@
         <v>8</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -41657,104 +41669,96 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R86" t="n">
+        <v>6</v>
+      </c>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
         <v>5</v>
       </c>
-      <c r="S86" t="n">
+      <c r="U86" t="n">
+        <v>19</v>
+      </c>
+      <c r="V86" t="n">
         <v>11</v>
       </c>
-      <c r="T86" t="n">
-        <v>11</v>
-      </c>
-      <c r="U86" t="n">
-        <v>18</v>
-      </c>
-      <c r="V86" t="n">
+      <c r="W86" t="n">
         <v>16</v>
       </c>
-      <c r="W86" t="n">
-        <v>10</v>
-      </c>
       <c r="X86" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y86" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="Z86" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Jan Breydelstadion</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>Olympialaan 74, Brugge</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>3.24</v>
+        <v>2.41</v>
       </c>
       <c r="AF86" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AJ86" t="n">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="AK86" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AL86" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AO86" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AR86" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AS86" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="AT86" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AU86" t="n">
         <v>4</v>
       </c>
       <c r="AV86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
         <v>1</v>
@@ -41763,22 +41767,22 @@
         <v>1</v>
       </c>
       <c r="AY86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB86" t="n">
-        <v>-1</v>
+        <v>537</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="BE86" t="n">
         <v>0</v>
@@ -41793,178 +41797,178 @@
         <v>1</v>
       </c>
       <c r="BI86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BO86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU86" t="n">
         <v>1</v>
       </c>
       <c r="BV86" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
         <v>6</v>
       </c>
-      <c r="BW86" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX86" t="n">
-        <v>9</v>
-      </c>
-      <c r="BY86" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ86" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CA86" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CB86" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR86" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS86" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU86" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV86" t="n">
+      <c r="CY86" t="n">
         <v>10</v>
       </c>
-      <c r="CW86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX86" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY86" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ86" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="DA86" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB86" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>30</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DF86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI86" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>90</v>
+      </c>
+      <c r="DK86" t="n">
         <v>50</v>
       </c>
-      <c r="DC86" t="n">
-        <v>90</v>
-      </c>
-      <c r="DD86" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DE86" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DF86" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG86" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DH86" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI86" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ86" t="n">
-        <v>30</v>
-      </c>
-      <c r="DK86" t="n">
-        <v>0</v>
-      </c>
       <c r="DL86" t="n">
-        <v>1.53</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="DN86" t="n">
-        <v>3.48</v>
+        <v>2.27</v>
       </c>
       <c r="DO86" t="n">
         <v>20</v>
@@ -41991,14 +41995,14 @@
         <v>1</v>
       </c>
       <c r="DW86" t="n">
-        <v>14.39</v>
+        <v>15.91</v>
       </c>
       <c r="DX86" t="n">
-        <v>8.57</v>
+        <v>8.35</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
@@ -42008,66 +42012,66 @@
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="ED86" t="inlineStr"/>
-      <c r="EE86" t="inlineStr"/>
-      <c r="EF86" t="inlineStr"/>
-      <c r="EG86" t="inlineStr"/>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
       <c r="EH86" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EK86" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL86" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EM86" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EN86" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr"/>
+      <c r="EL86" t="inlineStr"/>
+      <c r="EM86" t="inlineStr"/>
+      <c r="EN86" t="inlineStr"/>
       <c r="EO86" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP86" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.17</t>
         </is>
       </c>
     </row>
@@ -42087,76 +42091,76 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45949.58333333334</v>
+        <v>45949.6875</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
         <v>4</v>
       </c>
       <c r="J87" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>11</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
         <v>4</v>
       </c>
-      <c r="K87" t="n">
-        <v>4</v>
-      </c>
-      <c r="L87" t="n">
-        <v>8</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>6</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6</v>
-      </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U87" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V87" t="n">
         <v>11</v>
       </c>
       <c r="W87" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="X87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y87" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Z87" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr"/>
@@ -42164,85 +42168,85 @@
         <v>1</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AF87" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI87" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP87" t="n">
         <v>1.93</v>
       </c>
-      <c r="AJ87" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL87" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM87" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN87" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>2</v>
-      </c>
       <c r="AQ87" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AU87" t="n">
         <v>4</v>
       </c>
       <c r="AV87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX87" t="n">
         <v>1</v>
       </c>
       <c r="AY87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA87" t="n">
         <v>3</v>
       </c>
-      <c r="BA87" t="n">
-        <v>1</v>
-      </c>
       <c r="BB87" t="n">
-        <v>537</v>
+        <v>-1</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -42257,28 +42261,28 @@
         <v>1</v>
       </c>
       <c r="BI87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BK87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BN87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BO87" t="n">
         <v>0</v>
       </c>
       <c r="BP87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ87" t="n">
         <v>1</v>
@@ -42287,7 +42291,7 @@
         <v>0</v>
       </c>
       <c r="BS87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT87" t="n">
         <v>1</v>
@@ -42299,31 +42303,31 @@
         <v>65</v>
       </c>
       <c r="BW87" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BX87" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="BY87" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="BZ87" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="CA87" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.49</v>
+        <v>2.97</v>
       </c>
       <c r="CC87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD87" t="n">
         <v>0</v>
       </c>
       <c r="CE87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF87" t="n">
         <v>0</v>
@@ -42344,7 +42348,7 @@
         <v>0</v>
       </c>
       <c r="CL87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM87" t="n">
         <v>0</v>
@@ -42362,10 +42366,10 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="CS87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT87" t="n">
         <v>1</v>
@@ -42374,61 +42378,61 @@
         <v>11</v>
       </c>
       <c r="CV87" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CW87" t="n">
         <v>1</v>
       </c>
       <c r="CX87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CY87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ87" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="DA87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB87" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DC87" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="DE87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH87" t="n">
         <v>1.7</v>
       </c>
-      <c r="DF87" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DG87" t="n">
+      <c r="DI87" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL87" t="n">
         <v>1.6</v>
       </c>
-      <c r="DH87" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DI87" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DJ87" t="n">
-        <v>90</v>
-      </c>
-      <c r="DK87" t="n">
-        <v>50</v>
-      </c>
-      <c r="DL87" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="DM87" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DN87" t="n">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="DO87" t="n">
         <v>20</v>
@@ -42455,83 +42459,99 @@
         <v>1</v>
       </c>
       <c r="DW87" t="n">
-        <v>15.91</v>
+        <v>6.5</v>
       </c>
       <c r="DX87" t="n">
-        <v>8.35</v>
+        <v>3.24</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
           <t>2.59</t>
         </is>
       </c>
-      <c r="EB87" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EC87" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="ED87" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EE87" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EF87" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EG87" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="EH87" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EI87" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EK87" t="inlineStr"/>
-      <c r="EL87" t="inlineStr"/>
-      <c r="EM87" t="inlineStr"/>
-      <c r="EN87" t="inlineStr"/>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
       <c r="EO87" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EP87" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.33</t>
         </is>
       </c>
     </row>
@@ -42551,162 +42571,170 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45949.6875</v>
+        <v>45949.71875</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" t="n">
+        <v>12</v>
+      </c>
+      <c r="L88" t="n">
+        <v>15</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>7</v>
+      </c>
+      <c r="R88" t="n">
         <v>5</v>
       </c>
-      <c r="K88" t="n">
-        <v>6</v>
-      </c>
-      <c r="L88" t="n">
-        <v>11</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>2</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>3</v>
-      </c>
-      <c r="R88" t="n">
-        <v>4</v>
-      </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U88" t="n">
         <v>15</v>
       </c>
       <c r="V88" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X88" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y88" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Z88" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
       <c r="AC88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>2</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AN88" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.3</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
         <v>1</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA88" t="n">
         <v>3</v>
       </c>
       <c r="BB88" t="n">
-        <v>-1</v>
+        <v>535</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42721,64 +42749,64 @@
         <v>1</v>
       </c>
       <c r="BI88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL88" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BM88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BN88" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BO88" t="n">
         <v>0</v>
       </c>
       <c r="BP88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU88" t="n">
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="BW88" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="BX88" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="BY88" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="CA88" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="CB88" t="n">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -42814,7 +42842,7 @@
         <v>0</v>
       </c>
       <c r="CN88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -42826,73 +42854,73 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="CS88" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CT88" t="n">
         <v>1</v>
       </c>
       <c r="CU88" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CV88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW88" t="n">
         <v>1</v>
       </c>
       <c r="CX88" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CY88" t="n">
         <v>9</v>
       </c>
       <c r="CZ88" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="DA88" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DB88" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DC88" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.33</v>
+        <v>0.9</v>
       </c>
       <c r="DF88" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DG88" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI88" t="n">
         <v>1.7</v>
       </c>
-      <c r="DI88" t="n">
-        <v>1.8</v>
-      </c>
       <c r="DJ88" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="DK88" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="DO88" t="n">
         <v>20</v>
@@ -42910,7 +42938,7 @@
         <v>1</v>
       </c>
       <c r="DT88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU88" t="b">
         <v>0</v>
@@ -42919,99 +42947,83 @@
         <v>1</v>
       </c>
       <c r="DW88" t="n">
-        <v>6.5</v>
+        <v>15.39</v>
       </c>
       <c r="DX88" t="n">
-        <v>3.24</v>
+        <v>8.18</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr">
         <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr"/>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr"/>
       <c r="EG88" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI88" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EJ88" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EK88" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EL88" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr"/>
+      <c r="EM88" t="inlineStr"/>
       <c r="EN88" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EO88" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EP88" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.49</t>
         </is>
       </c>
     </row>
@@ -43031,170 +43043,170 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45949.71875</v>
+        <v>45950.54166666666</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
         <v>4</v>
       </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>5</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N89" t="n">
         <v>3</v>
       </c>
-      <c r="K89" t="n">
-        <v>12</v>
-      </c>
-      <c r="L89" t="n">
-        <v>15</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>2</v>
-      </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
+        <v>4</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="n">
         <v>7</v>
       </c>
-      <c r="R89" t="n">
-        <v>5</v>
-      </c>
-      <c r="S89" t="n">
-        <v>8</v>
-      </c>
       <c r="T89" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U89" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V89" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W89" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X89" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y89" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Z89" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
         <v>60</v>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Regenboogstadion</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>Zuiderlaan 17, Waregem</t>
-        </is>
-      </c>
-      <c r="AC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI89" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AK89" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL89" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM89" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN89" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO89" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AP89" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AQ89" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR89" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>535</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>50</v>
       </c>
       <c r="BE89" t="n">
         <v>0</v>
@@ -43209,64 +43221,64 @@
         <v>1</v>
       </c>
       <c r="BI89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ89" t="n">
         <v>1</v>
       </c>
       <c r="BK89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL89" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BM89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN89" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BO89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR89" t="n">
         <v>2</v>
       </c>
       <c r="BS89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU89" t="n">
         <v>1</v>
       </c>
       <c r="BV89" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BW89" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="BX89" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="BY89" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BZ89" t="n">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="CA89" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="CB89" t="n">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="CC89" t="n">
         <v>0</v>
@@ -43293,7 +43305,7 @@
         <v>1</v>
       </c>
       <c r="CK89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL89" t="n">
         <v>0</v>
@@ -43314,19 +43326,19 @@
         <v>1</v>
       </c>
       <c r="CR89" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CS89" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="CT89" t="n">
         <v>1</v>
       </c>
       <c r="CU89" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CV89" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="CW89" t="n">
         <v>1</v>
@@ -43335,52 +43347,52 @@
         <v>12</v>
       </c>
       <c r="CY89" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CZ89" t="n">
         <v>30</v>
       </c>
       <c r="DA89" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DB89" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="DC89" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DF89" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="DG89" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="DH89" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="DI89" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="DJ89" t="n">
         <v>70</v>
       </c>
       <c r="DK89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL89" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DM89" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="DN89" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="DO89" t="n">
         <v>20</v>
@@ -43389,32 +43401,32 @@
         <v>1</v>
       </c>
       <c r="DQ89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU89" t="b">
         <v>0</v>
       </c>
       <c r="DV89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW89" t="n">
-        <v>15.39</v>
+        <v>12.33</v>
       </c>
       <c r="DX89" t="n">
-        <v>8.18</v>
+        <v>2.18</v>
       </c>
       <c r="DY89" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ89" t="inlineStr">
@@ -43424,66 +43436,54 @@
       </c>
       <c r="EA89" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB89" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="EC89" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="ED89" t="inlineStr"/>
-      <c r="EE89" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
+      <c r="EE89" t="inlineStr"/>
       <c r="EF89" t="inlineStr"/>
-      <c r="EG89" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EH89" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="EI89" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EJ89" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
+      <c r="EG89" t="inlineStr"/>
+      <c r="EH89" t="inlineStr"/>
+      <c r="EI89" t="inlineStr"/>
+      <c r="EJ89" t="inlineStr"/>
       <c r="EK89" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL89" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EM89" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EN89" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO89" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EP89" t="inlineStr">
+        <is>
           <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL89" t="inlineStr"/>
-      <c r="EM89" t="inlineStr"/>
-      <c r="EN89" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EO89" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EP89" t="inlineStr">
-        <is>
-          <t>2.49</t>
         </is>
       </c>
     </row>
@@ -50188,7 +50188,7 @@
         <v>3</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -50232,7 +50232,7 @@
         <v>3</v>
       </c>
       <c r="AD104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE104" t="n">
         <v>1.94</v>
@@ -50352,13 +50352,13 @@
         <v>2</v>
       </c>
       <c r="BR104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS104" t="n">
         <v>3</v>
       </c>
       <c r="BT104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU104" t="n">
         <v>1</v>
@@ -50493,10 +50493,10 @@
         <v>1.61</v>
       </c>
       <c r="DM104" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="DN104" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DO104" t="n">
         <v>20</v>
@@ -51116,7 +51116,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45968.82291666666</v>
+        <v>45968.83333333334</v>
       </c>
       <c r="G106" t="n">
         <v>2</v>
@@ -52548,7 +52548,7 @@
         <v>4</v>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -52600,7 +52600,7 @@
         <v>4</v>
       </c>
       <c r="AD109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE109" t="n">
         <v>2.25</v>
@@ -52711,22 +52711,22 @@
         <v>6</v>
       </c>
       <c r="BO109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS109" t="n">
         <v>4</v>
       </c>
-      <c r="BR109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
       <c r="BT109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU109" t="n">
         <v>1</v>
@@ -52789,7 +52789,7 @@
         <v>0</v>
       </c>
       <c r="CO109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP109" t="n">
         <v>0</v>
@@ -60909,10 +60909,10 @@
         <v>1.85</v>
       </c>
       <c r="DM126" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="DN126" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DO126" t="n">
         <v>20</v>
@@ -63941,7 +63941,7 @@
         <v>14</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N133" t="n">
         <v>1</v>
@@ -63985,7 +63985,7 @@
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD133" t="n">
         <v>1</v>
@@ -64099,7 +64099,7 @@
         <v>10</v>
       </c>
       <c r="BO133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP133" t="n">
         <v>0</v>
@@ -64111,7 +64111,7 @@
         <v>1</v>
       </c>
       <c r="BS133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT133" t="n">
         <v>2</v>
@@ -68553,10 +68553,10 @@
         <v>1.62</v>
       </c>
       <c r="DM142" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="DN142" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DO142" t="n">
         <v>20</v>
@@ -74458,13 +74458,13 @@
         <v>4</v>
       </c>
       <c r="T155" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U155" t="n">
         <v>9</v>
       </c>
       <c r="V155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W155" t="n">
         <v>11</v>
@@ -74639,10 +74639,10 @@
         <v>1.19</v>
       </c>
       <c r="CA155" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="CB155" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="CC155" t="n">
         <v>1</v>
@@ -76875,7 +76875,7 @@
         <v>17</v>
       </c>
       <c r="W160" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X160" t="n">
         <v>11</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP161" headerRowCount="1">
-  <autoFilter ref="A1:EP161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP162" headerRowCount="1">
+  <autoFilter ref="A1:EP162"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP161"/>
+  <dimension ref="A1:EP162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE8" t="n">
         <v>1.3</v>
@@ -7065,7 +7065,7 @@
         <v>1.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE19" t="n">
         <v>1.11</v>
@@ -15701,7 +15701,7 @@
         <v>2.2</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -20037,7 +20037,7 @@
         <v>1.4</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -28137,7 +28137,7 @@
         <v>0.9</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -30534,7 +30534,7 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE62" t="n">
         <v>1.7</v>
@@ -31942,7 +31942,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE65" t="n">
         <v>0.7</v>
@@ -35749,7 +35749,7 @@
         <v>0.4</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -39090,7 +39090,7 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE80" t="n">
         <v>1.55</v>
@@ -46681,7 +46681,7 @@
         <v>1.2</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -48586,7 +48586,7 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE100" t="n">
         <v>0.9</v>
@@ -52837,7 +52837,7 @@
         <v>1.64</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -56610,7 +56610,7 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE117" t="n">
         <v>1</v>
@@ -60397,7 +60397,7 @@
         <v>1.4</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -60882,7 +60882,7 @@
         <v>64</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE126" t="n">
         <v>1</v>
@@ -67569,7 +67569,7 @@
         <v>1.33</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -71393,7 +71393,7 @@
         <v>1.7</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DF148" t="n">
         <v>1.56</v>
@@ -72342,7 +72342,7 @@
         <v>59</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DE150" t="n">
         <v>0.9</v>
@@ -77756,6 +77756,486 @@
       <c r="EP161" t="inlineStr">
         <is>
           <t>2.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>21</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>46038.82291666666</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>5</v>
+      </c>
+      <c r="J162" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" t="n">
+        <v>7</v>
+      </c>
+      <c r="L162" t="n">
+        <v>9</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>6</v>
+      </c>
+      <c r="R162" t="n">
+        <v>5</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="n">
+        <v>9</v>
+      </c>
+      <c r="U162" t="n">
+        <v>11</v>
+      </c>
+      <c r="V162" t="n">
+        <v>14</v>
+      </c>
+      <c r="W162" t="n">
+        <v>9</v>
+      </c>
+      <c r="X162" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>669434</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV162" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW162" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX162" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY162" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ162" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA162" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB162" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR162" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS162" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU162" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV162" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX162" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY162" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ162" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA162" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB162" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC162" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE162" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DF162" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DG162" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DH162" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DI162" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ162" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK162" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL162" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DM162" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DN162" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="DO162" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW162" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="DX162" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="DY162" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ162" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA162" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EB162" t="inlineStr">
+        <is>
+          <t>9.58</t>
+        </is>
+      </c>
+      <c r="EC162" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="ED162" t="inlineStr"/>
+      <c r="EE162" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EF162" t="inlineStr"/>
+      <c r="EG162" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH162" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI162" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EJ162" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK162" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EL162" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM162" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EN162" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO162" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP162" t="inlineStr">
+        <is>
+          <t>1.97</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP162" headerRowCount="1">
-  <autoFilter ref="A1:EP162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP169" headerRowCount="1">
+  <autoFilter ref="A1:EP169"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP162"/>
+  <dimension ref="A1:EP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>1.3</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         <v>2.2</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE9" t="n">
         <v>0.9</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE13" t="n">
         <v>0.91</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7553,7 +7553,7 @@
         <v>1.2</v>
       </c>
       <c r="DE14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8033,7 +8033,7 @@
         <v>0.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8518,10 +8518,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8998,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE17" t="n">
         <v>1.7</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE18" t="n">
         <v>0.9</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9969,7 +9969,7 @@
         <v>2.2</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10446,10 +10446,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10918,7 +10918,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE21" t="n">
         <v>1.55</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12377,7 +12377,7 @@
         <v>1.2</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>1.64</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         <v>0.9</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13814,7 +13814,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE27" t="n">
         <v>1.73</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14754,10 +14754,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15234,10 +15234,10 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15698,7 +15698,7 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE31" t="n">
         <v>0.91</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16186,10 +16186,10 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17149,7 +17149,7 @@
         <v>1.2</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17618,7 +17618,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE35" t="n">
         <v>1.7</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18101,7 +18101,7 @@
         <v>1.64</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19066,10 +19066,10 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20994,7 +20994,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE42" t="n">
         <v>0.9</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21482,7 +21482,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE43" t="n">
         <v>1.73</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21957,7 +21957,7 @@
         <v>0.9</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22426,10 +22426,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23389,7 +23389,7 @@
         <v>1.2</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23858,10 +23858,10 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24322,7 +24322,7 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE49" t="n">
         <v>1.55</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26237,7 +26237,7 @@
         <v>2.09</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26706,7 +26706,7 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE54" t="n">
         <v>0.7</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE56" t="n">
         <v>0.9</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28622,7 +28622,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE58" t="n">
         <v>1</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29113,7 +29113,7 @@
         <v>2.09</v>
       </c>
       <c r="DE59" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30054,10 +30054,10 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31009,7 +31009,7 @@
         <v>1.4</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32417,7 +32417,7 @@
         <v>0.9</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32902,10 +32902,10 @@
         <v>63</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE67" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33866,7 +33866,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE69" t="n">
         <v>0.7</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34330,10 +34330,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35274,10 +35274,10 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35746,7 +35746,7 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE73" t="n">
         <v>0.91</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36234,7 +36234,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE74" t="n">
         <v>1</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37685,7 +37685,7 @@
         <v>1.64</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38165,7 +38165,7 @@
         <v>2.09</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39578,10 +39578,10 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40083,7 +40083,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -40555,7 +40555,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40994,7 +40994,7 @@
         <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE84" t="n">
         <v>1</v>
@@ -41027,7 +41027,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41477,7 +41477,7 @@
         <v>0.64</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF85" t="n">
         <v>0.8</v>
@@ -41507,7 +41507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41938,10 +41938,10 @@
         <v>30</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF86" t="n">
         <v>0.4</v>
@@ -41971,7 +41971,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42402,10 +42402,10 @@
         <v>65</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF87" t="n">
         <v>1.8</v>
@@ -42435,7 +42435,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42890,7 +42890,7 @@
         <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE88" t="n">
         <v>0.9</v>
@@ -42923,7 +42923,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43365,7 +43365,7 @@
         <v>1.2</v>
       </c>
       <c r="DE89" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF89" t="n">
         <v>1</v>
@@ -43395,7 +43395,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43822,10 +43822,10 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44310,7 +44310,7 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE91" t="n">
         <v>0.9</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         <v>1.4</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45254,10 +45254,10 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47166,7 +47166,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE97" t="n">
         <v>1.7</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48114,7 +48114,7 @@
         <v>50</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE99" t="n">
         <v>1.55</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49069,7 +49069,7 @@
         <v>2.09</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49538,10 +49538,10 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50466,10 +50466,10 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE104" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -50499,7 +50499,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50957,7 +50957,7 @@
         <v>1.3</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51418,7 +51418,7 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE106" t="n">
         <v>1</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51909,7 +51909,7 @@
         <v>0.64</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52378,7 +52378,7 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE108" t="n">
         <v>0.7</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53794,10 +53794,10 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54266,10 +54266,10 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55666,10 +55666,10 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56138,7 +56138,7 @@
         <v>79</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE116" t="n">
         <v>0.9</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57093,7 +57093,7 @@
         <v>1.2</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58037,7 +58037,7 @@
         <v>1.3</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58981,7 +58981,7 @@
         <v>1.4</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59458,7 +59458,7 @@
         <v>50</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE123" t="n">
         <v>0.7</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59930,10 +59930,10 @@
         <v>57</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF124" t="n">
         <v>1.43</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60394,7 +60394,7 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE125" t="n">
         <v>0.91</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60885,7 +60885,7 @@
         <v>2.2</v>
       </c>
       <c r="DE126" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF126" t="n">
         <v>2.71</v>
@@ -60915,7 +60915,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61349,7 +61349,7 @@
         <v>1.2</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF127" t="n">
         <v>1.14</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62314,7 +62314,7 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE129" t="n">
         <v>1.7</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62827,7 +62827,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -63285,7 +63285,7 @@
         <v>0.64</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF131" t="n">
         <v>0.75</v>
@@ -63315,7 +63315,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63758,7 +63758,7 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE132" t="n">
         <v>0.9</v>
@@ -63791,7 +63791,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -64222,7 +64222,7 @@
         <v>69</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE133" t="n">
         <v>1.73</v>
@@ -64255,7 +64255,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64727,7 +64727,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65166,10 +65166,10 @@
         <v>59</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -65199,7 +65199,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65625,7 +65625,7 @@
         <v>1.64</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF136" t="n">
         <v>1.38</v>
@@ -65655,7 +65655,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66143,7 +66143,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66601,7 +66601,7 @@
         <v>1.2</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF138" t="n">
         <v>1.5</v>
@@ -66631,7 +66631,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67089,7 +67089,7 @@
         <v>0.64</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF139" t="n">
         <v>0.67</v>
@@ -67119,7 +67119,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67566,7 +67566,7 @@
         <v>57</v>
       </c>
       <c r="DD140" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE140" t="n">
         <v>0.91</v>
@@ -67599,7 +67599,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -68071,7 +68071,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -68526,10 +68526,10 @@
         <v>69</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE142" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF142" t="n">
         <v>1.75</v>
@@ -68559,7 +68559,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -68974,7 +68974,7 @@
         <v>53</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE143" t="n">
         <v>1.73</v>
@@ -69007,7 +69007,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69454,7 +69454,7 @@
         <v>66</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE144" t="n">
         <v>1.55</v>
@@ -69487,7 +69487,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -69975,7 +69975,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70422,10 +70422,10 @@
         <v>84</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF146" t="n">
         <v>1.44</v>
@@ -70455,7 +70455,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70902,10 +70902,10 @@
         <v>50</v>
       </c>
       <c r="DD147" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF147" t="n">
         <v>0.44</v>
@@ -70935,7 +70935,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -71390,7 +71390,7 @@
         <v>67</v>
       </c>
       <c r="DD148" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DE148" t="n">
         <v>0.91</v>
@@ -71423,7 +71423,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71870,7 +71870,7 @@
         <v>77</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE149" t="n">
         <v>1</v>
@@ -71903,7 +71903,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -72375,7 +72375,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -72814,10 +72814,10 @@
         <v>78</v>
       </c>
       <c r="DD151" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DF151" t="n">
         <v>2.11</v>
@@ -72847,7 +72847,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -73289,7 +73289,7 @@
         <v>1.64</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF152" t="n">
         <v>1.56</v>
@@ -73319,7 +73319,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73777,7 +73777,7 @@
         <v>0.9</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF153" t="n">
         <v>1</v>
@@ -73807,7 +73807,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -74279,7 +74279,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -74759,7 +74759,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -75247,7 +75247,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -75735,7 +75735,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -76223,7 +76223,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -76665,7 +76665,7 @@
         <v>1.3</v>
       </c>
       <c r="DE159" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF159" t="n">
         <v>1.33</v>
@@ -76695,7 +76695,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -77167,7 +77167,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -77622,7 +77622,7 @@
         <v>78</v>
       </c>
       <c r="DD161" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE161" t="n">
         <v>0.7</v>
@@ -77655,7 +77655,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -78236,6 +78236,3342 @@
       <c r="EP162" t="inlineStr">
         <is>
           <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>21</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>46039.625</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>4</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>4</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>10</v>
+      </c>
+      <c r="R163" t="n">
+        <v>5</v>
+      </c>
+      <c r="S163" t="n">
+        <v>12</v>
+      </c>
+      <c r="T163" t="n">
+        <v>2</v>
+      </c>
+      <c r="U163" t="n">
+        <v>22</v>
+      </c>
+      <c r="V163" t="n">
+        <v>7</v>
+      </c>
+      <c r="W163" t="n">
+        <v>9</v>
+      </c>
+      <c r="X163" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
+      <c r="AC163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>535</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV163" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW163" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX163" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY163" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ163" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CA163" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB163" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="CC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR163" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS163" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU163" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV163" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX163" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY163" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ163" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA163" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB163" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC163" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE163" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH163" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ163" t="n">
+        <v>49</v>
+      </c>
+      <c r="DK163" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL163" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM163" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DN163" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DO163" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW163" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="DX163" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="DY163" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="DZ163" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA163" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EB163" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EC163" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="ED163" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EE163" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF163" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG163" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EH163" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI163" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EJ163" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK163" t="inlineStr"/>
+      <c r="EL163" t="inlineStr"/>
+      <c r="EM163" t="inlineStr"/>
+      <c r="EN163" t="inlineStr"/>
+      <c r="EO163" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EP163" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>21</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>46039.71875</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" t="n">
+        <v>7</v>
+      </c>
+      <c r="K164" t="n">
+        <v>4</v>
+      </c>
+      <c r="L164" t="n">
+        <v>11</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>6</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2</v>
+      </c>
+      <c r="S164" t="n">
+        <v>11</v>
+      </c>
+      <c r="T164" t="n">
+        <v>6</v>
+      </c>
+      <c r="U164" t="n">
+        <v>17</v>
+      </c>
+      <c r="V164" t="n">
+        <v>8</v>
+      </c>
+      <c r="W164" t="n">
+        <v>11</v>
+      </c>
+      <c r="X164" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>2567</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV164" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW164" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX164" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY164" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ164" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB164" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN164" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR164" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS164" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU164" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV164" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY164" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ164" t="n">
+        <v>26</v>
+      </c>
+      <c r="DA164" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB164" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC164" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DE164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG164" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI164" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ164" t="n">
+        <v>74</v>
+      </c>
+      <c r="DK164" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL164" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM164" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN164" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DO164" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW164" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="DX164" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="DY164" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ164" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA164" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB164" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EC164" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="ED164" t="inlineStr"/>
+      <c r="EE164" t="inlineStr"/>
+      <c r="EF164" t="inlineStr"/>
+      <c r="EG164" t="inlineStr"/>
+      <c r="EH164" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI164" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ164" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EK164" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EL164" t="inlineStr"/>
+      <c r="EM164" t="inlineStr"/>
+      <c r="EN164" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EO164" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP164" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>21</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>46039.82291666666</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>7</v>
+      </c>
+      <c r="M165" t="n">
+        <v>4</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>6</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1</v>
+      </c>
+      <c r="S165" t="n">
+        <v>9</v>
+      </c>
+      <c r="T165" t="n">
+        <v>3</v>
+      </c>
+      <c r="U165" t="n">
+        <v>15</v>
+      </c>
+      <c r="V165" t="n">
+        <v>4</v>
+      </c>
+      <c r="W165" t="n">
+        <v>16</v>
+      </c>
+      <c r="X165" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV165" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW165" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX165" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY165" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ165" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA165" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CB165" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR165" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS165" t="n">
+        <v>38</v>
+      </c>
+      <c r="CT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU165" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV165" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX165" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY165" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ165" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA165" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB165" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC165" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DE165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DF165" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DG165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DH165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DI165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DJ165" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK165" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL165" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM165" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN165" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="DO165" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP165" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW165" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="DX165" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="DY165" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ165" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA165" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EB165" t="inlineStr">
+        <is>
+          <t>8.39</t>
+        </is>
+      </c>
+      <c r="EC165" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="ED165" t="inlineStr"/>
+      <c r="EE165" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF165" t="inlineStr"/>
+      <c r="EG165" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH165" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EI165" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EJ165" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK165" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL165" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM165" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EN165" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EO165" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EP165" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>21</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>46040.52083333334</v>
+      </c>
+      <c r="G166" t="n">
+        <v>4</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" t="n">
+        <v>6</v>
+      </c>
+      <c r="J166" t="n">
+        <v>9</v>
+      </c>
+      <c r="K166" t="n">
+        <v>8</v>
+      </c>
+      <c r="L166" t="n">
+        <v>17</v>
+      </c>
+      <c r="M166" t="n">
+        <v>4</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>6</v>
+      </c>
+      <c r="R166" t="n">
+        <v>4</v>
+      </c>
+      <c r="S166" t="n">
+        <v>12</v>
+      </c>
+      <c r="T166" t="n">
+        <v>6</v>
+      </c>
+      <c r="U166" t="n">
+        <v>18</v>
+      </c>
+      <c r="V166" t="n">
+        <v>10</v>
+      </c>
+      <c r="W166" t="n">
+        <v>12</v>
+      </c>
+      <c r="X166" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR166" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS166" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU166" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV166" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX166" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY166" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ166" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA166" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB166" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC166" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD166" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DE166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DI166" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ166" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK166" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL166" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM166" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN166" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO166" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW166" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="DX166" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DY166" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="DZ166" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="EA166" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EB166" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EC166" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED166" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EE166" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF166" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG166" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EH166" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI166" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EJ166" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EK166" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL166" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EM166" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EN166" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EO166" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EP166" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>21</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>46040.625</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="n">
+        <v>5</v>
+      </c>
+      <c r="L167" t="n">
+        <v>7</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>1</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>9</v>
+      </c>
+      <c r="T167" t="n">
+        <v>7</v>
+      </c>
+      <c r="U167" t="n">
+        <v>10</v>
+      </c>
+      <c r="V167" t="n">
+        <v>7</v>
+      </c>
+      <c r="W167" t="n">
+        <v>14</v>
+      </c>
+      <c r="X167" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>669388</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>31</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV167" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW167" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX167" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY167" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ167" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA167" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB167" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR167" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS167" t="n">
+        <v>41</v>
+      </c>
+      <c r="CT167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU167" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV167" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX167" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY167" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ167" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA167" t="n">
+        <v>53</v>
+      </c>
+      <c r="DB167" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC167" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD167" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DE167" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF167" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG167" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH167" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DI167" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ167" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK167" t="n">
+        <v>47</v>
+      </c>
+      <c r="DL167" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM167" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN167" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO167" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW167" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="DX167" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DY167" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ167" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="EA167" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EB167" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EC167" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="ED167" t="inlineStr"/>
+      <c r="EE167" t="inlineStr"/>
+      <c r="EF167" t="inlineStr"/>
+      <c r="EG167" t="inlineStr"/>
+      <c r="EH167" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI167" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EJ167" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EK167" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL167" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM167" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EN167" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EO167" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP167" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>21</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>46040.72916666666</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2</v>
+      </c>
+      <c r="J168" t="n">
+        <v>7</v>
+      </c>
+      <c r="K168" t="n">
+        <v>9</v>
+      </c>
+      <c r="L168" t="n">
+        <v>16</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>5</v>
+      </c>
+      <c r="R168" t="n">
+        <v>4</v>
+      </c>
+      <c r="S168" t="n">
+        <v>11</v>
+      </c>
+      <c r="T168" t="n">
+        <v>9</v>
+      </c>
+      <c r="U168" t="n">
+        <v>16</v>
+      </c>
+      <c r="V168" t="n">
+        <v>13</v>
+      </c>
+      <c r="W168" t="n">
+        <v>14</v>
+      </c>
+      <c r="X168" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>529</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV168" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW168" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX168" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY168" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ168" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB168" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR168" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS168" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU168" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV168" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX168" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY168" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ168" t="n">
+        <v>30</v>
+      </c>
+      <c r="DA168" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB168" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC168" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD168" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DE168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH168" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI168" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ168" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK168" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM168" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DN168" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DO168" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW168" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="DX168" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DY168" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="DZ168" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="EA168" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB168" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="EC168" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="ED168" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE168" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EF168" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG168" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EH168" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI168" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EJ168" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EK168" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL168" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EM168" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN168" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EO168" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EP168" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>21</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>46040.76041666666</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>2</v>
+      </c>
+      <c r="K169" t="n">
+        <v>3</v>
+      </c>
+      <c r="L169" t="n">
+        <v>5</v>
+      </c>
+      <c r="M169" t="n">
+        <v>3</v>
+      </c>
+      <c r="N169" t="n">
+        <v>5</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>7</v>
+      </c>
+      <c r="R169" t="n">
+        <v>3</v>
+      </c>
+      <c r="S169" t="n">
+        <v>14</v>
+      </c>
+      <c r="T169" t="n">
+        <v>17</v>
+      </c>
+      <c r="U169" t="n">
+        <v>21</v>
+      </c>
+      <c r="V169" t="n">
+        <v>20</v>
+      </c>
+      <c r="W169" t="n">
+        <v>10</v>
+      </c>
+      <c r="X169" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR169" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS169" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU169" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV169" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX169" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY169" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ169" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA169" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB169" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC169" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD169" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE169" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG169" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ169" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK169" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL169" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DM169" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN169" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO169" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW169" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DX169" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DY169" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="DZ169" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA169" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EB169" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="EC169" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="ED169" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EE169" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EF169" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG169" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EH169" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI169" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EJ169" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EK169" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL169" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EM169" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EN169" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO169" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EP169" t="inlineStr">
+        <is>
+          <t>2.04</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -77944,7 +77944,7 @@
         <v>0</v>
       </c>
       <c r="BF162" t="n">
-        <v>-1</v>
+        <v>17525</v>
       </c>
       <c r="BG162" t="n">
         <v>2</v>
@@ -78076,7 +78076,7 @@
         <v>1</v>
       </c>
       <c r="CX162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CY162" t="n">
         <v>5</v>
@@ -78424,7 +78424,7 @@
         <v>0</v>
       </c>
       <c r="BF163" t="n">
-        <v>-1</v>
+        <v>6340</v>
       </c>
       <c r="BG163" t="n">
         <v>2</v>
@@ -78896,7 +78896,7 @@
         <v>0</v>
       </c>
       <c r="BF164" t="n">
-        <v>-1</v>
+        <v>6000</v>
       </c>
       <c r="BG164" t="n">
         <v>2</v>
@@ -79257,10 +79257,10 @@
         <v>13</v>
       </c>
       <c r="Y165" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z165" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -79360,7 +79360,7 @@
         <v>0</v>
       </c>
       <c r="BF165" t="n">
-        <v>-1</v>
+        <v>8000</v>
       </c>
       <c r="BG165" t="n">
         <v>2</v>
@@ -79840,7 +79840,7 @@
         <v>0</v>
       </c>
       <c r="BF166" t="n">
-        <v>-1</v>
+        <v>15708</v>
       </c>
       <c r="BG166" t="n">
         <v>2</v>
@@ -80320,7 +80320,7 @@
         <v>0</v>
       </c>
       <c r="BF167" t="n">
-        <v>-1</v>
+        <v>1458</v>
       </c>
       <c r="BG167" t="n">
         <v>2</v>
@@ -80671,13 +80671,13 @@
         <v>4</v>
       </c>
       <c r="S168" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T168" t="n">
         <v>9</v>
       </c>
       <c r="U168" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V168" t="n">
         <v>13</v>
@@ -80689,10 +80689,10 @@
         <v>10</v>
       </c>
       <c r="Y168" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z168" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -80792,7 +80792,7 @@
         <v>0</v>
       </c>
       <c r="BF168" t="n">
-        <v>-1</v>
+        <v>12425</v>
       </c>
       <c r="BG168" t="n">
         <v>2</v>
@@ -80852,13 +80852,13 @@
         <v>93</v>
       </c>
       <c r="BZ168" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="CA168" t="n">
         <v>1.53</v>
       </c>
       <c r="CB168" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="CC168" t="n">
         <v>0</v>
@@ -81144,7 +81144,7 @@
         <v>3</v>
       </c>
       <c r="N169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -81171,7 +81171,7 @@
         <v>20</v>
       </c>
       <c r="W169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X169" t="n">
         <v>18</v>
@@ -81188,7 +81188,7 @@
         <v>3</v>
       </c>
       <c r="AD169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE169" t="n">
         <v>1.77</v>
@@ -81272,7 +81272,7 @@
         <v>0</v>
       </c>
       <c r="BF169" t="n">
-        <v>-1</v>
+        <v>6004</v>
       </c>
       <c r="BG169" t="n">
         <v>2</v>
@@ -81308,13 +81308,13 @@
         <v>3</v>
       </c>
       <c r="BR169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS169" t="n">
         <v>2</v>
       </c>
       <c r="BT169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU169" t="n">
         <v>1</v>
@@ -81398,7 +81398,7 @@
         <v>18</v>
       </c>
       <c r="CV169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW169" t="n">
         <v>1</v>
@@ -81509,26 +81509,10 @@
           <t>3.65</t>
         </is>
       </c>
-      <c r="ED169" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="EE169" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EF169" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EG169" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
+      <c r="ED169" t="inlineStr"/>
+      <c r="EE169" t="inlineStr"/>
+      <c r="EF169" t="inlineStr"/>
+      <c r="EG169" t="inlineStr"/>
       <c r="EH169" t="inlineStr">
         <is>
           <t>1.27</t>
@@ -81544,26 +81528,10 @@
           <t>1.87</t>
         </is>
       </c>
-      <c r="EK169" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EL169" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EM169" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EN169" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="EK169" t="inlineStr"/>
+      <c r="EL169" t="inlineStr"/>
+      <c r="EM169" t="inlineStr"/>
+      <c r="EN169" t="inlineStr"/>
       <c r="EO169" t="inlineStr">
         <is>
           <t>1.82</t>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP169" headerRowCount="1">
-  <autoFilter ref="A1:EP169"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP170" headerRowCount="1">
+  <autoFilter ref="A1:EP170"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP169"/>
+  <dimension ref="A1:EP170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5161,7 +5161,7 @@
         <v>2.27</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE12" t="n">
         <v>0.9</v>
@@ -12374,7 +12374,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE24" t="n">
         <v>1.18</v>
@@ -14285,7 +14285,7 @@
         <v>1.4</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -17146,7 +17146,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE34" t="n">
         <v>1.3</v>
@@ -23386,7 +23386,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE47" t="n">
         <v>1.55</v>
@@ -25277,7 +25277,7 @@
         <v>1.64</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -31481,7 +31481,7 @@
         <v>2.09</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF64" t="n">
         <v>1.25</v>
@@ -33378,7 +33378,7 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE68" t="n">
         <v>1.73</v>
@@ -34805,7 +34805,7 @@
         <v>0.64</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -42893,7 +42893,7 @@
         <v>1.5</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -43362,7 +43362,7 @@
         <v>60</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE89" t="n">
         <v>0.9</v>
@@ -45287,7 +45287,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -47626,7 +47626,7 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE98" t="n">
         <v>1</v>
@@ -50005,7 +50005,7 @@
         <v>0.9</v>
       </c>
       <c r="DE103" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF103" t="n">
         <v>0.83</v>
@@ -55186,7 +55186,7 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE114" t="n">
         <v>1</v>
@@ -56141,7 +56141,7 @@
         <v>1.55</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF116" t="n">
         <v>1.43</v>
@@ -63761,7 +63761,7 @@
         <v>2.8</v>
       </c>
       <c r="DE132" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF132" t="n">
         <v>3</v>
@@ -66598,7 +66598,7 @@
         <v>63</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE138" t="n">
         <v>1</v>
@@ -72345,7 +72345,7 @@
         <v>2.2</v>
       </c>
       <c r="DE150" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF150" t="n">
         <v>2.38</v>
@@ -75214,7 +75214,7 @@
         <v>62</v>
       </c>
       <c r="DD156" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DE156" t="n">
         <v>1.7</v>
@@ -81540,6 +81540,494 @@
       <c r="EP169" t="inlineStr">
         <is>
           <t>2.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>22</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>46045.82291666666</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" t="n">
+        <v>8</v>
+      </c>
+      <c r="K170" t="n">
+        <v>4</v>
+      </c>
+      <c r="L170" t="n">
+        <v>12</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>1</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7</v>
+      </c>
+      <c r="S170" t="n">
+        <v>12</v>
+      </c>
+      <c r="T170" t="n">
+        <v>8</v>
+      </c>
+      <c r="U170" t="n">
+        <v>13</v>
+      </c>
+      <c r="V170" t="n">
+        <v>15</v>
+      </c>
+      <c r="W170" t="n">
+        <v>13</v>
+      </c>
+      <c r="X170" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV170" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW170" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX170" t="n">
+        <v>128</v>
+      </c>
+      <c r="BY170" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ170" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB170" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR170" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS170" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU170" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV170" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY170" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ170" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA170" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB170" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC170" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD170" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DE170" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF170" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DH170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI170" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ170" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK170" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM170" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN170" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO170" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW170" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="DX170" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="DY170" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ170" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA170" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EB170" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EC170" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="ED170" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EE170" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF170" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG170" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EH170" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI170" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EJ170" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK170" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL170" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM170" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EN170" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EO170" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP170" t="inlineStr">
+        <is>
+          <t>2.01</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP170" headerRowCount="1">
-  <autoFilter ref="A1:EP170"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP177" headerRowCount="1">
+  <autoFilter ref="A1:EP177"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP170"/>
+  <dimension ref="A1:EP177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1802,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2285,7 +2285,7 @@
         <v>0.64</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE5" t="n">
         <v>1.36</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3726,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4206,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE8" t="n">
         <v>1.18</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5630,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE10" t="n">
         <v>1.73</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         <v>1.55</v>
       </c>
       <c r="DE11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6577,7 +6577,7 @@
         <v>1.09</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE14" t="n">
         <v>0.9</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9001,7 +9001,7 @@
         <v>1.55</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>2.27</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9511,7 +9511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9999,7 +9999,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10479,7 +10479,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>1.82</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10951,7 +10951,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11406,10 +11406,10 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11894,10 +11894,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11927,7 +11927,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12407,7 +12407,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12862,7 +12862,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13342,7 +13342,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE26" t="n">
         <v>1.18</v>
@@ -13375,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13847,7 +13847,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14282,7 +14282,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE28" t="n">
         <v>1.09</v>
@@ -14315,7 +14315,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14787,7 +14787,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15267,7 +15267,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15731,7 +15731,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16219,7 +16219,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16677,7 +16677,7 @@
         <v>0.64</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16707,7 +16707,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17149,7 +17149,7 @@
         <v>1.09</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -17179,7 +17179,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17621,7 +17621,7 @@
         <v>1.5</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17651,7 +17651,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18098,7 +18098,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE36" t="n">
         <v>1.55</v>
@@ -18131,7 +18131,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18586,10 +18586,10 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18619,7 +18619,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19557,7 +19557,7 @@
         <v>0.64</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19587,7 +19587,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20034,7 +20034,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE40" t="n">
         <v>0.91</v>
@@ -20067,7 +20067,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20555,7 +20555,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20997,7 +20997,7 @@
         <v>1.55</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -21027,7 +21027,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21515,7 +21515,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21954,7 +21954,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE44" t="n">
         <v>1.36</v>
@@ -21987,7 +21987,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22459,7 +22459,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22914,10 +22914,10 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE46" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22947,7 +22947,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23419,7 +23419,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23891,7 +23891,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24325,7 +24325,7 @@
         <v>0.64</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -24355,7 +24355,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24810,7 +24810,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE50" t="n">
         <v>1.73</v>
@@ -24843,7 +24843,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25274,7 +25274,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE51" t="n">
         <v>1.09</v>
@@ -25307,7 +25307,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25749,7 +25749,7 @@
         <v>0.64</v>
       </c>
       <c r="DE52" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -25779,7 +25779,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26234,7 +26234,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE53" t="n">
         <v>1.18</v>
@@ -26267,7 +26267,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26709,7 +26709,7 @@
         <v>2.27</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26739,7 +26739,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27178,10 +27178,10 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE55" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -27211,7 +27211,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>1.82</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -27679,7 +27679,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28134,7 +28134,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE57" t="n">
         <v>0.91</v>
@@ -28167,7 +28167,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28625,7 +28625,7 @@
         <v>1.55</v>
       </c>
       <c r="DE58" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -28655,7 +28655,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29110,7 +29110,7 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE59" t="n">
         <v>0.9</v>
@@ -29143,7 +29143,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29582,10 +29582,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -29615,7 +29615,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30087,7 +30087,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30534,10 +30534,10 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30567,7 +30567,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31006,10 +31006,10 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -31039,7 +31039,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
         <v>1.09</v>
@@ -31511,7 +31511,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31942,10 +31942,10 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -31975,7 +31975,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32414,7 +32414,7 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE66" t="n">
         <v>1.2</v>
@@ -32447,7 +32447,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32935,7 +32935,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33411,7 +33411,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33869,7 +33869,7 @@
         <v>2.8</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33899,7 +33899,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34363,7 +34363,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34835,7 +34835,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35307,7 +35307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35779,7 +35779,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36237,7 +36237,7 @@
         <v>1.82</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -36267,7 +36267,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36714,10 +36714,10 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -36747,7 +36747,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37194,10 +37194,10 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE76" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -37227,7 +37227,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -37715,7 +37715,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38162,7 +38162,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE78" t="n">
         <v>1.36</v>
@@ -38195,7 +38195,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38634,10 +38634,10 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -38667,7 +38667,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39090,10 +39090,10 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -39123,7 +39123,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39611,7 +39611,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40050,10 +40050,10 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF82" t="n">
         <v>1.6</v>
@@ -40083,7 +40083,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -40522,7 +40522,7 @@
         <v>60</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE83" t="n">
         <v>1.73</v>
@@ -40555,7 +40555,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40997,7 +40997,7 @@
         <v>2.8</v>
       </c>
       <c r="DE84" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -41027,7 +41027,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41507,7 +41507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41971,7 +41971,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42435,7 +42435,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42923,7 +42923,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43395,7 +43395,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43855,7 +43855,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44313,7 +44313,7 @@
         <v>1.55</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -44343,7 +44343,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44774,7 +44774,7 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE92" t="n">
         <v>1</v>
@@ -44807,7 +44807,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45726,7 +45726,7 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE94" t="n">
         <v>1.73</v>
@@ -45759,7 +45759,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46209,7 +46209,7 @@
         <v>0.64</v>
       </c>
       <c r="DE95" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -46239,7 +46239,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46678,7 +46678,7 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE96" t="n">
         <v>0.91</v>
@@ -46711,7 +46711,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>2.8</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -47199,7 +47199,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47629,7 +47629,7 @@
         <v>1.09</v>
       </c>
       <c r="DE98" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -47659,7 +47659,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48117,7 +48117,7 @@
         <v>1.5</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -48147,7 +48147,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48586,10 +48586,10 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -48619,7 +48619,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49066,7 +49066,7 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE101" t="n">
         <v>1.55</v>
@@ -49099,7 +49099,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49571,7 +49571,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50002,7 +50002,7 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE103" t="n">
         <v>1.09</v>
@@ -50035,7 +50035,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50499,7 +50499,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50954,10 +50954,10 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -50987,7 +50987,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51421,7 +51421,7 @@
         <v>0.64</v>
       </c>
       <c r="DE106" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -51451,7 +51451,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51939,7 +51939,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52381,7 +52381,7 @@
         <v>1.55</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -52411,7 +52411,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52834,7 +52834,7 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE109" t="n">
         <v>0.91</v>
@@ -52867,7 +52867,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53322,7 +53322,7 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE110" t="n">
         <v>1.73</v>
@@ -53355,7 +53355,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54299,7 +54299,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54730,10 +54730,10 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -54763,7 +54763,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55189,7 +55189,7 @@
         <v>1.09</v>
       </c>
       <c r="DE114" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -55219,7 +55219,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55669,7 +55669,7 @@
         <v>2.8</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -55699,7 +55699,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -56610,10 +56610,10 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE117" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF117" t="n">
         <v>2.67</v>
@@ -56643,7 +56643,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57090,7 +57090,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE118" t="n">
         <v>1.55</v>
@@ -57123,7 +57123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -57562,10 +57562,10 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -57595,7 +57595,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58034,7 +58034,7 @@
         <v>54</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE120" t="n">
         <v>1.2</v>
@@ -58067,7 +58067,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58490,10 +58490,10 @@
         <v>62</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -58523,7 +58523,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58978,7 +58978,7 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE122" t="n">
         <v>1.36</v>
@@ -59011,7 +59011,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59461,7 +59461,7 @@
         <v>0.64</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -59491,7 +59491,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59933,7 +59933,7 @@
         <v>1.5</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF124" t="n">
         <v>1.43</v>
@@ -59963,7 +59963,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60427,7 +60427,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -60882,7 +60882,7 @@
         <v>64</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE126" t="n">
         <v>0.9</v>
@@ -60915,7 +60915,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61346,7 +61346,7 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -61379,7 +61379,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61826,10 +61826,10 @@
         <v>50</v>
       </c>
       <c r="DD128" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF128" t="n">
         <v>2.13</v>
@@ -61859,7 +61859,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62317,7 +62317,7 @@
         <v>1.82</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -62347,7 +62347,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62794,10 +62794,10 @@
         <v>63</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF130" t="n">
         <v>1.5</v>
@@ -62827,7 +62827,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -63315,7 +63315,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63791,7 +63791,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -64255,7 +64255,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64694,10 +64694,10 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE134" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF134" t="n">
         <v>1.25</v>
@@ -64727,7 +64727,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65199,7 +65199,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65622,7 +65622,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE136" t="n">
         <v>1.18</v>
@@ -65655,7 +65655,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66110,10 +66110,10 @@
         <v>69</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE137" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -66143,7 +66143,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66631,7 +66631,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67119,7 +67119,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67599,7 +67599,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -68038,10 +68038,10 @@
         <v>66</v>
       </c>
       <c r="DD141" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE141" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF141" t="n">
         <v>2.22</v>
@@ -68071,7 +68071,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -68559,7 +68559,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -69007,7 +69007,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69457,7 +69457,7 @@
         <v>1.55</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF144" t="n">
         <v>1.5</v>
@@ -69487,7 +69487,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -69942,10 +69942,10 @@
         <v>82</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF145" t="n">
         <v>1.38</v>
@@ -69975,7 +69975,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70455,7 +70455,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70935,7 +70935,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -71423,7 +71423,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71873,7 +71873,7 @@
         <v>2.8</v>
       </c>
       <c r="DE149" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF149" t="n">
         <v>2.75</v>
@@ -71903,7 +71903,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -72342,7 +72342,7 @@
         <v>59</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE150" t="n">
         <v>1.09</v>
@@ -72375,7 +72375,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -72847,7 +72847,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -73286,7 +73286,7 @@
         <v>64</v>
       </c>
       <c r="DD152" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE152" t="n">
         <v>1.2</v>
@@ -73319,7 +73319,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73774,10 +73774,10 @@
         <v>65</v>
       </c>
       <c r="DD153" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF153" t="n">
         <v>1</v>
@@ -73807,7 +73807,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -74246,7 +74246,7 @@
         <v>80</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DE154" t="n">
         <v>1.73</v>
@@ -74279,7 +74279,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -74729,7 +74729,7 @@
         <v>0.64</v>
       </c>
       <c r="DE155" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF155" t="n">
         <v>0.6</v>
@@ -74759,7 +74759,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -75217,7 +75217,7 @@
         <v>1.09</v>
       </c>
       <c r="DE156" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF156" t="n">
         <v>1.33</v>
@@ -75247,7 +75247,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -75702,10 +75702,10 @@
         <v>70</v>
       </c>
       <c r="DD157" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE157" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF157" t="n">
         <v>2.3</v>
@@ -75735,7 +75735,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -76190,10 +76190,10 @@
         <v>80</v>
       </c>
       <c r="DD158" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DE158" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DF158" t="n">
         <v>1.5</v>
@@ -76223,7 +76223,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -76662,7 +76662,7 @@
         <v>56</v>
       </c>
       <c r="DD159" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE159" t="n">
         <v>1</v>
@@ -76695,7 +76695,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -77134,10 +77134,10 @@
         <v>67</v>
       </c>
       <c r="DD160" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DF160" t="n">
         <v>1.44</v>
@@ -77167,7 +77167,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -77625,7 +77625,7 @@
         <v>1.82</v>
       </c>
       <c r="DE161" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF161" t="n">
         <v>1.56</v>
@@ -77655,7 +77655,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -78094,7 +78094,7 @@
         <v>58</v>
       </c>
       <c r="DD162" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE162" t="n">
         <v>0.91</v>
@@ -78127,7 +78127,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -78607,7 +78607,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -79049,7 +79049,7 @@
         <v>1.55</v>
       </c>
       <c r="DE164" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF164" t="n">
         <v>1.7</v>
@@ -79079,7 +79079,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -79543,7 +79543,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -80023,7 +80023,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -80503,7 +80503,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -80975,7 +80975,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -81455,7 +81455,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -81952,82 +81952,3410 @@
       </c>
       <c r="EA170" t="inlineStr">
         <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EB170" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EC170" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="ED170" t="inlineStr"/>
+      <c r="EE170" t="inlineStr"/>
+      <c r="EF170" t="inlineStr"/>
+      <c r="EG170" t="inlineStr"/>
+      <c r="EH170" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI170" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EJ170" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EK170" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL170" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM170" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EN170" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EO170" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP170" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>22</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>46046.625</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3</v>
+      </c>
+      <c r="J171" t="n">
+        <v>6</v>
+      </c>
+      <c r="K171" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" t="n">
+        <v>11</v>
+      </c>
+      <c r="M171" t="n">
+        <v>2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>1</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6</v>
+      </c>
+      <c r="S171" t="n">
+        <v>5</v>
+      </c>
+      <c r="T171" t="n">
+        <v>9</v>
+      </c>
+      <c r="U171" t="n">
+        <v>6</v>
+      </c>
+      <c r="V171" t="n">
+        <v>15</v>
+      </c>
+      <c r="W171" t="n">
+        <v>10</v>
+      </c>
+      <c r="X171" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV171" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW171" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX171" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY171" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ171" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB171" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR171" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS171" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU171" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV171" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX171" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY171" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ171" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA171" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB171" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC171" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD171" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE171" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DF171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DG171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DH171" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DI171" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ171" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK171" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL171" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM171" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN171" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO171" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW171" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="DX171" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="DY171" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ171" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="EA171" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EB171" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EC171" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="ED171" t="inlineStr"/>
+      <c r="EE171" t="inlineStr"/>
+      <c r="EF171" t="inlineStr"/>
+      <c r="EG171" t="inlineStr"/>
+      <c r="EH171" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI171" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EJ171" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK171" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL171" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM171" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EN171" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EO171" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EP171" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>22</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>46046.71875</v>
+      </c>
+      <c r="G172" t="n">
+        <v>4</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3</v>
+      </c>
+      <c r="I172" t="n">
+        <v>7</v>
+      </c>
+      <c r="J172" t="n">
+        <v>7</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>7</v>
+      </c>
+      <c r="M172" t="n">
+        <v>3</v>
+      </c>
+      <c r="N172" t="n">
+        <v>3</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>7</v>
+      </c>
+      <c r="R172" t="n">
+        <v>4</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" t="n">
+        <v>17</v>
+      </c>
+      <c r="V172" t="n">
+        <v>5</v>
+      </c>
+      <c r="W172" t="n">
+        <v>11</v>
+      </c>
+      <c r="X172" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV172" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW172" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX172" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY172" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ172" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CA172" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CB172" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR172" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS172" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU172" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV172" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY172" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ172" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA172" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB172" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC172" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD172" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE172" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DF172" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG172" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH172" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DI172" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ172" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK172" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL172" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DM172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN172" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO172" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW172" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="DX172" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="DY172" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ172" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="EA172" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EB172" t="inlineStr">
+        <is>
+          <t>7.21</t>
+        </is>
+      </c>
+      <c r="EC172" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="ED172" t="inlineStr"/>
+      <c r="EE172" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EF172" t="inlineStr"/>
+      <c r="EG172" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EH172" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI172" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EJ172" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EK172" t="inlineStr"/>
+      <c r="EL172" t="inlineStr"/>
+      <c r="EM172" t="inlineStr"/>
+      <c r="EN172" t="inlineStr"/>
+      <c r="EO172" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EP172" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>22</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>46046.82291666666</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>4</v>
+      </c>
+      <c r="K173" t="n">
+        <v>9</v>
+      </c>
+      <c r="L173" t="n">
+        <v>13</v>
+      </c>
+      <c r="M173" t="n">
+        <v>3</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2</v>
+      </c>
+      <c r="S173" t="n">
+        <v>12</v>
+      </c>
+      <c r="T173" t="n">
+        <v>11</v>
+      </c>
+      <c r="U173" t="n">
+        <v>17</v>
+      </c>
+      <c r="V173" t="n">
+        <v>13</v>
+      </c>
+      <c r="W173" t="n">
+        <v>16</v>
+      </c>
+      <c r="X173" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV173" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW173" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX173" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY173" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ173" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA173" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB173" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR173" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS173" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU173" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV173" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX173" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY173" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ173" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA173" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB173" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC173" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD173" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DE173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF173" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DG173" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DH173" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DI173" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DJ173" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK173" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL173" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM173" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN173" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DO173" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW173" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="DX173" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="DY173" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ173" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="EA173" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EB173" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC173" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="ED173" t="inlineStr"/>
+      <c r="EE173" t="inlineStr"/>
+      <c r="EF173" t="inlineStr"/>
+      <c r="EG173" t="inlineStr"/>
+      <c r="EH173" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI173" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EJ173" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK173" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL173" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM173" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EN173" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EO173" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP173" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>22</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>46047.52083333334</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>4</v>
+      </c>
+      <c r="K174" t="n">
+        <v>6</v>
+      </c>
+      <c r="L174" t="n">
+        <v>10</v>
+      </c>
+      <c r="M174" t="n">
+        <v>2</v>
+      </c>
+      <c r="N174" t="n">
+        <v>2</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>4</v>
+      </c>
+      <c r="R174" t="n">
+        <v>3</v>
+      </c>
+      <c r="S174" t="n">
+        <v>7</v>
+      </c>
+      <c r="T174" t="n">
+        <v>9</v>
+      </c>
+      <c r="U174" t="n">
+        <v>11</v>
+      </c>
+      <c r="V174" t="n">
+        <v>12</v>
+      </c>
+      <c r="W174" t="n">
+        <v>13</v>
+      </c>
+      <c r="X174" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>529</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV174" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW174" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX174" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY174" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA174" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB174" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR174" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS174" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU174" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV174" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX174" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY174" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ174" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA174" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB174" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC174" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE174" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF174" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG174" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ174" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK174" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL174" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN174" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO174" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW174" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DX174" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="DY174" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="DZ174" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA174" t="inlineStr">
+        <is>
           <t>2.95</t>
         </is>
       </c>
-      <c r="EB170" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="EC170" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="ED170" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="EE170" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EF170" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EG170" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EH170" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EI170" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="EJ170" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK170" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EL170" t="inlineStr">
+      <c r="EB174" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EC174" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED174" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EE174" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF174" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EG174" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EH174" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI174" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EJ174" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK174" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL174" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EM174" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN174" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EO174" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EP174" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>22</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>46047.625</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="n">
+        <v>2</v>
+      </c>
+      <c r="J175" t="n">
+        <v>4</v>
+      </c>
+      <c r="K175" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" t="n">
+        <v>6</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>6</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2</v>
+      </c>
+      <c r="S175" t="n">
+        <v>8</v>
+      </c>
+      <c r="T175" t="n">
+        <v>9</v>
+      </c>
+      <c r="U175" t="n">
+        <v>14</v>
+      </c>
+      <c r="V175" t="n">
+        <v>11</v>
+      </c>
+      <c r="W175" t="n">
+        <v>9</v>
+      </c>
+      <c r="X175" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV175" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW175" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX175" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY175" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB175" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR175" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS175" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU175" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV175" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX175" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY175" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ175" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA175" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB175" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC175" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD175" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE175" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF175" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG175" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH175" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DI175" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DJ175" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK175" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL175" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DM175" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN175" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DO175" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW175" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DX175" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="DY175" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ175" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA175" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EB175" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="EC175" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="ED175" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EE175" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF175" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG175" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH175" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EI175" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EJ175" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK175" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EL175" t="inlineStr"/>
+      <c r="EM175" t="inlineStr"/>
+      <c r="EN175" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EO175" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EP175" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>22</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>46047.72916666666</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>6</v>
+      </c>
+      <c r="K176" t="n">
+        <v>6</v>
+      </c>
+      <c r="L176" t="n">
+        <v>12</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+      <c r="N176" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>3</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2</v>
+      </c>
+      <c r="S176" t="n">
+        <v>17</v>
+      </c>
+      <c r="T176" t="n">
+        <v>7</v>
+      </c>
+      <c r="U176" t="n">
+        <v>20</v>
+      </c>
+      <c r="V176" t="n">
+        <v>9</v>
+      </c>
+      <c r="W176" t="n">
+        <v>13</v>
+      </c>
+      <c r="X176" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV176" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW176" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX176" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY176" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ176" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB176" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR176" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS176" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU176" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV176" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX176" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY176" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ176" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA176" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB176" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC176" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD176" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE176" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DF176" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DG176" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DH176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI176" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DJ176" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK176" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL176" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DO176" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW176" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DX176" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DY176" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="DZ176" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA176" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EB176" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="EC176" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="ED176" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EE176" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF176" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG176" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EH176" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EI176" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EJ176" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK176" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL176" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EM176" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EN176" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EO176" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP176" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>22</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>46047.76041666666</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" t="n">
+        <v>9</v>
+      </c>
+      <c r="K177" t="n">
+        <v>5</v>
+      </c>
+      <c r="L177" t="n">
+        <v>14</v>
+      </c>
+      <c r="M177" t="n">
+        <v>3</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>2</v>
+      </c>
+      <c r="R177" t="n">
+        <v>4</v>
+      </c>
+      <c r="S177" t="n">
+        <v>12</v>
+      </c>
+      <c r="T177" t="n">
+        <v>8</v>
+      </c>
+      <c r="U177" t="n">
+        <v>14</v>
+      </c>
+      <c r="V177" t="n">
+        <v>12</v>
+      </c>
+      <c r="W177" t="n">
+        <v>10</v>
+      </c>
+      <c r="X177" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ177" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT177" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX177" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY177" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR177" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS177" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU177" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV177" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX177" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY177" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ177" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA177" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB177" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC177" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE177" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF177" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG177" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DH177" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DI177" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ177" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK177" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM177" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN177" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO177" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW177" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DX177" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="DY177" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="DZ177" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA177" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EB177" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EC177" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="ED177" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EE177" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EM170" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EN170" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EO170" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EP170" t="inlineStr">
-        <is>
-          <t>2.01</t>
+      <c r="EF177" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG177" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EH177" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI177" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EJ177" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK177" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EL177" t="inlineStr"/>
+      <c r="EM177" t="inlineStr"/>
+      <c r="EN177" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EO177" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EP177" t="inlineStr">
+        <is>
+          <t>2.36</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -81728,7 +81728,7 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>-1</v>
+        <v>15559</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -82200,7 +82200,7 @@
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>-1</v>
+        <v>5221</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -82569,10 +82569,10 @@
         <v>13</v>
       </c>
       <c r="Y172" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z172" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -82672,7 +82672,7 @@
         <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>-1</v>
+        <v>21152</v>
       </c>
       <c r="BG172" t="n">
         <v>2</v>
@@ -83136,7 +83136,7 @@
         <v>0</v>
       </c>
       <c r="BF173" t="n">
-        <v>-1</v>
+        <v>5251</v>
       </c>
       <c r="BG173" t="n">
         <v>2</v>
@@ -83608,7 +83608,7 @@
         <v>0</v>
       </c>
       <c r="BF174" t="n">
-        <v>-1</v>
+        <v>14464</v>
       </c>
       <c r="BG174" t="n">
         <v>2</v>
@@ -84096,7 +84096,7 @@
         <v>0</v>
       </c>
       <c r="BF175" t="n">
-        <v>-1</v>
+        <v>13800</v>
       </c>
       <c r="BG175" t="n">
         <v>2</v>
@@ -84473,10 +84473,10 @@
         <v>16</v>
       </c>
       <c r="Y176" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z176" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
@@ -84576,7 +84576,7 @@
         <v>0</v>
       </c>
       <c r="BF176" t="n">
-        <v>-1</v>
+        <v>15792</v>
       </c>
       <c r="BG176" t="n">
         <v>2</v>
@@ -85064,7 +85064,7 @@
         <v>0</v>
       </c>
       <c r="BF177" t="n">
-        <v>-1</v>
+        <v>12955</v>
       </c>
       <c r="BG177" t="n">
         <v>2</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL177" headerRowCount="1">
-  <autoFilter ref="A1:EL177"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL185" headerRowCount="1">
+  <autoFilter ref="A1:EL185"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL177"/>
+  <dimension ref="A1:EL185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE3" t="n">
         <v>1.27</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2698,11 +2698,11 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE4" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE4" t="n">
-        <v>1.55</v>
-      </c>
       <c r="DF4" t="n">
         <v>0</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE5" t="n">
         <v>1.36</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3637,7 +3637,7 @@
         <v>2</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4098,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4565,7 +4565,7 @@
         <v>2.27</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5018,10 +5018,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         <v>1.36</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE12" t="n">
         <v>0.91</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7333,7 +7333,7 @@
         <v>1.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7794,10 +7794,10 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE18" t="n">
         <v>0.91</v>
@@ -9227,7 +9227,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10133,7 +10133,7 @@
         <v>1.55</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11058,10 +11058,10 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11994,10 +11994,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12930,10 +12930,10 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13386,10 +13386,10 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13841,7 +13841,7 @@
         <v>1.36</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14294,7 +14294,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE29" t="n">
         <v>1.36</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14758,10 +14758,10 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15206,7 +15206,7 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE31" t="n">
         <v>0.91</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15681,7 +15681,7 @@
         <v>1.55</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16150,10 +16150,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16183,7 +16183,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16606,7 +16606,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE34" t="n">
         <v>1.27</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17062,7 +17062,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE35" t="n">
         <v>1.82</v>
@@ -17095,7 +17095,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17529,7 +17529,7 @@
         <v>1.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17998,7 +17998,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE37" t="n">
         <v>1.5</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -18462,7 +18462,7 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE38" t="n">
         <v>1</v>
@@ -18495,7 +18495,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18934,7 +18934,7 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE39" t="n">
         <v>1.82</v>
@@ -18967,7 +18967,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19873,7 +19873,7 @@
         <v>1.55</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20359,7 +20359,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20801,7 +20801,7 @@
         <v>1.82</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21254,7 +21254,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE44" t="n">
         <v>1.36</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21710,10 +21710,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22638,10 +22638,10 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23094,7 +23094,7 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE48" t="n">
         <v>1</v>
@@ -23127,7 +23127,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23542,7 +23542,7 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE49" t="n">
         <v>1.5</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24014,10 +24014,10 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24465,7 +24465,7 @@
         <v>1.5</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24918,10 +24918,10 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -24951,7 +24951,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25393,7 +25393,7 @@
         <v>2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25846,10 +25846,10 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -25879,7 +25879,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26305,7 +26305,7 @@
         <v>1.18</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26787,7 +26787,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27226,7 +27226,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE57" t="n">
         <v>0.91</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27731,7 +27731,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28173,7 +28173,7 @@
         <v>2</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30461,7 +30461,7 @@
         <v>2</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF64" t="n">
         <v>1.25</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30909,7 +30909,7 @@
         <v>2.27</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31362,10 +31362,10 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31834,10 +31834,10 @@
         <v>63</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32294,10 +32294,10 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32766,10 +32766,10 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33214,10 +33214,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33670,10 +33670,10 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34129,7 +34129,7 @@
         <v>1.55</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34582,7 +34582,7 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE73" t="n">
         <v>0.91</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35057,7 +35057,7 @@
         <v>1.82</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -35087,7 +35087,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35982,7 +35982,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE76" t="n">
         <v>0.92</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38319,7 +38319,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38742,10 +38742,10 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF82" t="n">
         <v>1.6</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39198,10 +39198,10 @@
         <v>60</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39654,10 +39654,10 @@
         <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40118,10 +40118,10 @@
         <v>90</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF85" t="n">
         <v>0.8</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40566,10 +40566,10 @@
         <v>30</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF86" t="n">
         <v>0.4</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41014,10 +41014,10 @@
         <v>65</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF87" t="n">
         <v>1.8</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41486,10 +41486,10 @@
         <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -41519,7 +41519,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41942,10 +41942,10 @@
         <v>60</v>
       </c>
       <c r="DD89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE89" t="n">
         <v>1.09</v>
-      </c>
-      <c r="DE89" t="n">
-        <v>0.9</v>
       </c>
       <c r="DF89" t="n">
         <v>1</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42389,7 +42389,7 @@
         <v>1.55</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42891,7 +42891,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44229,7 +44229,7 @@
         <v>1.5</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44690,7 +44690,7 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE95" t="n">
         <v>0.92</v>
@@ -44723,7 +44723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45618,7 +45618,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE97" t="n">
         <v>1.82</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46062,10 +46062,10 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46534,7 +46534,7 @@
         <v>50</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE99" t="n">
         <v>1.5</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47457,7 +47457,7 @@
         <v>2</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47913,7 +47913,7 @@
         <v>1.55</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48358,10 +48358,10 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF103" t="n">
         <v>0.83</v>
@@ -48391,7 +48391,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48806,10 +48806,10 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49278,7 +49278,7 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE105" t="n">
         <v>1.27</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49726,7 +49726,7 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE106" t="n">
         <v>0.92</v>
@@ -49759,7 +49759,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50198,7 +50198,7 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE107" t="n">
         <v>1</v>
@@ -50231,7 +50231,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50657,7 +50657,7 @@
         <v>1.55</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -50687,7 +50687,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51569,7 +51569,7 @@
         <v>2</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52022,7 +52022,7 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE111" t="n">
         <v>1.36</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52481,7 +52481,7 @@
         <v>1.82</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53366,7 +53366,7 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE114" t="n">
         <v>0.92</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -53830,7 +53830,7 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE115" t="n">
         <v>1.27</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54289,7 +54289,7 @@
         <v>1.55</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF116" t="n">
         <v>1.43</v>
@@ -54319,7 +54319,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -54745,7 +54745,7 @@
         <v>2.27</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF117" t="n">
         <v>2.67</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55209,7 +55209,7 @@
         <v>1.18</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56118,10 +56118,10 @@
         <v>54</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56558,7 +56558,7 @@
         <v>62</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE121" t="n">
         <v>1.82</v>
@@ -56591,7 +56591,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57494,10 +57494,10 @@
         <v>50</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -57527,7 +57527,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57950,7 +57950,7 @@
         <v>57</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE124" t="n">
         <v>1.27</v>
@@ -57983,7 +57983,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58873,7 +58873,7 @@
         <v>2.27</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF126" t="n">
         <v>2.71</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60287,7 +60287,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60718,7 +60718,7 @@
         <v>63</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE130" t="n">
         <v>0.91</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61190,7 +61190,7 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE131" t="n">
         <v>1.36</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61650,10 +61650,10 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF132" t="n">
         <v>3</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62098,10 +62098,10 @@
         <v>69</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62557,7 +62557,7 @@
         <v>1.36</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF134" t="n">
         <v>1.25</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63013,7 +63013,7 @@
         <v>1.55</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63453,7 +63453,7 @@
         <v>1.5</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF136" t="n">
         <v>1.38</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -63922,7 +63922,7 @@
         <v>69</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE137" t="n">
         <v>0.92</v>
@@ -63955,7 +63955,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64394,7 +64394,7 @@
         <v>63</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE138" t="n">
         <v>1</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -64866,10 +64866,10 @@
         <v>88</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF139" t="n">
         <v>0.67</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65330,7 +65330,7 @@
         <v>57</v>
       </c>
       <c r="DD140" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE140" t="n">
         <v>0.91</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66261,7 +66261,7 @@
         <v>1.82</v>
       </c>
       <c r="DE142" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF142" t="n">
         <v>1.75</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66690,10 +66690,10 @@
         <v>53</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF143" t="n">
         <v>0.5</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67629,7 +67629,7 @@
         <v>1.18</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF145" t="n">
         <v>1.38</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68093,7 +68093,7 @@
         <v>1.55</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF146" t="n">
         <v>1.44</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68554,7 +68554,7 @@
         <v>50</v>
       </c>
       <c r="DD147" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE147" t="n">
         <v>1.36</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69490,7 +69490,7 @@
         <v>77</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE149" t="n">
         <v>0.92</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69949,7 +69949,7 @@
         <v>2.27</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF150" t="n">
         <v>2.38</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70402,10 +70402,10 @@
         <v>78</v>
       </c>
       <c r="DD151" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF151" t="n">
         <v>2.11</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70861,7 +70861,7 @@
         <v>1.5</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF152" t="n">
         <v>1.56</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71330,7 +71330,7 @@
         <v>65</v>
       </c>
       <c r="DD153" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE153" t="n">
         <v>1.27</v>
@@ -71363,7 +71363,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71789,7 +71789,7 @@
         <v>1.18</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF154" t="n">
         <v>1.33</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72250,7 +72250,7 @@
         <v>80</v>
       </c>
       <c r="DD155" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE155" t="n">
         <v>1.5</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72722,7 +72722,7 @@
         <v>62</v>
       </c>
       <c r="DD156" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE156" t="n">
         <v>1.82</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73197,7 +73197,7 @@
         <v>2</v>
       </c>
       <c r="DE157" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF157" t="n">
         <v>2.3</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74122,7 +74122,7 @@
         <v>56</v>
       </c>
       <c r="DD159" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE159" t="n">
         <v>1</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75053,7 +75053,7 @@
         <v>1.82</v>
       </c>
       <c r="DE161" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF161" t="n">
         <v>1.56</v>
@@ -75083,7 +75083,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -75970,10 +75970,10 @@
         <v>79</v>
       </c>
       <c r="DD163" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE163" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF163" t="n">
         <v>1.33</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76459,7 +76459,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76874,10 +76874,10 @@
         <v>79</v>
       </c>
       <c r="DD165" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE165" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF165" t="n">
         <v>2.78</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77341,7 +77341,7 @@
         <v>1.82</v>
       </c>
       <c r="DE166" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF166" t="n">
         <v>1.7</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77802,10 +77802,10 @@
         <v>59</v>
       </c>
       <c r="DD167" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DE167" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF167" t="n">
         <v>0.4</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -78722,7 +78722,7 @@
         <v>65</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DE169" t="n">
         <v>1</v>
@@ -78755,7 +78755,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79162,10 +79162,10 @@
         <v>65</v>
       </c>
       <c r="DD170" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE170" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF170" t="n">
         <v>1.2</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -79618,7 +79618,7 @@
         <v>60</v>
       </c>
       <c r="DD171" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE171" t="n">
         <v>1.82</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80522,7 +80522,7 @@
         <v>67</v>
       </c>
       <c r="DD173" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DE173" t="n">
         <v>1.5</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -80981,7 +80981,7 @@
         <v>1.5</v>
       </c>
       <c r="DE174" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DF174" t="n">
         <v>1.64</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82389,7 +82389,7 @@
         <v>1.36</v>
       </c>
       <c r="DE177" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF177" t="n">
         <v>1.4</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82512,6 +82512,3742 @@
       <c r="EL177" t="inlineStr">
         <is>
           <t>2.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>23</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>46052.82291666666</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" t="n">
+        <v>6</v>
+      </c>
+      <c r="K178" t="n">
+        <v>5</v>
+      </c>
+      <c r="L178" t="n">
+        <v>11</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>2</v>
+      </c>
+      <c r="R178" t="n">
+        <v>3</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4</v>
+      </c>
+      <c r="T178" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" t="n">
+        <v>6</v>
+      </c>
+      <c r="V178" t="n">
+        <v>8</v>
+      </c>
+      <c r="W178" t="n">
+        <v>13</v>
+      </c>
+      <c r="X178" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN178" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR178" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS178" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU178" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV178" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX178" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY178" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ178" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA178" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB178" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC178" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD178" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE178" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF178" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DG178" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DH178" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DI178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DJ178" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK178" t="n">
+        <v>41</v>
+      </c>
+      <c r="DL178" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM178" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN178" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO178" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW178" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DX178" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="DY178" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="DZ178" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EA178" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EB178" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC178" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="ED178" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EE178" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EF178" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG178" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EH178" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI178" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EJ178" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK178" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EL178" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>23</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>46053.625</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" t="n">
+        <v>5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>7</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>9</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3</v>
+      </c>
+      <c r="T179" t="n">
+        <v>6</v>
+      </c>
+      <c r="U179" t="n">
+        <v>3</v>
+      </c>
+      <c r="V179" t="n">
+        <v>15</v>
+      </c>
+      <c r="W179" t="n">
+        <v>10</v>
+      </c>
+      <c r="X179" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>5450</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>131</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR179" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS179" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU179" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV179" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX179" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY179" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ179" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA179" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB179" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC179" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD179" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DE179" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF179" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DG179" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DH179" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DI179" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ179" t="n">
+        <v>68</v>
+      </c>
+      <c r="DK179" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL179" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM179" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN179" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO179" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW179" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="DX179" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="DY179" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="DZ179" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EA179" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EB179" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC179" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="ED179" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EE179" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EF179" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG179" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EH179" t="inlineStr"/>
+      <c r="EI179" t="inlineStr"/>
+      <c r="EJ179" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EK179" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL179" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>23</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>46053.71875</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>7</v>
+      </c>
+      <c r="K180" t="n">
+        <v>3</v>
+      </c>
+      <c r="L180" t="n">
+        <v>10</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>5</v>
+      </c>
+      <c r="R180" t="n">
+        <v>4</v>
+      </c>
+      <c r="S180" t="n">
+        <v>14</v>
+      </c>
+      <c r="T180" t="n">
+        <v>3</v>
+      </c>
+      <c r="U180" t="n">
+        <v>19</v>
+      </c>
+      <c r="V180" t="n">
+        <v>7</v>
+      </c>
+      <c r="W180" t="n">
+        <v>8</v>
+      </c>
+      <c r="X180" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>534</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR180" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS180" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU180" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV180" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX180" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY180" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ180" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA180" t="n">
+        <v>91</v>
+      </c>
+      <c r="DB180" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC180" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE180" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DF180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG180" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DH180" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI180" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ180" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK180" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM180" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN180" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO180" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW180" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="DX180" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DY180" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="DZ180" t="inlineStr"/>
+      <c r="EA180" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB180" t="inlineStr"/>
+      <c r="EC180" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="ED180" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EE180" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EF180" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EG180" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EH180" t="inlineStr"/>
+      <c r="EI180" t="inlineStr"/>
+      <c r="EJ180" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EK180" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL180" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>23</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>46053.82291666666</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2</v>
+      </c>
+      <c r="I181" t="n">
+        <v>2</v>
+      </c>
+      <c r="J181" t="n">
+        <v>6</v>
+      </c>
+      <c r="K181" t="n">
+        <v>6</v>
+      </c>
+      <c r="L181" t="n">
+        <v>12</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>2</v>
+      </c>
+      <c r="R181" t="n">
+        <v>5</v>
+      </c>
+      <c r="S181" t="n">
+        <v>11</v>
+      </c>
+      <c r="T181" t="n">
+        <v>10</v>
+      </c>
+      <c r="U181" t="n">
+        <v>13</v>
+      </c>
+      <c r="V181" t="n">
+        <v>15</v>
+      </c>
+      <c r="W181" t="n">
+        <v>6</v>
+      </c>
+      <c r="X181" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>529</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR181" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS181" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU181" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV181" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX181" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY181" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ181" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA181" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC181" t="n">
+        <v>87</v>
+      </c>
+      <c r="DD181" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DE181" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF181" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DG181" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DH181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DI181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ181" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK181" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL181" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM181" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN181" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO181" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP181" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ181" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW181" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DX181" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY181" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="DZ181" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EA181" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EB181" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC181" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="ED181" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EE181" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EF181" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EG181" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH181" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI181" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EJ181" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EK181" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL181" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>23</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>46054.52083333334</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" t="n">
+        <v>9</v>
+      </c>
+      <c r="K182" t="n">
+        <v>4</v>
+      </c>
+      <c r="L182" t="n">
+        <v>13</v>
+      </c>
+      <c r="M182" t="n">
+        <v>2</v>
+      </c>
+      <c r="N182" t="n">
+        <v>4</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>3</v>
+      </c>
+      <c r="R182" t="n">
+        <v>4</v>
+      </c>
+      <c r="S182" t="n">
+        <v>6</v>
+      </c>
+      <c r="T182" t="n">
+        <v>11</v>
+      </c>
+      <c r="U182" t="n">
+        <v>9</v>
+      </c>
+      <c r="V182" t="n">
+        <v>15</v>
+      </c>
+      <c r="W182" t="n">
+        <v>10</v>
+      </c>
+      <c r="X182" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS182" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV182" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW182" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX182" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY182" t="n">
+        <v>141</v>
+      </c>
+      <c r="BZ182" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA182" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CB182" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM182" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR182" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS182" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU182" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV182" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX182" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY182" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ182" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA182" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB182" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC182" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE182" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF182" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DG182" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH182" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI182" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ182" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK182" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL182" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM182" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN182" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO182" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP182" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ182" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW182" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="DX182" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="DY182" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="DZ182" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EA182" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EB182" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EC182" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="ED182" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE182" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="EF182" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EG182" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EH182" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI182" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EJ182" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EK182" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL182" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>23</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>46054.625</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" t="n">
+        <v>3</v>
+      </c>
+      <c r="J183" t="n">
+        <v>8</v>
+      </c>
+      <c r="K183" t="n">
+        <v>2</v>
+      </c>
+      <c r="L183" t="n">
+        <v>10</v>
+      </c>
+      <c r="M183" t="n">
+        <v>5</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>7</v>
+      </c>
+      <c r="R183" t="n">
+        <v>4</v>
+      </c>
+      <c r="S183" t="n">
+        <v>15</v>
+      </c>
+      <c r="T183" t="n">
+        <v>4</v>
+      </c>
+      <c r="U183" t="n">
+        <v>22</v>
+      </c>
+      <c r="V183" t="n">
+        <v>8</v>
+      </c>
+      <c r="W183" t="n">
+        <v>12</v>
+      </c>
+      <c r="X183" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT183" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV183" t="n">
+        <v>83</v>
+      </c>
+      <c r="BW183" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX183" t="n">
+        <v>20</v>
+      </c>
+      <c r="BY183" t="n">
+        <v>29</v>
+      </c>
+      <c r="BZ183" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA183" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB183" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="CC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL183" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR183" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS183" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU183" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV183" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX183" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY183" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ183" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA183" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB183" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC183" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD183" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DE183" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF183" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DG183" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DH183" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DI183" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ183" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK183" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL183" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM183" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN183" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO183" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW183" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="DX183" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY183" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="DZ183" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EA183" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EB183" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC183" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="ED183" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EE183" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EF183" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG183" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH183" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI183" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ183" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EK183" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EL183" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>23</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>46054.72916666666</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>5</v>
+      </c>
+      <c r="K184" t="n">
+        <v>5</v>
+      </c>
+      <c r="L184" t="n">
+        <v>10</v>
+      </c>
+      <c r="M184" t="n">
+        <v>3</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>5</v>
+      </c>
+      <c r="R184" t="n">
+        <v>2</v>
+      </c>
+      <c r="S184" t="n">
+        <v>8</v>
+      </c>
+      <c r="T184" t="n">
+        <v>6</v>
+      </c>
+      <c r="U184" t="n">
+        <v>13</v>
+      </c>
+      <c r="V184" t="n">
+        <v>8</v>
+      </c>
+      <c r="W184" t="n">
+        <v>12</v>
+      </c>
+      <c r="X184" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV184" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW184" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX184" t="n">
+        <v>49</v>
+      </c>
+      <c r="BY184" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR184" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS184" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU184" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV184" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX184" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY184" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ184" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA184" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB184" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC184" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD184" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DE184" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DG184" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DH184" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DI184" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ184" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK184" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL184" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DM184" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DN184" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DO184" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW184" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="DX184" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DY184" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="DZ184" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EA184" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EB184" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC184" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="ED184" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EE184" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EF184" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG184" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EH184" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EI184" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ184" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EK184" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL184" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>23</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>46054.76041666666</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
+      <c r="I185" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>7</v>
+      </c>
+      <c r="K185" t="n">
+        <v>5</v>
+      </c>
+      <c r="L185" t="n">
+        <v>12</v>
+      </c>
+      <c r="M185" t="n">
+        <v>3</v>
+      </c>
+      <c r="N185" t="n">
+        <v>6</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>5</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7</v>
+      </c>
+      <c r="S185" t="n">
+        <v>11</v>
+      </c>
+      <c r="T185" t="n">
+        <v>6</v>
+      </c>
+      <c r="U185" t="n">
+        <v>16</v>
+      </c>
+      <c r="V185" t="n">
+        <v>13</v>
+      </c>
+      <c r="W185" t="n">
+        <v>19</v>
+      </c>
+      <c r="X185" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS185" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT185" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV185" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW185" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX185" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY185" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ185" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB185" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR185" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS185" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU185" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV185" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX185" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY185" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ185" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA185" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB185" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC185" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD185" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DE185" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF185" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DG185" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DH185" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DI185" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DJ185" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK185" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL185" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM185" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN185" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO185" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW185" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DX185" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="DY185" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="DZ185" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EA185" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EB185" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EC185" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="ED185" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EE185" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EF185" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG185" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EH185" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI185" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EJ185" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EK185" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EL185" t="inlineStr">
+        <is>
+          <t>2.16</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -83636,7 +83636,7 @@
         <v>0</v>
       </c>
       <c r="BF180" t="n">
-        <v>-1</v>
+        <v>6463</v>
       </c>
       <c r="BG180" t="n">
         <v>2</v>
@@ -84084,7 +84084,7 @@
         <v>0</v>
       </c>
       <c r="BF181" t="n">
-        <v>-1</v>
+        <v>6542</v>
       </c>
       <c r="BG181" t="n">
         <v>2</v>
@@ -84556,7 +84556,7 @@
         <v>0</v>
       </c>
       <c r="BF182" t="n">
-        <v>-1</v>
+        <v>25217</v>
       </c>
       <c r="BG182" t="n">
         <v>2</v>
@@ -85020,7 +85020,7 @@
         <v>0</v>
       </c>
       <c r="BF183" t="n">
-        <v>-1</v>
+        <v>2852</v>
       </c>
       <c r="BG183" t="n">
         <v>2</v>
@@ -85492,7 +85492,7 @@
         <v>0</v>
       </c>
       <c r="BF184" t="n">
-        <v>-1</v>
+        <v>7217</v>
       </c>
       <c r="BG184" t="n">
         <v>2</v>
@@ -85964,7 +85964,7 @@
         <v>0</v>
       </c>
       <c r="BF185" t="n">
-        <v>-1</v>
+        <v>5919</v>
       </c>
       <c r="BG185" t="n">
         <v>2</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -84432,13 +84432,13 @@
         <v>3</v>
       </c>
       <c r="R182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
       </c>
       <c r="T182" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U182" t="n">
         <v>9</v>
@@ -84619,10 +84619,10 @@
         <v>1.04</v>
       </c>
       <c r="CA182" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="CB182" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="CC182" t="n">
         <v>0</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL189" headerRowCount="1">
-  <autoFilter ref="A1:EL189"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL193" headerRowCount="1">
+  <autoFilter ref="A1:EL193"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL189"/>
+  <dimension ref="A1:EL193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         <v>1.17</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4562,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE8" t="n">
         <v>1.33</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>1.58</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6861,7 +6861,7 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7330,10 +7330,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7797,7 +7797,7 @@
         <v>0.58</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE16" t="n">
         <v>1.17</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9666,7 +9666,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE19" t="n">
         <v>1.42</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13838,7 +13838,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE28" t="n">
         <v>1.08</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14294,10 +14294,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14761,7 +14761,7 @@
         <v>0.58</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15209,7 +15209,7 @@
         <v>2.08</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15681,7 +15681,7 @@
         <v>1.42</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -19398,10 +19398,10 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19873,7 +19873,7 @@
         <v>1.42</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21257,7 +21257,7 @@
         <v>0.92</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21710,10 +21710,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22182,7 +22182,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
         <v>0.92</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26302,7 +26302,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE55" t="n">
         <v>1.33</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27229,7 +27229,7 @@
         <v>0.92</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28173,7 +28173,7 @@
         <v>2</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28626,7 +28626,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE60" t="n">
         <v>1.5</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29085,7 +29085,7 @@
         <v>1.42</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29546,7 +29546,7 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE62" t="n">
         <v>1.92</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30002,7 +30002,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE63" t="n">
         <v>1.42</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE65" t="n">
         <v>0.92</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31365,7 +31365,7 @@
         <v>0.92</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31837,7 +31837,7 @@
         <v>1.5</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32766,7 +32766,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE69" t="n">
         <v>0.92</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34585,7 +34585,7 @@
         <v>0.58</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35518,7 +35518,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE75" t="n">
         <v>1.92</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36921,7 +36921,7 @@
         <v>2</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37374,7 +37374,7 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE79" t="n">
         <v>0.83</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37814,7 +37814,7 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE80" t="n">
         <v>1.5</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39654,7 +39654,7 @@
         <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE84" t="n">
         <v>1.33</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41017,7 +41017,7 @@
         <v>2.08</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF87" t="n">
         <v>1.8</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41945,7 +41945,7 @@
         <v>1.25</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF89" t="n">
         <v>1</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42389,7 +42389,7 @@
         <v>1.42</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43306,7 +43306,7 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE92" t="n">
         <v>1.17</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43773,7 +43773,7 @@
         <v>1.67</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45146,10 +45146,10 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45618,7 +45618,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE97" t="n">
         <v>1.92</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46990,7 +46990,7 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE100" t="n">
         <v>0.83</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48809,7 +48809,7 @@
         <v>2.08</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51097,7 +51097,7 @@
         <v>1.5</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52025,7 +52025,7 @@
         <v>2.08</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52926,7 +52926,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE113" t="n">
         <v>1.5</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -53830,7 +53830,7 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE115" t="n">
         <v>1.42</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54742,7 +54742,7 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE117" t="n">
         <v>1.33</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55206,7 +55206,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE118" t="n">
         <v>1.5</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56121,7 +56121,7 @@
         <v>1.17</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -57030,10 +57030,10 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58401,7 +58401,7 @@
         <v>1.42</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58870,10 +58870,10 @@
         <v>64</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF126" t="n">
         <v>2.71</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59318,7 +59318,7 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE127" t="n">
         <v>1.17</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61193,7 +61193,7 @@
         <v>0.58</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF131" t="n">
         <v>0.75</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61650,7 +61650,7 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE132" t="n">
         <v>1.08</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62554,7 +62554,7 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE134" t="n">
         <v>1.33</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63013,7 +63013,7 @@
         <v>1.42</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65333,7 +65333,7 @@
         <v>1.5</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66261,7 +66261,7 @@
         <v>1.67</v>
       </c>
       <c r="DE142" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF142" t="n">
         <v>1.75</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67626,7 +67626,7 @@
         <v>82</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE145" t="n">
         <v>0.92</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68557,7 +68557,7 @@
         <v>0.58</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF147" t="n">
         <v>0.44</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69029,7 +69029,7 @@
         <v>1.42</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF148" t="n">
         <v>1.56</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69490,7 +69490,7 @@
         <v>77</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE149" t="n">
         <v>0.92</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69946,7 +69946,7 @@
         <v>59</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE150" t="n">
         <v>1.08</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70861,7 +70861,7 @@
         <v>1.5</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF152" t="n">
         <v>1.56</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71786,7 +71786,7 @@
         <v>80</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE154" t="n">
         <v>1.58</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -74578,7 +74578,7 @@
         <v>67</v>
       </c>
       <c r="DD160" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE160" t="n">
         <v>0.83</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75506,10 +75506,10 @@
         <v>58</v>
       </c>
       <c r="DD162" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF162" t="n">
         <v>2.44</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76874,7 +76874,7 @@
         <v>79</v>
       </c>
       <c r="DD165" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE165" t="n">
         <v>1.5</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77341,7 +77341,7 @@
         <v>1.67</v>
       </c>
       <c r="DE166" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF166" t="n">
         <v>1.7</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77805,7 +77805,7 @@
         <v>0.58</v>
       </c>
       <c r="DE167" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF167" t="n">
         <v>0.4</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78261,7 +78261,7 @@
         <v>1.42</v>
       </c>
       <c r="DE168" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DF168" t="n">
         <v>1.4</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80074,7 +80074,7 @@
         <v>71</v>
       </c>
       <c r="DD172" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DE172" t="n">
         <v>0.92</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81450,7 +81450,7 @@
         <v>80</v>
       </c>
       <c r="DD175" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DE175" t="n">
         <v>1.42</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82386,7 +82386,7 @@
         <v>70</v>
       </c>
       <c r="DD177" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DE177" t="n">
         <v>0.92</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82883,7 +82883,7 @@
         <v>2.66</v>
       </c>
       <c r="DO178" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP178" t="b">
         <v>1</v>
@@ -83325,7 +83325,7 @@
         <v>0.58</v>
       </c>
       <c r="DE179" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF179" t="n">
         <v>0.64</v>
@@ -83355,7 +83355,7 @@
         <v>2.71</v>
       </c>
       <c r="DO179" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -84709,7 +84709,7 @@
         <v>1.25</v>
       </c>
       <c r="DE182" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF182" t="n">
         <v>1.09</v>
@@ -84739,7 +84739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO182" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -85203,7 +85203,7 @@
         <v>2.77</v>
       </c>
       <c r="DO183" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP183" t="b">
         <v>1</v>
@@ -85642,7 +85642,7 @@
         <v>77</v>
       </c>
       <c r="DD184" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE184" t="n">
         <v>1.58</v>
@@ -85675,7 +85675,7 @@
         <v>3.71</v>
       </c>
       <c r="DO184" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP184" t="b">
         <v>1</v>
@@ -86147,7 +86147,7 @@
         <v>2.75</v>
       </c>
       <c r="DO185" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -86436,7 +86436,7 @@
         <v>0</v>
       </c>
       <c r="BF186" t="n">
-        <v>-1</v>
+        <v>5629</v>
       </c>
       <c r="BG186" t="n">
         <v>2</v>
@@ -87683,13 +87683,13 @@
         <v>4</v>
       </c>
       <c r="S189" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T189" t="n">
         <v>9</v>
       </c>
       <c r="U189" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V189" t="n">
         <v>13</v>
@@ -87864,13 +87864,13 @@
         <v>61</v>
       </c>
       <c r="BZ189" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="CA189" t="n">
         <v>1.63</v>
       </c>
       <c r="CB189" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="CC189" t="n">
         <v>0</v>
@@ -88088,6 +88088,1858 @@
       <c r="EL189" t="inlineStr">
         <is>
           <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>24</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>46061.52083333334</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2</v>
+      </c>
+      <c r="J190" t="n">
+        <v>5</v>
+      </c>
+      <c r="K190" t="n">
+        <v>7</v>
+      </c>
+      <c r="L190" t="n">
+        <v>12</v>
+      </c>
+      <c r="M190" t="n">
+        <v>2</v>
+      </c>
+      <c r="N190" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>8</v>
+      </c>
+      <c r="R190" t="n">
+        <v>3</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="n">
+        <v>8</v>
+      </c>
+      <c r="U190" t="n">
+        <v>18</v>
+      </c>
+      <c r="V190" t="n">
+        <v>11</v>
+      </c>
+      <c r="W190" t="n">
+        <v>9</v>
+      </c>
+      <c r="X190" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV190" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW190" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX190" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY190" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ190" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CA190" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB190" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="CC190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR190" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS190" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU190" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV190" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX190" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY190" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ190" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA190" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB190" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC190" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD190" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE190" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF190" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DG190" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DH190" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DI190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ190" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK190" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL190" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM190" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN190" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="DO190" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP190" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ190" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR190" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS190" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT190" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU190" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV190" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW190" t="inlineStr"/>
+      <c r="DX190" t="inlineStr"/>
+      <c r="DY190" t="inlineStr"/>
+      <c r="DZ190" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EA190" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EB190" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EC190" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="ED190" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EE190" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF190" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG190" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EH190" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI190" t="inlineStr"/>
+      <c r="EJ190" t="inlineStr"/>
+      <c r="EK190" t="inlineStr"/>
+      <c r="EL190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>24</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>46061.625</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="n">
+        <v>3</v>
+      </c>
+      <c r="J191" t="n">
+        <v>9</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>10</v>
+      </c>
+      <c r="M191" t="n">
+        <v>4</v>
+      </c>
+      <c r="N191" t="n">
+        <v>4</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>8</v>
+      </c>
+      <c r="R191" t="n">
+        <v>1</v>
+      </c>
+      <c r="S191" t="n">
+        <v>8</v>
+      </c>
+      <c r="T191" t="n">
+        <v>5</v>
+      </c>
+      <c r="U191" t="n">
+        <v>16</v>
+      </c>
+      <c r="V191" t="n">
+        <v>6</v>
+      </c>
+      <c r="W191" t="n">
+        <v>12</v>
+      </c>
+      <c r="X191" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT191" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV191" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW191" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX191" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY191" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ191" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CA191" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB191" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR191" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS191" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU191" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV191" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX191" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY191" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ191" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA191" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB191" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC191" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD191" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DE191" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF191" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DG191" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DH191" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI191" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DJ191" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK191" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL191" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM191" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DN191" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO191" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW191" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="DX191" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DY191" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="DZ191" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EA191" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="EB191" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="EC191" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="ED191" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EE191" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF191" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EG191" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EH191" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EI191" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EJ191" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EK191" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EL191" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>24</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>46061.72916666666</v>
+      </c>
+      <c r="G192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>3</v>
+      </c>
+      <c r="J192" t="n">
+        <v>7</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>7</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>2</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>11</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>11</v>
+      </c>
+      <c r="T192" t="n">
+        <v>5</v>
+      </c>
+      <c r="U192" t="n">
+        <v>22</v>
+      </c>
+      <c r="V192" t="n">
+        <v>5</v>
+      </c>
+      <c r="W192" t="n">
+        <v>8</v>
+      </c>
+      <c r="X192" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU192" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV192" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW192" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX192" t="n">
+        <v>131</v>
+      </c>
+      <c r="BY192" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ192" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CA192" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CB192" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI192" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ192" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ192" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR192" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS192" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT192" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU192" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV192" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW192" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX192" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY192" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ192" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA192" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB192" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC192" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD192" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF192" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DG192" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DH192" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DI192" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ192" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK192" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL192" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DM192" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DN192" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO192" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP192" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ192" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR192" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS192" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT192" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU192" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV192" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW192" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="DX192" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="DY192" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DZ192" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EA192" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="EB192" t="inlineStr">
+        <is>
+          <t>10.94</t>
+        </is>
+      </c>
+      <c r="EC192" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="ED192" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EE192" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EF192" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG192" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH192" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EI192" t="inlineStr"/>
+      <c r="EJ192" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EK192" t="inlineStr"/>
+      <c r="EL192" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>24</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>46061.76041666666</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>2</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6</v>
+      </c>
+      <c r="L193" t="n">
+        <v>9</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>2</v>
+      </c>
+      <c r="R193" t="n">
+        <v>5</v>
+      </c>
+      <c r="S193" t="n">
+        <v>6</v>
+      </c>
+      <c r="T193" t="n">
+        <v>11</v>
+      </c>
+      <c r="U193" t="n">
+        <v>8</v>
+      </c>
+      <c r="V193" t="n">
+        <v>16</v>
+      </c>
+      <c r="W193" t="n">
+        <v>9</v>
+      </c>
+      <c r="X193" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV193" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW193" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX193" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY193" t="n">
+        <v>143</v>
+      </c>
+      <c r="BZ193" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA193" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CB193" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI193" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ193" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP193" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ193" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR193" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS193" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT193" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU193" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV193" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW193" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX193" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY193" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ193" t="n">
+        <v>18</v>
+      </c>
+      <c r="DA193" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB193" t="n">
+        <v>14</v>
+      </c>
+      <c r="DC193" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE193" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF193" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG193" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DH193" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ193" t="n">
+        <v>82</v>
+      </c>
+      <c r="DK193" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL193" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM193" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN193" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DO193" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP193" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ193" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR193" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS193" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT193" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU193" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV193" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW193" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DX193" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="DY193" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="DZ193" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EA193" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EB193" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EC193" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED193" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EE193" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF193" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG193" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EH193" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI193" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EJ193" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EK193" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL193" t="inlineStr">
+        <is>
+          <t>3.00</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL193" headerRowCount="1">
-  <autoFilter ref="A1:EL193"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL197" headerRowCount="1">
+  <autoFilter ref="A1:EL197"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL193"/>
+  <dimension ref="A1:EL197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE7" t="n">
         <v>1.33</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4565,7 +4565,7 @@
         <v>2.33</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         <v>2.08</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE10" t="n">
         <v>1.58</v>
@@ -6386,10 +6386,10 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE17" t="n">
         <v>1.92</v>
@@ -9197,7 +9197,7 @@
         <v>2.08</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -10589,7 +10589,7 @@
         <v>1.67</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11994,10 +11994,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12930,10 +12930,10 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13838,10 +13838,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15678,7 +15678,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -16606,7 +16606,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE34" t="n">
         <v>1.42</v>
@@ -18001,7 +18001,7 @@
         <v>1.17</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18495,7 +18495,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19398,7 +19398,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE40" t="n">
         <v>0.83</v>
@@ -20326,10 +20326,10 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20359,7 +20359,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21254,7 +21254,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE44" t="n">
         <v>1.25</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE47" t="n">
         <v>1.5</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23545,7 +23545,7 @@
         <v>0.58</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24465,7 +24465,7 @@
         <v>1.5</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -25393,7 +25393,7 @@
         <v>2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26757,7 +26757,7 @@
         <v>1.67</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -26787,7 +26787,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27226,7 +27226,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE57" t="n">
         <v>0.83</v>
@@ -27698,7 +27698,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE58" t="n">
         <v>0.92</v>
@@ -28629,7 +28629,7 @@
         <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30002,7 +30002,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE63" t="n">
         <v>1.42</v>
@@ -30461,7 +30461,7 @@
         <v>2</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF64" t="n">
         <v>1.25</v>
@@ -31362,7 +31362,7 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
@@ -32294,7 +32294,7 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE68" t="n">
         <v>1.58</v>
@@ -33217,7 +33217,7 @@
         <v>2.08</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -33673,7 +33673,7 @@
         <v>0.58</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -34126,7 +34126,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE72" t="n">
         <v>1.5</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35087,7 +35087,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35518,7 +35518,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE75" t="n">
         <v>1.92</v>
@@ -37377,7 +37377,7 @@
         <v>1.33</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37817,7 +37817,7 @@
         <v>2.33</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -39198,7 +39198,7 @@
         <v>60</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE83" t="n">
         <v>1.58</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40121,7 +40121,7 @@
         <v>0.58</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF85" t="n">
         <v>0.8</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41489,7 +41489,7 @@
         <v>1.5</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -41942,7 +41942,7 @@
         <v>60</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -42386,7 +42386,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE90" t="n">
         <v>1</v>
@@ -42861,7 +42861,7 @@
         <v>1.42</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -43306,7 +43306,7 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE92" t="n">
         <v>1.17</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46062,7 +46062,7 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE98" t="n">
         <v>1.33</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46537,7 +46537,7 @@
         <v>1.5</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -46993,7 +46993,7 @@
         <v>2.33</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -47913,7 +47913,7 @@
         <v>1.42</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -48358,10 +48358,10 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF103" t="n">
         <v>0.83</v>
@@ -48391,7 +48391,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50654,7 +50654,7 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE108" t="n">
         <v>0.92</v>
@@ -52481,7 +52481,7 @@
         <v>1.67</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52926,10 +52926,10 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53366,7 +53366,7 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE114" t="n">
         <v>0.92</v>
@@ -54289,7 +54289,7 @@
         <v>1.42</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF116" t="n">
         <v>1.43</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55665,7 +55665,7 @@
         <v>1.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -56558,7 +56558,7 @@
         <v>62</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE121" t="n">
         <v>1.92</v>
@@ -57030,7 +57030,7 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE122" t="n">
         <v>1.25</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58398,7 +58398,7 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE125" t="n">
         <v>0.83</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59785,7 +59785,7 @@
         <v>2</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF128" t="n">
         <v>2.13</v>
@@ -60721,7 +60721,7 @@
         <v>1.17</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF130" t="n">
         <v>1.5</v>
@@ -61653,7 +61653,7 @@
         <v>2.83</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF132" t="n">
         <v>3</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62554,7 +62554,7 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE134" t="n">
         <v>1.33</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63453,7 +63453,7 @@
         <v>1.5</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF136" t="n">
         <v>1.38</v>
@@ -63922,7 +63922,7 @@
         <v>69</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE137" t="n">
         <v>0.92</v>
@@ -64394,7 +64394,7 @@
         <v>63</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE138" t="n">
         <v>1.17</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67154,10 +67154,10 @@
         <v>66</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF144" t="n">
         <v>1.5</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -68090,10 +68090,10 @@
         <v>84</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF146" t="n">
         <v>1.44</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69949,7 +69949,7 @@
         <v>2.33</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF150" t="n">
         <v>2.38</v>
@@ -71330,7 +71330,7 @@
         <v>65</v>
       </c>
       <c r="DD153" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE153" t="n">
         <v>1.42</v>
@@ -72253,7 +72253,7 @@
         <v>0.58</v>
       </c>
       <c r="DE155" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF155" t="n">
         <v>0.6</v>
@@ -72722,7 +72722,7 @@
         <v>62</v>
       </c>
       <c r="DD156" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE156" t="n">
         <v>1.92</v>
@@ -74578,10 +74578,10 @@
         <v>67</v>
       </c>
       <c r="DD160" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF160" t="n">
         <v>1.44</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75973,7 +75973,7 @@
         <v>1.5</v>
       </c>
       <c r="DE163" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF163" t="n">
         <v>1.33</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -78258,7 +78258,7 @@
         <v>70</v>
       </c>
       <c r="DD168" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE168" t="n">
         <v>1.25</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -79162,10 +79162,10 @@
         <v>65</v>
       </c>
       <c r="DD170" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE170" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF170" t="n">
         <v>1.2</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -80522,10 +80522,10 @@
         <v>67</v>
       </c>
       <c r="DD173" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE173" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DF173" t="n">
         <v>0.9</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -81917,7 +81917,7 @@
         <v>2</v>
       </c>
       <c r="DE176" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF176" t="n">
         <v>2.09</v>
@@ -82386,7 +82386,7 @@
         <v>70</v>
       </c>
       <c r="DD177" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE177" t="n">
         <v>0.92</v>
@@ -82853,7 +82853,7 @@
         <v>1.17</v>
       </c>
       <c r="DE178" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF178" t="n">
         <v>1.18</v>
@@ -84706,7 +84706,7 @@
         <v>62</v>
       </c>
       <c r="DD182" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE182" t="n">
         <v>1</v>
@@ -85173,7 +85173,7 @@
         <v>0.58</v>
       </c>
       <c r="DE183" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF183" t="n">
         <v>0.64</v>
@@ -85203,7 +85203,7 @@
         <v>2.77</v>
       </c>
       <c r="DO183" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP183" t="b">
         <v>1</v>
@@ -86114,7 +86114,7 @@
         <v>73</v>
       </c>
       <c r="DD185" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE185" t="n">
         <v>1.5</v>
@@ -86147,7 +86147,7 @@
         <v>2.75</v>
       </c>
       <c r="DO185" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -87045,7 +87045,7 @@
         <v>1.5</v>
       </c>
       <c r="DE187" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DF187" t="n">
         <v>1.36</v>
@@ -87498,7 +87498,7 @@
         <v>78</v>
       </c>
       <c r="DD188" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE188" t="n">
         <v>1.42</v>
@@ -87987,7 +87987,7 @@
         <v>3.03</v>
       </c>
       <c r="DO189" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -89806,7 +89806,7 @@
         <v>69</v>
       </c>
       <c r="DD193" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE193" t="n">
         <v>1</v>
@@ -89940,6 +89940,1862 @@
       <c r="EL193" t="inlineStr">
         <is>
           <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>25</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>46066.82291666666</v>
+      </c>
+      <c r="G194" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" t="n">
+        <v>3</v>
+      </c>
+      <c r="I194" t="n">
+        <v>5</v>
+      </c>
+      <c r="J194" t="n">
+        <v>2</v>
+      </c>
+      <c r="K194" t="n">
+        <v>4</v>
+      </c>
+      <c r="L194" t="n">
+        <v>6</v>
+      </c>
+      <c r="M194" t="n">
+        <v>2</v>
+      </c>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>6</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7</v>
+      </c>
+      <c r="S194" t="n">
+        <v>7</v>
+      </c>
+      <c r="T194" t="n">
+        <v>5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>13</v>
+      </c>
+      <c r="V194" t="n">
+        <v>12</v>
+      </c>
+      <c r="W194" t="n">
+        <v>11</v>
+      </c>
+      <c r="X194" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU194" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV194" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW194" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX194" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY194" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ194" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA194" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB194" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CC194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP194" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR194" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS194" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU194" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV194" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX194" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY194" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ194" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA194" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB194" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC194" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD194" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE194" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DF194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ194" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK194" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL194" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM194" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN194" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO194" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU194" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV194" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW194" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DX194" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DY194" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="DZ194" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EA194" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EB194" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EC194" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="ED194" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EE194" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EF194" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EG194" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EH194" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI194" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EJ194" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK194" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL194" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>25</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>46067.625</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" t="n">
+        <v>5</v>
+      </c>
+      <c r="J195" t="n">
+        <v>10</v>
+      </c>
+      <c r="K195" t="n">
+        <v>7</v>
+      </c>
+      <c r="L195" t="n">
+        <v>17</v>
+      </c>
+      <c r="M195" t="n">
+        <v>2</v>
+      </c>
+      <c r="N195" t="n">
+        <v>1</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>8</v>
+      </c>
+      <c r="R195" t="n">
+        <v>4</v>
+      </c>
+      <c r="S195" t="n">
+        <v>12</v>
+      </c>
+      <c r="T195" t="n">
+        <v>9</v>
+      </c>
+      <c r="U195" t="n">
+        <v>20</v>
+      </c>
+      <c r="V195" t="n">
+        <v>13</v>
+      </c>
+      <c r="W195" t="n">
+        <v>8</v>
+      </c>
+      <c r="X195" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>690</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV195" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW195" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX195" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY195" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ195" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CA195" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CB195" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="CC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM195" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP195" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR195" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS195" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU195" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV195" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW195" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX195" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY195" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ195" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA195" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB195" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC195" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD195" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DE195" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DF195" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DG195" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH195" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DI195" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ195" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK195" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL195" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN195" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO195" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU195" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV195" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW195" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DX195" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="DY195" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="DZ195" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EA195" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EB195" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EC195" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED195" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EE195" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF195" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG195" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EH195" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI195" t="inlineStr"/>
+      <c r="EJ195" t="inlineStr"/>
+      <c r="EK195" t="inlineStr"/>
+      <c r="EL195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>25</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>46067.71875</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3</v>
+      </c>
+      <c r="I196" t="n">
+        <v>5</v>
+      </c>
+      <c r="J196" t="n">
+        <v>12</v>
+      </c>
+      <c r="K196" t="n">
+        <v>4</v>
+      </c>
+      <c r="L196" t="n">
+        <v>16</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>3</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>7</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7</v>
+      </c>
+      <c r="S196" t="n">
+        <v>18</v>
+      </c>
+      <c r="T196" t="n">
+        <v>4</v>
+      </c>
+      <c r="U196" t="n">
+        <v>25</v>
+      </c>
+      <c r="V196" t="n">
+        <v>11</v>
+      </c>
+      <c r="W196" t="n">
+        <v>8</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV196" t="n">
+        <v>94</v>
+      </c>
+      <c r="BW196" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX196" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY196" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ196" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CA196" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB196" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="CC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR196" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS196" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU196" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV196" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX196" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY196" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ196" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA196" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB196" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC196" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD196" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DE196" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DF196" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DG196" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ196" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK196" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL196" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN196" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO196" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU196" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV196" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW196" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DX196" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DY196" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DZ196" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EA196" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EB196" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EC196" t="inlineStr"/>
+      <c r="ED196" t="inlineStr"/>
+      <c r="EE196" t="inlineStr"/>
+      <c r="EF196" t="inlineStr"/>
+      <c r="EG196" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EH196" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI196" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EJ196" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EK196" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EL196" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>25</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>46067.82291666666</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>2</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="n">
+        <v>5</v>
+      </c>
+      <c r="L197" t="n">
+        <v>8</v>
+      </c>
+      <c r="M197" t="n">
+        <v>4</v>
+      </c>
+      <c r="N197" t="n">
+        <v>4</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>2</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="n">
+        <v>13</v>
+      </c>
+      <c r="U197" t="n">
+        <v>7</v>
+      </c>
+      <c r="V197" t="n">
+        <v>16</v>
+      </c>
+      <c r="W197" t="n">
+        <v>8</v>
+      </c>
+      <c r="X197" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT197" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV197" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW197" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX197" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY197" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ197" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CA197" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB197" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR197" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS197" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU197" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV197" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX197" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY197" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ197" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA197" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB197" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC197" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD197" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DE197" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DF197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG197" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI197" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DJ197" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK197" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL197" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DM197" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DN197" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO197" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP197" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ197" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR197" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS197" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT197" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU197" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV197" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW197" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DX197" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="DY197" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="DZ197" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="EA197" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EB197" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC197" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED197" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EE197" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF197" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG197" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EH197" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EI197" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EJ197" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EK197" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EL197" t="inlineStr">
+        <is>
+          <t>3.26</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL197" headerRowCount="1">
-  <autoFilter ref="A1:EL197"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL201" headerRowCount="1">
+  <autoFilter ref="A1:EL201"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL197"/>
+  <dimension ref="A1:EL201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE2" t="n">
         <v>1.46</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3634,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE9" t="n">
         <v>1.23</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         <v>1.38</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5933,7 +5933,7 @@
         <v>1.42</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6861,7 +6861,7 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7794,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE15" t="n">
         <v>1</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE18" t="n">
         <v>0.77</v>
@@ -9227,7 +9227,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11530,10 +11530,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12466,7 +12466,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE25" t="n">
         <v>1.17</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13389,7 +13389,7 @@
         <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15206,10 +15206,10 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16150,10 +16150,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16183,7 +16183,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17095,7 +17095,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17526,7 +17526,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE36" t="n">
         <v>1.5</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -18934,7 +18934,7 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE39" t="n">
         <v>1.92</v>
@@ -18967,7 +18967,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19401,7 +19401,7 @@
         <v>1.38</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20801,7 +20801,7 @@
         <v>1.67</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22185,7 +22185,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23127,7 +23127,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24017,7 +24017,7 @@
         <v>1.17</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24462,7 +24462,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE51" t="n">
         <v>1.23</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE52" t="n">
         <v>1.33</v>
@@ -24951,7 +24951,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25390,7 +25390,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE53" t="n">
         <v>1.46</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25846,10 +25846,10 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -25879,7 +25879,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27229,7 +27229,7 @@
         <v>1.08</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27701,7 +27701,7 @@
         <v>1.31</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -27731,7 +27731,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28170,7 +28170,7 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE59" t="n">
         <v>1</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30458,7 +30458,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE64" t="n">
         <v>1.23</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30909,7 +30909,7 @@
         <v>2.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32297,7 +32297,7 @@
         <v>1.23</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32769,7 +32769,7 @@
         <v>2.83</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33214,7 +33214,7 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE70" t="n">
         <v>1.46</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33670,7 +33670,7 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE71" t="n">
         <v>1.23</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34585,7 +34585,7 @@
         <v>0.58</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35985,7 +35985,7 @@
         <v>1.17</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36454,7 +36454,7 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE77" t="n">
         <v>1.42</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36918,7 +36918,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE78" t="n">
         <v>1.25</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38319,7 +38319,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38745,7 +38745,7 @@
         <v>1.17</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF82" t="n">
         <v>1.6</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39201,7 +39201,7 @@
         <v>1.08</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40118,7 +40118,7 @@
         <v>90</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE85" t="n">
         <v>1.46</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41014,7 +41014,7 @@
         <v>65</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE87" t="n">
         <v>1</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41519,7 +41519,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42891,7 +42891,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44226,10 +44226,10 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44690,10 +44690,10 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -44723,7 +44723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45149,7 +45149,7 @@
         <v>1.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47454,7 +47454,7 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE101" t="n">
         <v>1.5</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48806,7 +48806,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE104" t="n">
         <v>1</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49729,7 +49729,7 @@
         <v>0.58</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -49759,7 +49759,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50198,7 +50198,7 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE107" t="n">
         <v>1.17</v>
@@ -50231,7 +50231,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50657,7 +50657,7 @@
         <v>1.31</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -50687,7 +50687,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51094,10 +51094,10 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51566,10 +51566,10 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52022,7 +52022,7 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE111" t="n">
         <v>1.25</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -53369,7 +53369,7 @@
         <v>1.23</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54319,7 +54319,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55662,7 +55662,7 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE119" t="n">
         <v>0.77</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56591,7 +56591,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57497,7 +57497,7 @@
         <v>0.58</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -57527,7 +57527,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57983,7 +57983,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58401,7 +58401,7 @@
         <v>1.31</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59782,7 +59782,7 @@
         <v>50</v>
       </c>
       <c r="DD128" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE128" t="n">
         <v>1.46</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60287,7 +60287,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61190,7 +61190,7 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE131" t="n">
         <v>1.25</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -62098,10 +62098,10 @@
         <v>69</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE136" t="n">
         <v>1.46</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -63925,7 +63925,7 @@
         <v>1.08</v>
       </c>
       <c r="DE137" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -63955,7 +63955,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64866,7 +64866,7 @@
         <v>88</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE139" t="n">
         <v>1.5</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65333,7 +65333,7 @@
         <v>1.5</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65786,7 +65786,7 @@
         <v>66</v>
       </c>
       <c r="DD141" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE141" t="n">
         <v>1.92</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66693,7 +66693,7 @@
         <v>0.58</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF143" t="n">
         <v>0.5</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67629,7 +67629,7 @@
         <v>1.33</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF145" t="n">
         <v>1.38</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -69029,7 +69029,7 @@
         <v>1.42</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF148" t="n">
         <v>1.56</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69493,7 +69493,7 @@
         <v>2.83</v>
       </c>
       <c r="DE149" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF149" t="n">
         <v>2.75</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70402,7 +70402,7 @@
         <v>78</v>
       </c>
       <c r="DD151" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE151" t="n">
         <v>1.5</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70858,7 +70858,7 @@
         <v>64</v>
       </c>
       <c r="DD152" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE152" t="n">
         <v>1</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71363,7 +71363,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71789,7 +71789,7 @@
         <v>1.33</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF154" t="n">
         <v>1.33</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72250,7 +72250,7 @@
         <v>80</v>
       </c>
       <c r="DD155" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE155" t="n">
         <v>1.46</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73194,7 +73194,7 @@
         <v>70</v>
       </c>
       <c r="DD157" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE157" t="n">
         <v>1.33</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73666,10 +73666,10 @@
         <v>80</v>
       </c>
       <c r="DD158" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE158" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF158" t="n">
         <v>1.5</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -75053,7 +75053,7 @@
         <v>1.67</v>
       </c>
       <c r="DE161" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF161" t="n">
         <v>1.56</v>
@@ -75083,7 +75083,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75509,7 +75509,7 @@
         <v>2.33</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF162" t="n">
         <v>2.44</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76459,7 +76459,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78722,7 +78722,7 @@
         <v>65</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE169" t="n">
         <v>1.17</v>
@@ -78755,7 +78755,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80077,7 +80077,7 @@
         <v>2.33</v>
       </c>
       <c r="DE172" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF172" t="n">
         <v>2.2</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80978,7 +80978,7 @@
         <v>86</v>
       </c>
       <c r="DD174" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DE174" t="n">
         <v>1.33</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81914,7 +81914,7 @@
         <v>68</v>
       </c>
       <c r="DD176" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE176" t="n">
         <v>0.77</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82389,7 +82389,7 @@
         <v>1.38</v>
       </c>
       <c r="DE177" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF177" t="n">
         <v>1.4</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82883,7 +82883,7 @@
         <v>2.66</v>
       </c>
       <c r="DO178" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP178" t="b">
         <v>1</v>
@@ -83322,7 +83322,7 @@
         <v>85</v>
       </c>
       <c r="DD179" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DE179" t="n">
         <v>1</v>
@@ -83355,7 +83355,7 @@
         <v>2.71</v>
       </c>
       <c r="DO179" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -83789,7 +83789,7 @@
         <v>1.5</v>
       </c>
       <c r="DE180" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DF180" t="n">
         <v>1.5</v>
@@ -83819,7 +83819,7 @@
         <v>3.02</v>
       </c>
       <c r="DO180" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP180" t="b">
         <v>1</v>
@@ -84234,7 +84234,7 @@
         <v>87</v>
       </c>
       <c r="DD181" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DE181" t="n">
         <v>1.33</v>
@@ -84267,7 +84267,7 @@
         <v>3.01</v>
       </c>
       <c r="DO181" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP181" t="b">
         <v>1</v>
@@ -84739,7 +84739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO182" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -85645,7 +85645,7 @@
         <v>2.83</v>
       </c>
       <c r="DE184" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF184" t="n">
         <v>2.8</v>
@@ -85675,7 +85675,7 @@
         <v>3.71</v>
       </c>
       <c r="DO184" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP184" t="b">
         <v>1</v>
@@ -86619,7 +86619,7 @@
         <v>3.37</v>
       </c>
       <c r="DO186" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP186" t="b">
         <v>1</v>
@@ -87075,7 +87075,7 @@
         <v>2.78</v>
       </c>
       <c r="DO187" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP187" t="b">
         <v>1</v>
@@ -87531,7 +87531,7 @@
         <v>2.76</v>
       </c>
       <c r="DO188" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP188" t="b">
         <v>1</v>
@@ -88459,7 +88459,7 @@
         <v>3.51</v>
       </c>
       <c r="DO190" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP190" t="b">
         <v>1</v>
@@ -88873,7 +88873,7 @@
         <v>2.83</v>
       </c>
       <c r="DE191" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF191" t="n">
         <v>2.82</v>
@@ -88903,7 +88903,7 @@
         <v>2.93</v>
       </c>
       <c r="DO191" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP191" t="b">
         <v>1</v>
@@ -89375,7 +89375,7 @@
         <v>2.89</v>
       </c>
       <c r="DO192" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP192" t="b">
         <v>1</v>
@@ -89839,7 +89839,7 @@
         <v>2.48</v>
       </c>
       <c r="DO193" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP193" t="b">
         <v>1</v>
@@ -90497,10 +90497,10 @@
         <v>8</v>
       </c>
       <c r="Y195" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z195" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
@@ -91798,6 +91798,1846 @@
           <t>3.26</t>
         </is>
       </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>25</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>46068.52083333334</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2</v>
+      </c>
+      <c r="I198" t="n">
+        <v>3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" t="n">
+        <v>8</v>
+      </c>
+      <c r="L198" t="n">
+        <v>10</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>3</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>5</v>
+      </c>
+      <c r="R198" t="n">
+        <v>3</v>
+      </c>
+      <c r="S198" t="n">
+        <v>13</v>
+      </c>
+      <c r="T198" t="n">
+        <v>7</v>
+      </c>
+      <c r="U198" t="n">
+        <v>18</v>
+      </c>
+      <c r="V198" t="n">
+        <v>10</v>
+      </c>
+      <c r="W198" t="n">
+        <v>9</v>
+      </c>
+      <c r="X198" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV198" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW198" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX198" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY198" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ198" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CA198" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB198" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP198" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR198" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS198" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU198" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV198" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX198" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY198" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ198" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA198" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB198" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC198" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD198" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DE198" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DF198" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DG198" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DH198" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI198" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DJ198" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK198" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL198" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM198" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DN198" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DO198" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP198" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ198" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR198" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS198" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT198" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU198" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV198" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW198" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DX198" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DY198" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="DZ198" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="EA198" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="EB198" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC198" t="inlineStr"/>
+      <c r="ED198" t="inlineStr"/>
+      <c r="EE198" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EF198" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EG198" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH198" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EI198" t="inlineStr"/>
+      <c r="EJ198" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EK198" t="inlineStr"/>
+      <c r="EL198" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>25</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>46068.625</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" t="n">
+        <v>2</v>
+      </c>
+      <c r="J199" t="n">
+        <v>4</v>
+      </c>
+      <c r="K199" t="n">
+        <v>2</v>
+      </c>
+      <c r="L199" t="n">
+        <v>6</v>
+      </c>
+      <c r="M199" t="n">
+        <v>2</v>
+      </c>
+      <c r="N199" t="n">
+        <v>4</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>1</v>
+      </c>
+      <c r="R199" t="n">
+        <v>8</v>
+      </c>
+      <c r="S199" t="n">
+        <v>4</v>
+      </c>
+      <c r="T199" t="n">
+        <v>4</v>
+      </c>
+      <c r="U199" t="n">
+        <v>5</v>
+      </c>
+      <c r="V199" t="n">
+        <v>12</v>
+      </c>
+      <c r="W199" t="n">
+        <v>16</v>
+      </c>
+      <c r="X199" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>534</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV199" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW199" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX199" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY199" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ199" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CA199" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR199" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS199" t="n">
+        <v>41</v>
+      </c>
+      <c r="CT199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU199" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV199" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX199" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY199" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ199" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA199" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB199" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC199" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD199" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE199" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG199" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI199" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ199" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK199" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM199" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN199" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DO199" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP199" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ199" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR199" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS199" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT199" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU199" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV199" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW199" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DX199" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DY199" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="DZ199" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EA199" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="EB199" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EC199" t="inlineStr"/>
+      <c r="ED199" t="inlineStr"/>
+      <c r="EE199" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EF199" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EG199" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EH199" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI199" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EJ199" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK199" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL199" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>25</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>46068.73958333334</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>8</v>
+      </c>
+      <c r="K200" t="n">
+        <v>4</v>
+      </c>
+      <c r="L200" t="n">
+        <v>12</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>5</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>5</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>14</v>
+      </c>
+      <c r="T200" t="n">
+        <v>7</v>
+      </c>
+      <c r="U200" t="n">
+        <v>19</v>
+      </c>
+      <c r="V200" t="n">
+        <v>7</v>
+      </c>
+      <c r="W200" t="n">
+        <v>15</v>
+      </c>
+      <c r="X200" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV200" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW200" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX200" t="n">
+        <v>125</v>
+      </c>
+      <c r="BY200" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ200" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA200" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB200" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM200" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR200" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS200" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU200" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV200" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX200" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY200" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ200" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA200" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB200" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC200" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD200" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DE200" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DF200" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG200" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI200" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ200" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK200" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL200" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM200" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN200" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO200" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV200" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW200" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="DX200" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY200" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="DZ200" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EA200" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EB200" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="EC200" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="ED200" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EE200" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EF200" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EG200" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH200" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI200" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EJ200" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EK200" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL200" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>25</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>46068.77083333334</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3</v>
+      </c>
+      <c r="H201" t="n">
+        <v>2</v>
+      </c>
+      <c r="I201" t="n">
+        <v>5</v>
+      </c>
+      <c r="J201" t="n">
+        <v>7</v>
+      </c>
+      <c r="K201" t="n">
+        <v>6</v>
+      </c>
+      <c r="L201" t="n">
+        <v>13</v>
+      </c>
+      <c r="M201" t="n">
+        <v>3</v>
+      </c>
+      <c r="N201" t="n">
+        <v>3</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>7</v>
+      </c>
+      <c r="R201" t="n">
+        <v>3</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="n">
+        <v>9</v>
+      </c>
+      <c r="U201" t="n">
+        <v>17</v>
+      </c>
+      <c r="V201" t="n">
+        <v>12</v>
+      </c>
+      <c r="W201" t="n">
+        <v>11</v>
+      </c>
+      <c r="X201" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT201" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV201" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW201" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX201" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY201" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ201" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CA201" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB201" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CC201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR201" t="n">
+        <v>36</v>
+      </c>
+      <c r="CS201" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU201" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV201" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX201" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY201" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ201" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA201" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB201" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC201" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD201" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DE201" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DF201" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DG201" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH201" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI201" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ201" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK201" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL201" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DM201" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN201" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DO201" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU201" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV201" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW201" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DX201" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DY201" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="DZ201" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EA201" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EB201" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="EC201" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="ED201" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EE201" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF201" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG201" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EH201" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EI201" t="inlineStr"/>
+      <c r="EJ201" t="inlineStr"/>
+      <c r="EK201" t="inlineStr"/>
+      <c r="EL201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -92337,10 +92337,10 @@
         <v>14</v>
       </c>
       <c r="Y199" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z199" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA199" t="inlineStr">
         <is>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL201" headerRowCount="1">
-  <autoFilter ref="A1:EL201"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL202" headerRowCount="1">
+  <autoFilter ref="A1:EL202"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL201"/>
+  <dimension ref="A1:EL202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2241,7 +2241,7 @@
         <v>0.58</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE13" t="n">
         <v>0.85</v>
@@ -9669,7 +9669,7 @@
         <v>2.33</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10586,7 +10586,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE21" t="n">
         <v>1.46</v>
@@ -16609,7 +16609,7 @@
         <v>1.23</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -20798,7 +20798,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE43" t="n">
         <v>1.69</v>
@@ -26754,7 +26754,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE56" t="n">
         <v>0.77</v>
@@ -30005,7 +30005,7 @@
         <v>1.38</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35054,7 +35054,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE74" t="n">
         <v>1.33</v>
@@ -36457,7 +36457,7 @@
         <v>1.38</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -43770,7 +43770,7 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE93" t="n">
         <v>1.25</v>
@@ -49281,7 +49281,7 @@
         <v>1.17</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -52478,7 +52478,7 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE112" t="n">
         <v>1.46</v>
@@ -53833,7 +53833,7 @@
         <v>2.83</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -57953,7 +57953,7 @@
         <v>1.5</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF124" t="n">
         <v>1.43</v>
@@ -60254,7 +60254,7 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE129" t="n">
         <v>1.92</v>
@@ -66258,7 +66258,7 @@
         <v>69</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE142" t="n">
         <v>1</v>
@@ -71333,7 +71333,7 @@
         <v>1.08</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF153" t="n">
         <v>1</v>
@@ -75050,7 +75050,7 @@
         <v>78</v>
       </c>
       <c r="DD161" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE161" t="n">
         <v>1.08</v>
@@ -76429,7 +76429,7 @@
         <v>1.42</v>
       </c>
       <c r="DE164" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF164" t="n">
         <v>1.7</v>
@@ -77338,7 +77338,7 @@
         <v>68</v>
       </c>
       <c r="DD166" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE166" t="n">
         <v>1</v>
@@ -81453,7 +81453,7 @@
         <v>1.33</v>
       </c>
       <c r="DE175" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF175" t="n">
         <v>1.2</v>
@@ -87501,7 +87501,7 @@
         <v>1.31</v>
       </c>
       <c r="DE188" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF188" t="n">
         <v>1.55</v>
@@ -87954,7 +87954,7 @@
         <v>69</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DE189" t="n">
         <v>1.17</v>
@@ -93638,6 +93638,442 @@
       <c r="EJ201" t="inlineStr"/>
       <c r="EK201" t="inlineStr"/>
       <c r="EL201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>26</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>46073.82291666666</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>4</v>
+      </c>
+      <c r="K202" t="n">
+        <v>10</v>
+      </c>
+      <c r="L202" t="n">
+        <v>14</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>4</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>1</v>
+      </c>
+      <c r="R202" t="n">
+        <v>4</v>
+      </c>
+      <c r="S202" t="n">
+        <v>4</v>
+      </c>
+      <c r="T202" t="n">
+        <v>19</v>
+      </c>
+      <c r="U202" t="n">
+        <v>5</v>
+      </c>
+      <c r="V202" t="n">
+        <v>23</v>
+      </c>
+      <c r="W202" t="n">
+        <v>7</v>
+      </c>
+      <c r="X202" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>2567</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV202" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW202" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX202" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY202" t="n">
+        <v>132</v>
+      </c>
+      <c r="BZ202" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA202" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CB202" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CC202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR202" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS202" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU202" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV202" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX202" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY202" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ202" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA202" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB202" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC202" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD202" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DE202" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DF202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG202" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DH202" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI202" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DJ202" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK202" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL202" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM202" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN202" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO202" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW202" t="inlineStr"/>
+      <c r="DX202" t="inlineStr"/>
+      <c r="DY202" t="inlineStr"/>
+      <c r="DZ202" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EA202" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EB202" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EC202" t="inlineStr"/>
+      <c r="ED202" t="inlineStr"/>
+      <c r="EE202" t="inlineStr"/>
+      <c r="EF202" t="inlineStr"/>
+      <c r="EG202" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EH202" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI202" t="inlineStr"/>
+      <c r="EJ202" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK202" t="inlineStr"/>
+      <c r="EL202" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -96443,13 +96443,13 @@
         <v>5</v>
       </c>
       <c r="S208" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T208" t="n">
         <v>7</v>
       </c>
       <c r="U208" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V208" t="n">
         <v>12</v>
@@ -96624,13 +96624,13 @@
         <v>78</v>
       </c>
       <c r="BZ208" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="CA208" t="n">
         <v>1.36</v>
       </c>
       <c r="CB208" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="CC208" t="n">
         <v>0</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL209" headerRowCount="1">
-  <autoFilter ref="A1:EL209"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL213" headerRowCount="1">
+  <autoFilter ref="A1:EL213"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL209"/>
+  <dimension ref="A1:EL213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.46</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE6" t="n">
         <v>1.08</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>1.69</v>
@@ -5933,7 +5933,7 @@
         <v>1.54</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE12" t="n">
         <v>0.77</v>
@@ -6861,7 +6861,7 @@
         <v>1.54</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -8269,7 +8269,7 @@
         <v>2.85</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
         <v>1.31</v>
       </c>
       <c r="DE17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -11530,10 +11530,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11994,7 +11994,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE24" t="n">
         <v>1.46</v>
@@ -12466,10 +12466,10 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13838,7 +13838,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE28" t="n">
         <v>1.23</v>
@@ -15209,7 +15209,7 @@
         <v>2.15</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16606,7 +16606,7 @@
         <v>25</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE34" t="n">
         <v>1.54</v>
@@ -17065,7 +17065,7 @@
         <v>1.38</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17095,7 +17095,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17526,7 +17526,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE36" t="n">
         <v>1.62</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18465,7 +18465,7 @@
         <v>0.54</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -18937,7 +18937,7 @@
         <v>0.54</v>
       </c>
       <c r="DE39" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -19398,10 +19398,10 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22185,7 +22185,7 @@
         <v>1.23</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE47" t="n">
         <v>1.62</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23097,7 +23097,7 @@
         <v>1.38</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23127,7 +23127,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24462,7 +24462,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE51" t="n">
         <v>1.23</v>
@@ -25390,7 +25390,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE53" t="n">
         <v>1.46</v>
@@ -27229,7 +27229,7 @@
         <v>1.08</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27701,7 +27701,7 @@
         <v>1.31</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -28170,7 +28170,7 @@
         <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE59" t="n">
         <v>0.92</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29549,7 +29549,7 @@
         <v>2.38</v>
       </c>
       <c r="DE62" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -30002,7 +30002,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE63" t="n">
         <v>1.54</v>
@@ -30458,7 +30458,7 @@
         <v>59</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
         <v>1.23</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32294,7 +32294,7 @@
         <v>50</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE68" t="n">
         <v>1.69</v>
@@ -34585,7 +34585,7 @@
         <v>0.54</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -35518,10 +35518,10 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE75" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35985,7 +35985,7 @@
         <v>1.08</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36454,7 +36454,7 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE77" t="n">
         <v>1.54</v>
@@ -36918,7 +36918,7 @@
         <v>58</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE78" t="n">
         <v>1.38</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38289,7 +38289,7 @@
         <v>1.54</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41942,7 +41942,7 @@
         <v>60</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE89" t="n">
         <v>0.92</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43306,10 +43306,10 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44226,7 +44226,7 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE94" t="n">
         <v>1.69</v>
@@ -44693,7 +44693,7 @@
         <v>0.54</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -45149,7 +45149,7 @@
         <v>1.23</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -45621,7 +45621,7 @@
         <v>2.85</v>
       </c>
       <c r="DE97" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -46062,7 +46062,7 @@
         <v>84</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE98" t="n">
         <v>1.23</v>
@@ -47454,7 +47454,7 @@
         <v>50</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE101" t="n">
         <v>1.62</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49729,7 +49729,7 @@
         <v>0.54</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -50201,7 +50201,7 @@
         <v>0.54</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -51094,10 +51094,10 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51566,7 +51566,7 @@
         <v>50</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE110" t="n">
         <v>1.69</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52926,7 +52926,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE113" t="n">
         <v>1.46</v>
@@ -53366,10 +53366,10 @@
         <v>79</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -55662,7 +55662,7 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE119" t="n">
         <v>0.77</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56561,7 +56561,7 @@
         <v>1.08</v>
       </c>
       <c r="DE121" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -56591,7 +56591,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57030,7 +57030,7 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE122" t="n">
         <v>1.38</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58401,7 +58401,7 @@
         <v>1.31</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -59321,7 +59321,7 @@
         <v>1.23</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF127" t="n">
         <v>1.14</v>
@@ -59782,7 +59782,7 @@
         <v>50</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE128" t="n">
         <v>1.46</v>
@@ -60257,7 +60257,7 @@
         <v>1.54</v>
       </c>
       <c r="DE129" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -62554,7 +62554,7 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE134" t="n">
         <v>1.23</v>
@@ -63450,7 +63450,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE136" t="n">
         <v>1.46</v>
@@ -63925,7 +63925,7 @@
         <v>1.08</v>
       </c>
       <c r="DE137" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -63955,7 +63955,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64394,10 +64394,10 @@
         <v>63</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF138" t="n">
         <v>1.5</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -65333,7 +65333,7 @@
         <v>1.38</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65786,10 +65786,10 @@
         <v>66</v>
       </c>
       <c r="DD141" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE141" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF141" t="n">
         <v>2.22</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -69029,7 +69029,7 @@
         <v>1.54</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF148" t="n">
         <v>1.56</v>
@@ -69493,7 +69493,7 @@
         <v>2.85</v>
       </c>
       <c r="DE149" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF149" t="n">
         <v>2.75</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70858,7 +70858,7 @@
         <v>64</v>
       </c>
       <c r="DD152" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE152" t="n">
         <v>1.15</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -72722,10 +72722,10 @@
         <v>62</v>
       </c>
       <c r="DD156" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE156" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF156" t="n">
         <v>1.33</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73194,7 +73194,7 @@
         <v>70</v>
       </c>
       <c r="DD157" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE157" t="n">
         <v>1.23</v>
@@ -73666,10 +73666,10 @@
         <v>80</v>
       </c>
       <c r="DD158" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE158" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF158" t="n">
         <v>1.5</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74125,7 +74125,7 @@
         <v>1.08</v>
       </c>
       <c r="DE159" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF159" t="n">
         <v>1.33</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -74578,7 +74578,7 @@
         <v>67</v>
       </c>
       <c r="DD160" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE160" t="n">
         <v>0.77</v>
@@ -75509,7 +75509,7 @@
         <v>2.38</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF162" t="n">
         <v>2.44</v>
@@ -78725,7 +78725,7 @@
         <v>2.15</v>
       </c>
       <c r="DE169" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF169" t="n">
         <v>2.2</v>
@@ -78755,7 +78755,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79162,7 +79162,7 @@
         <v>65</v>
       </c>
       <c r="DD170" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE170" t="n">
         <v>1.23</v>
@@ -79621,7 +79621,7 @@
         <v>1.08</v>
       </c>
       <c r="DE171" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF171" t="n">
         <v>1.3</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80077,7 +80077,7 @@
         <v>2.38</v>
       </c>
       <c r="DE172" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF172" t="n">
         <v>2.2</v>
@@ -80978,7 +80978,7 @@
         <v>86</v>
       </c>
       <c r="DD174" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE174" t="n">
         <v>1.23</v>
@@ -81914,7 +81914,7 @@
         <v>68</v>
       </c>
       <c r="DD176" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE176" t="n">
         <v>0.77</v>
@@ -82386,7 +82386,7 @@
         <v>70</v>
       </c>
       <c r="DD177" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE177" t="n">
         <v>1.08</v>
@@ -84706,7 +84706,7 @@
         <v>62</v>
       </c>
       <c r="DD182" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE182" t="n">
         <v>1.15</v>
@@ -84739,7 +84739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO182" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -86147,7 +86147,7 @@
         <v>2.75</v>
       </c>
       <c r="DO185" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -86589,7 +86589,7 @@
         <v>1.54</v>
       </c>
       <c r="DE186" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF186" t="n">
         <v>1.55</v>
@@ -87957,7 +87957,7 @@
         <v>1.54</v>
       </c>
       <c r="DE189" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF189" t="n">
         <v>1.82</v>
@@ -88873,7 +88873,7 @@
         <v>2.85</v>
       </c>
       <c r="DE191" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF191" t="n">
         <v>2.82</v>
@@ -89806,7 +89806,7 @@
         <v>69</v>
       </c>
       <c r="DD193" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE193" t="n">
         <v>0.92</v>
@@ -89839,7 +89839,7 @@
         <v>2.48</v>
       </c>
       <c r="DO193" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP193" t="b">
         <v>1</v>
@@ -90278,7 +90278,7 @@
         <v>75</v>
       </c>
       <c r="DD194" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE194" t="n">
         <v>1.46</v>
@@ -91662,7 +91662,7 @@
         <v>63</v>
       </c>
       <c r="DD197" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE197" t="n">
         <v>1.46</v>
@@ -92590,7 +92590,7 @@
         <v>83</v>
       </c>
       <c r="DD199" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE199" t="n">
         <v>1.08</v>
@@ -93054,10 +93054,10 @@
         <v>59</v>
       </c>
       <c r="DD200" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DE200" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF200" t="n">
         <v>2</v>
@@ -93087,7 +93087,7 @@
         <v>2.89</v>
       </c>
       <c r="DO200" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP200" t="b">
         <v>0</v>
@@ -93521,7 +93521,7 @@
         <v>2.15</v>
       </c>
       <c r="DE201" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF201" t="n">
         <v>2.08</v>
@@ -93551,7 +93551,7 @@
         <v>2.94</v>
       </c>
       <c r="DO201" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP201" t="b">
         <v>1</v>
@@ -94405,7 +94405,7 @@
         <v>0.54</v>
       </c>
       <c r="DE203" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF203" t="n">
         <v>0.58</v>
@@ -94869,7 +94869,7 @@
         <v>2.38</v>
       </c>
       <c r="DE204" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF204" t="n">
         <v>2.33</v>
@@ -96275,7 +96275,7 @@
         <v>2.5</v>
       </c>
       <c r="DO207" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP207" t="b">
         <v>1</v>
@@ -96747,7 +96747,7 @@
         <v>2.94</v>
       </c>
       <c r="DO208" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP208" t="b">
         <v>1</v>
@@ -97312,6 +97312,1846 @@
       <c r="EL209" t="inlineStr">
         <is>
           <t>1.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>27</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>46080.82291666666</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="n">
+        <v>2</v>
+      </c>
+      <c r="J210" t="n">
+        <v>4</v>
+      </c>
+      <c r="K210" t="n">
+        <v>3</v>
+      </c>
+      <c r="L210" t="n">
+        <v>7</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>3</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>2</v>
+      </c>
+      <c r="R210" t="n">
+        <v>3</v>
+      </c>
+      <c r="S210" t="n">
+        <v>7</v>
+      </c>
+      <c r="T210" t="n">
+        <v>9</v>
+      </c>
+      <c r="U210" t="n">
+        <v>9</v>
+      </c>
+      <c r="V210" t="n">
+        <v>12</v>
+      </c>
+      <c r="W210" t="n">
+        <v>12</v>
+      </c>
+      <c r="X210" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>Stade Maurice Dufrasne</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>Rue de la Centrale 2, Sclessin, Luik</t>
+        </is>
+      </c>
+      <c r="AC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR210" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT210" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV210" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW210" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX210" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY210" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA210" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB210" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP210" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR210" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS210" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU210" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV210" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW210" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX210" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY210" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ210" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA210" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB210" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC210" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD210" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DE210" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF210" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DG210" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DH210" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI210" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DJ210" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK210" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL210" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM210" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DN210" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DO210" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP210" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ210" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR210" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS210" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT210" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU210" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV210" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW210" t="inlineStr"/>
+      <c r="DX210" t="inlineStr"/>
+      <c r="DY210" t="inlineStr"/>
+      <c r="DZ210" t="inlineStr"/>
+      <c r="EA210" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EB210" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EC210" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED210" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EE210" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EF210" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EG210" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EH210" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI210" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ210" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK210" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EL210" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>27</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="n">
+        <v>3</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>8</v>
+      </c>
+      <c r="L211" t="n">
+        <v>9</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>3</v>
+      </c>
+      <c r="R211" t="n">
+        <v>5</v>
+      </c>
+      <c r="S211" t="n">
+        <v>2</v>
+      </c>
+      <c r="T211" t="n">
+        <v>11</v>
+      </c>
+      <c r="U211" t="n">
+        <v>5</v>
+      </c>
+      <c r="V211" t="n">
+        <v>16</v>
+      </c>
+      <c r="W211" t="n">
+        <v>11</v>
+      </c>
+      <c r="X211" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT211" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV211" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW211" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX211" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY211" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ211" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CA211" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB211" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR211" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS211" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU211" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV211" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX211" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY211" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ211" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA211" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB211" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC211" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE211" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DF211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG211" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DH211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI211" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ211" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK211" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL211" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM211" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN211" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO211" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP211" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ211" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR211" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS211" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT211" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU211" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV211" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW211" t="inlineStr"/>
+      <c r="DX211" t="inlineStr"/>
+      <c r="DY211" t="inlineStr"/>
+      <c r="DZ211" t="inlineStr"/>
+      <c r="EA211" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EB211" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC211" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="ED211" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EE211" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EF211" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EG211" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EH211" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EI211" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ211" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EK211" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EL211" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>27</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>46081.71875</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="n">
+        <v>4</v>
+      </c>
+      <c r="L212" t="n">
+        <v>7</v>
+      </c>
+      <c r="M212" t="n">
+        <v>2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>6</v>
+      </c>
+      <c r="R212" t="n">
+        <v>3</v>
+      </c>
+      <c r="S212" t="n">
+        <v>6</v>
+      </c>
+      <c r="T212" t="n">
+        <v>7</v>
+      </c>
+      <c r="U212" t="n">
+        <v>12</v>
+      </c>
+      <c r="V212" t="n">
+        <v>10</v>
+      </c>
+      <c r="W212" t="n">
+        <v>11</v>
+      </c>
+      <c r="X212" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>1048</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV212" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW212" t="n">
+        <v>75</v>
+      </c>
+      <c r="BX212" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY212" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ212" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CA212" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB212" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO212" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR212" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS212" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU212" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV212" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX212" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY212" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ212" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA212" t="n">
+        <v>96</v>
+      </c>
+      <c r="DB212" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC212" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE212" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF212" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG212" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH212" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI212" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ212" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK212" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL212" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM212" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN212" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO212" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP212" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV212" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW212" t="inlineStr"/>
+      <c r="DX212" t="inlineStr"/>
+      <c r="DY212" t="inlineStr"/>
+      <c r="DZ212" t="inlineStr"/>
+      <c r="EA212" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EB212" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EC212" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="ED212" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EE212" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EF212" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EG212" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH212" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EI212" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EJ212" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EK212" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EL212" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>27</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>46081.82291666666</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>6</v>
+      </c>
+      <c r="J213" t="n">
+        <v>9</v>
+      </c>
+      <c r="K213" t="n">
+        <v>7</v>
+      </c>
+      <c r="L213" t="n">
+        <v>16</v>
+      </c>
+      <c r="M213" t="n">
+        <v>4</v>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>6</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2</v>
+      </c>
+      <c r="S213" t="n">
+        <v>8</v>
+      </c>
+      <c r="T213" t="n">
+        <v>5</v>
+      </c>
+      <c r="U213" t="n">
+        <v>14</v>
+      </c>
+      <c r="V213" t="n">
+        <v>7</v>
+      </c>
+      <c r="W213" t="n">
+        <v>16</v>
+      </c>
+      <c r="X213" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>Stade Constant Vanden Stock</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>Avenue Théo Verbeeck 2, Brussel</t>
+        </is>
+      </c>
+      <c r="AC213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>61</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR213" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT213" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV213" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW213" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX213" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY213" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ213" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CA213" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB213" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CC213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP213" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR213" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS213" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU213" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV213" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX213" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY213" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ213" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA213" t="n">
+        <v>58</v>
+      </c>
+      <c r="DB213" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC213" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD213" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE213" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF213" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG213" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH213" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DI213" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ213" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK213" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL213" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM213" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN213" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DO213" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV213" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW213" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="DX213" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DY213" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DZ213" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EA213" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB213" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EC213" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="ED213" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EE213" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EF213" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="EG213" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EH213" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EI213" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ213" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EK213" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EL213" t="inlineStr">
+        <is>
+          <t>1.45</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL213" headerRowCount="1">
-  <autoFilter ref="A1:EL213"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL217" headerRowCount="1">
+  <autoFilter ref="A1:EL217"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL213"/>
+  <dimension ref="A1:EL217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5021,7 +5021,7 @@
         <v>2.15</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         <v>1.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
         <v>0.79</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6389,7 +6389,7 @@
         <v>1.21</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE14" t="n">
         <v>0.92</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7794,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE15" t="n">
         <v>1.15</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE17" t="n">
         <v>1.86</v>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9197,7 +9197,7 @@
         <v>2.15</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9227,7 +9227,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10130,7 +10130,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE20" t="n">
         <v>1.62</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10589,7 +10589,7 @@
         <v>1.54</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13389,7 +13389,7 @@
         <v>1.38</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13841,7 +13841,7 @@
         <v>1.5</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15678,7 +15678,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE32" t="n">
         <v>0.92</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16150,7 +16150,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE33" t="n">
         <v>1.08</v>
@@ -16183,7 +16183,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18001,7 +18001,7 @@
         <v>1.08</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -18495,7 +18495,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18934,7 +18934,7 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE39" t="n">
         <v>1.86</v>
@@ -18967,7 +18967,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19870,7 +19870,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE41" t="n">
         <v>0.92</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20326,10 +20326,10 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20359,7 +20359,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20801,7 +20801,7 @@
         <v>1.54</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22182,7 +22182,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE46" t="n">
         <v>0.79</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23545,7 +23545,7 @@
         <v>0.54</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF49" t="n">
         <v>0.33</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24017,7 +24017,7 @@
         <v>1.08</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24465,7 +24465,7 @@
         <v>1.5</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE52" t="n">
         <v>1.23</v>
@@ -24951,7 +24951,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25879,7 +25879,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26302,7 +26302,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE55" t="n">
         <v>1.23</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26757,7 +26757,7 @@
         <v>1.54</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -26787,7 +26787,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27698,7 +27698,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE58" t="n">
         <v>0.79</v>
@@ -27731,7 +27731,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28626,10 +28626,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29082,7 +29082,7 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE61" t="n">
         <v>1.38</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30461,7 +30461,7 @@
         <v>2</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF64" t="n">
         <v>1.25</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32297,7 +32297,7 @@
         <v>1.21</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33670,10 +33670,10 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34126,7 +34126,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE72" t="n">
         <v>1.62</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35087,7 +35087,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37374,10 +37374,10 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37817,7 +37817,7 @@
         <v>2.38</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF80" t="n">
         <v>2.5</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38286,7 +38286,7 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE81" t="n">
         <v>1</v>
@@ -38319,7 +38319,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39201,7 +39201,7 @@
         <v>1.08</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40118,7 +40118,7 @@
         <v>90</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE85" t="n">
         <v>1.46</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41489,7 +41489,7 @@
         <v>1.38</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -41519,7 +41519,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42386,7 +42386,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE90" t="n">
         <v>1.15</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42858,10 +42858,10 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -42891,7 +42891,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44229,7 +44229,7 @@
         <v>1.5</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44690,7 +44690,7 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE95" t="n">
         <v>0.79</v>
@@ -44723,7 +44723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45146,7 +45146,7 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE96" t="n">
         <v>0.86</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46537,7 +46537,7 @@
         <v>1.38</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF99" t="n">
         <v>1.67</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46993,7 +46993,7 @@
         <v>2.38</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47910,7 +47910,7 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE102" t="n">
         <v>1.46</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48361,7 +48361,7 @@
         <v>1.08</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF103" t="n">
         <v>0.83</v>
@@ -48391,7 +48391,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49759,7 +49759,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50198,7 +50198,7 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE107" t="n">
         <v>1</v>
@@ -50231,7 +50231,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50654,7 +50654,7 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE108" t="n">
         <v>1.08</v>
@@ -50687,7 +50687,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51569,7 +51569,7 @@
         <v>2</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52929,7 +52929,7 @@
         <v>1.5</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54286,10 +54286,10 @@
         <v>79</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF116" t="n">
         <v>1.43</v>
@@ -54319,7 +54319,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55206,7 +55206,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE118" t="n">
         <v>1.62</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55665,7 +55665,7 @@
         <v>1.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -57527,7 +57527,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57983,7 +57983,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58398,7 +58398,7 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE125" t="n">
         <v>0.86</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59318,7 +59318,7 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59785,7 +59785,7 @@
         <v>2</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF128" t="n">
         <v>2.13</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60287,7 +60287,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60721,7 +60721,7 @@
         <v>1.08</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF130" t="n">
         <v>1.5</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61190,7 +61190,7 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE131" t="n">
         <v>1.38</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61653,7 +61653,7 @@
         <v>2.85</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF132" t="n">
         <v>3</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62101,7 +62101,7 @@
         <v>2.15</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63010,7 +63010,7 @@
         <v>59</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE135" t="n">
         <v>1.15</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -64866,7 +64866,7 @@
         <v>88</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE139" t="n">
         <v>1.62</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66693,7 +66693,7 @@
         <v>0.54</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF143" t="n">
         <v>0.5</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67154,10 +67154,10 @@
         <v>66</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF144" t="n">
         <v>1.5</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67626,7 +67626,7 @@
         <v>82</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE145" t="n">
         <v>1.08</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68090,7 +68090,7 @@
         <v>84</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE146" t="n">
         <v>1.46</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69026,7 +69026,7 @@
         <v>67</v>
       </c>
       <c r="DD148" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE148" t="n">
         <v>0.86</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69949,7 +69949,7 @@
         <v>2.38</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF150" t="n">
         <v>2.38</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -71363,7 +71363,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71786,10 +71786,10 @@
         <v>80</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF154" t="n">
         <v>1.33</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72250,10 +72250,10 @@
         <v>80</v>
       </c>
       <c r="DD155" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE155" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF155" t="n">
         <v>0.6</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -74581,7 +74581,7 @@
         <v>1.5</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF160" t="n">
         <v>1.44</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75083,7 +75083,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76426,7 +76426,7 @@
         <v>74</v>
       </c>
       <c r="DD164" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE164" t="n">
         <v>1.54</v>
@@ -76459,7 +76459,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78258,7 +78258,7 @@
         <v>70</v>
       </c>
       <c r="DD168" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE168" t="n">
         <v>1.38</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -79165,7 +79165,7 @@
         <v>1.21</v>
       </c>
       <c r="DE170" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF170" t="n">
         <v>1.2</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80525,7 +80525,7 @@
         <v>1.08</v>
       </c>
       <c r="DE173" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF173" t="n">
         <v>0.9</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81450,7 +81450,7 @@
         <v>80</v>
       </c>
       <c r="DD175" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE175" t="n">
         <v>1.54</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81917,7 +81917,7 @@
         <v>2</v>
       </c>
       <c r="DE176" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF176" t="n">
         <v>2.09</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82853,7 +82853,7 @@
         <v>1.08</v>
       </c>
       <c r="DE178" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF178" t="n">
         <v>1.18</v>
@@ -82883,7 +82883,7 @@
         <v>2.66</v>
       </c>
       <c r="DO178" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP178" t="b">
         <v>1</v>
@@ -83322,7 +83322,7 @@
         <v>85</v>
       </c>
       <c r="DD179" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE179" t="n">
         <v>0.92</v>
@@ -83355,7 +83355,7 @@
         <v>2.71</v>
       </c>
       <c r="DO179" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -83819,7 +83819,7 @@
         <v>3.02</v>
       </c>
       <c r="DO180" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP180" t="b">
         <v>1</v>
@@ -84267,7 +84267,7 @@
         <v>3.01</v>
       </c>
       <c r="DO181" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP181" t="b">
         <v>1</v>
@@ -85203,7 +85203,7 @@
         <v>2.77</v>
       </c>
       <c r="DO183" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP183" t="b">
         <v>1</v>
@@ -85645,7 +85645,7 @@
         <v>2.85</v>
       </c>
       <c r="DE184" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF184" t="n">
         <v>2.8</v>
@@ -85675,7 +85675,7 @@
         <v>3.71</v>
       </c>
       <c r="DO184" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP184" t="b">
         <v>1</v>
@@ -86586,7 +86586,7 @@
         <v>73</v>
       </c>
       <c r="DD186" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE186" t="n">
         <v>1.86</v>
@@ -86619,7 +86619,7 @@
         <v>3.37</v>
       </c>
       <c r="DO186" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP186" t="b">
         <v>1</v>
@@ -87045,7 +87045,7 @@
         <v>1.38</v>
       </c>
       <c r="DE187" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF187" t="n">
         <v>1.36</v>
@@ -87075,7 +87075,7 @@
         <v>2.78</v>
       </c>
       <c r="DO187" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP187" t="b">
         <v>1</v>
@@ -87498,7 +87498,7 @@
         <v>78</v>
       </c>
       <c r="DD188" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE188" t="n">
         <v>1.54</v>
@@ -87531,7 +87531,7 @@
         <v>2.76</v>
       </c>
       <c r="DO188" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP188" t="b">
         <v>1</v>
@@ -87987,7 +87987,7 @@
         <v>3.03</v>
       </c>
       <c r="DO189" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -88426,7 +88426,7 @@
         <v>78</v>
       </c>
       <c r="DD190" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE190" t="n">
         <v>1.15</v>
@@ -88459,7 +88459,7 @@
         <v>3.51</v>
       </c>
       <c r="DO190" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP190" t="b">
         <v>1</v>
@@ -88903,7 +88903,7 @@
         <v>2.93</v>
       </c>
       <c r="DO191" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP191" t="b">
         <v>1</v>
@@ -89375,7 +89375,7 @@
         <v>2.89</v>
       </c>
       <c r="DO192" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP192" t="b">
         <v>1</v>
@@ -90311,7 +90311,7 @@
         <v>2.87</v>
       </c>
       <c r="DO194" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP194" t="b">
         <v>1</v>
@@ -90753,7 +90753,7 @@
         <v>1.08</v>
       </c>
       <c r="DE195" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DF195" t="n">
         <v>0.92</v>
@@ -90783,7 +90783,7 @@
         <v>2.81</v>
       </c>
       <c r="DO195" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP195" t="b">
         <v>1</v>
@@ -91206,10 +91206,10 @@
         <v>75</v>
       </c>
       <c r="DD196" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DE196" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DF196" t="n">
         <v>1.42</v>
@@ -91239,7 +91239,7 @@
         <v>2.88</v>
       </c>
       <c r="DO196" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP196" t="b">
         <v>1</v>
@@ -91665,7 +91665,7 @@
         <v>1.21</v>
       </c>
       <c r="DE197" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DF197" t="n">
         <v>1.25</v>
@@ -91695,7 +91695,7 @@
         <v>2.98</v>
       </c>
       <c r="DO197" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP197" t="b">
         <v>1</v>
@@ -92134,10 +92134,10 @@
         <v>88</v>
       </c>
       <c r="DD198" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE198" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF198" t="n">
         <v>0.58</v>
@@ -92167,7 +92167,7 @@
         <v>3.27</v>
       </c>
       <c r="DO198" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP198" t="b">
         <v>1</v>
@@ -92623,7 +92623,7 @@
         <v>3.07</v>
       </c>
       <c r="DO199" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP199" t="b">
         <v>1</v>
@@ -94007,7 +94007,7 @@
         <v>3.06</v>
       </c>
       <c r="DO202" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP202" t="b">
         <v>1</v>
@@ -94435,7 +94435,7 @@
         <v>2.78</v>
       </c>
       <c r="DO203" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP203" t="b">
         <v>1</v>
@@ -94899,7 +94899,7 @@
         <v>3.39</v>
       </c>
       <c r="DO204" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP204" t="b">
         <v>1</v>
@@ -95347,7 +95347,7 @@
         <v>3.12</v>
       </c>
       <c r="DO205" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP205" t="b">
         <v>1</v>
@@ -95786,7 +95786,7 @@
         <v>75</v>
       </c>
       <c r="DD206" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE206" t="n">
         <v>1.38</v>
@@ -95819,7 +95819,7 @@
         <v>2.97</v>
       </c>
       <c r="DO206" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP206" t="b">
         <v>1</v>
@@ -97178,7 +97178,7 @@
         <v>83</v>
       </c>
       <c r="DD209" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE209" t="n">
         <v>1.23</v>
@@ -97211,7 +97211,7 @@
         <v>3.1</v>
       </c>
       <c r="DO209" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP209" t="b">
         <v>1</v>
@@ -97853,10 +97853,10 @@
         <v>9</v>
       </c>
       <c r="Y211" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z211" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
@@ -98723,10 +98723,10 @@
         <v>9</v>
       </c>
       <c r="K213" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L213" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M213" t="n">
         <v>4</v>
@@ -98871,28 +98871,28 @@
         <v>-1</v>
       </c>
       <c r="BG213" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH213" t="n">
         <v>1</v>
       </c>
       <c r="BI213" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BJ213" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BK213" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL213" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BM213" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BN213" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO213" t="n">
         <v>0</v>
@@ -98967,10 +98967,10 @@
         <v>1</v>
       </c>
       <c r="CM213" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN213" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO213" t="n">
         <v>0</v>
@@ -99154,6 +99154,1846 @@
           <t>1.45</t>
         </is>
       </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>27</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="G214" t="n">
+        <v>3</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>3</v>
+      </c>
+      <c r="J214" t="n">
+        <v>7</v>
+      </c>
+      <c r="K214" t="n">
+        <v>8</v>
+      </c>
+      <c r="L214" t="n">
+        <v>15</v>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>6</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="n">
+        <v>12</v>
+      </c>
+      <c r="U214" t="n">
+        <v>16</v>
+      </c>
+      <c r="V214" t="n">
+        <v>14</v>
+      </c>
+      <c r="W214" t="n">
+        <v>9</v>
+      </c>
+      <c r="X214" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV214" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW214" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX214" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY214" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ214" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA214" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB214" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="CC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN214" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP214" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR214" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS214" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU214" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV214" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX214" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY214" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ214" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA214" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB214" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC214" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD214" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE214" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF214" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DG214" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DH214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI214" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ214" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK214" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DM214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="DO214" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP214" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ214" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR214" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS214" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT214" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU214" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV214" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW214" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="DX214" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="DY214" t="inlineStr"/>
+      <c r="DZ214" t="inlineStr"/>
+      <c r="EA214" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EB214" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EC214" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="ED214" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EE214" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="EF214" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EG214" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH214" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EI214" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ214" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK214" t="inlineStr"/>
+      <c r="EL214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>27</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>46082.625</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>5</v>
+      </c>
+      <c r="K215" t="n">
+        <v>3</v>
+      </c>
+      <c r="L215" t="n">
+        <v>8</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="n">
+        <v>1</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>4</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
+        <v>6</v>
+      </c>
+      <c r="U215" t="n">
+        <v>8</v>
+      </c>
+      <c r="V215" t="n">
+        <v>7</v>
+      </c>
+      <c r="W215" t="n">
+        <v>5</v>
+      </c>
+      <c r="X215" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV215" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW215" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX215" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY215" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ215" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA215" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB215" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP215" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR215" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS215" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU215" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV215" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX215" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY215" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ215" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA215" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB215" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC215" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE215" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF215" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DG215" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DH215" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI215" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DJ215" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK215" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL215" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DM215" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DN215" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO215" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV215" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW215" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="DX215" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="DY215" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DZ215" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EA215" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EB215" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC215" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="ED215" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="EE215" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EF215" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EG215" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EH215" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EI215" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ215" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EK215" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL215" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>27</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>46082.72916666666</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" t="n">
+        <v>3</v>
+      </c>
+      <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="n">
+        <v>4</v>
+      </c>
+      <c r="L216" t="n">
+        <v>6</v>
+      </c>
+      <c r="M216" t="n">
+        <v>4</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" t="n">
+        <v>1</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>3</v>
+      </c>
+      <c r="R216" t="n">
+        <v>5</v>
+      </c>
+      <c r="S216" t="n">
+        <v>6</v>
+      </c>
+      <c r="T216" t="n">
+        <v>10</v>
+      </c>
+      <c r="U216" t="n">
+        <v>9</v>
+      </c>
+      <c r="V216" t="n">
+        <v>15</v>
+      </c>
+      <c r="W216" t="n">
+        <v>8</v>
+      </c>
+      <c r="X216" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ216" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV216" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW216" t="n">
+        <v>81</v>
+      </c>
+      <c r="BX216" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY216" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ216" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CA216" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CB216" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM216" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR216" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS216" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU216" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV216" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX216" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY216" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ216" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA216" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB216" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC216" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD216" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DE216" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DF216" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DG216" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DH216" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI216" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DJ216" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK216" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL216" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM216" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DN216" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DO216" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP216" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ216" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR216" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS216" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT216" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU216" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV216" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW216" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="DX216" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="DY216" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="DZ216" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EA216" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EB216" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EC216" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="ED216" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EE216" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EF216" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG216" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH216" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EI216" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ216" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EK216" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EL216" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>27</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>46082.76041666666</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>9</v>
+      </c>
+      <c r="K217" t="n">
+        <v>4</v>
+      </c>
+      <c r="L217" t="n">
+        <v>13</v>
+      </c>
+      <c r="M217" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>8</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6</v>
+      </c>
+      <c r="S217" t="n">
+        <v>13</v>
+      </c>
+      <c r="T217" t="n">
+        <v>5</v>
+      </c>
+      <c r="U217" t="n">
+        <v>21</v>
+      </c>
+      <c r="V217" t="n">
+        <v>11</v>
+      </c>
+      <c r="W217" t="n">
+        <v>10</v>
+      </c>
+      <c r="X217" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS217" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU217" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV217" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW217" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX217" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY217" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ217" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CA217" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB217" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR217" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS217" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU217" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV217" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX217" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY217" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ217" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA217" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB217" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC217" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD217" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE217" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DF217" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DG217" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DH217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DI217" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DJ217" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK217" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM217" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN217" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO217" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV217" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW217" t="inlineStr"/>
+      <c r="DX217" t="inlineStr"/>
+      <c r="DY217" t="inlineStr"/>
+      <c r="DZ217" t="inlineStr"/>
+      <c r="EA217" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EB217" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EC217" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED217" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EE217" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="EF217" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EG217" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH217" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EI217" t="inlineStr"/>
+      <c r="EJ217" t="inlineStr"/>
+      <c r="EK217" t="inlineStr"/>
+      <c r="EL217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -99678,13 +99678,13 @@
         <v>4</v>
       </c>
       <c r="T215" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U215" t="n">
         <v>8</v>
       </c>
       <c r="V215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W215" t="n">
         <v>5</v>
@@ -99859,10 +99859,10 @@
         <v>1.08</v>
       </c>
       <c r="CA215" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="CB215" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="CC215" t="n">
         <v>0</v>
@@ -99919,7 +99919,7 @@
         <v>1</v>
       </c>
       <c r="CU215" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV215" t="n">
         <v>6</v>
@@ -100150,13 +100150,13 @@
         <v>6</v>
       </c>
       <c r="T216" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U216" t="n">
         <v>9</v>
       </c>
       <c r="V216" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W216" t="n">
         <v>8</v>
@@ -100331,10 +100331,10 @@
         <v>0.98</v>
       </c>
       <c r="CA216" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="CB216" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="CC216" t="n">
         <v>0</v>
@@ -100619,13 +100619,13 @@
         <v>6</v>
       </c>
       <c r="S217" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T217" t="n">
         <v>5</v>
       </c>
       <c r="U217" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V217" t="n">
         <v>11</v>
@@ -100800,13 +100800,13 @@
         <v>82</v>
       </c>
       <c r="BZ217" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="CA217" t="n">
         <v>1.39</v>
       </c>
       <c r="CB217" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="CC217" t="n">
         <v>0</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL217" headerRowCount="1">
-  <autoFilter ref="A1:EL217"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL219" headerRowCount="1">
+  <autoFilter ref="A1:EL219"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL217"/>
+  <dimension ref="A1:EL219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE5" t="n">
         <v>1.38</v>
@@ -3637,7 +3637,7 @@
         <v>2</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE7" t="n">
         <v>1.23</v>
@@ -7333,7 +7333,7 @@
         <v>1.36</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE22" t="n">
         <v>1.23</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12930,7 +12930,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE26" t="n">
         <v>1.46</v>
@@ -15681,7 +15681,7 @@
         <v>1.21</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -16153,7 +16153,7 @@
         <v>0.57</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -17998,7 +17998,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE37" t="n">
         <v>1.43</v>
@@ -19873,7 +19873,7 @@
         <v>1.5</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF41" t="n">
         <v>1.5</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21254,7 +21254,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE44" t="n">
         <v>1.38</v>
@@ -24014,7 +24014,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE50" t="n">
         <v>1.79</v>
@@ -25849,7 +25849,7 @@
         <v>2.15</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -27226,7 +27226,7 @@
         <v>67</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE57" t="n">
         <v>0.86</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28173,7 +28173,7 @@
         <v>2</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF59" t="n">
         <v>1.33</v>
@@ -30909,7 +30909,7 @@
         <v>2.38</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF65" t="n">
         <v>3</v>
@@ -31362,7 +31362,7 @@
         <v>71</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE66" t="n">
         <v>1.15</v>
@@ -31837,7 +31837,7 @@
         <v>1.38</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32769,7 +32769,7 @@
         <v>2.85</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -35982,7 +35982,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE76" t="n">
         <v>0.79</v>
@@ -38319,7 +38319,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38742,10 +38742,10 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF82" t="n">
         <v>1.6</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39198,7 +39198,7 @@
         <v>60</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE83" t="n">
         <v>1.79</v>
@@ -41945,7 +41945,7 @@
         <v>1.21</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF89" t="n">
         <v>1</v>
@@ -48358,7 +48358,7 @@
         <v>59</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE103" t="n">
         <v>1.14</v>
@@ -48809,7 +48809,7 @@
         <v>2.15</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF104" t="n">
         <v>1.67</v>
@@ -49278,7 +49278,7 @@
         <v>45</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE105" t="n">
         <v>1.54</v>
@@ -50657,7 +50657,7 @@
         <v>1.21</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF108" t="n">
         <v>1.33</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -56118,7 +56118,7 @@
         <v>54</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE120" t="n">
         <v>1.15</v>
@@ -56558,7 +56558,7 @@
         <v>62</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE121" t="n">
         <v>1.86</v>
@@ -57497,7 +57497,7 @@
         <v>0.54</v>
       </c>
       <c r="DE123" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF123" t="n">
         <v>0.43</v>
@@ -58873,7 +58873,7 @@
         <v>2.38</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF126" t="n">
         <v>2.71</v>
@@ -60718,7 +60718,7 @@
         <v>63</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE130" t="n">
         <v>0.79</v>
@@ -63922,7 +63922,7 @@
         <v>69</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE137" t="n">
         <v>0.79</v>
@@ -66261,7 +66261,7 @@
         <v>1.54</v>
       </c>
       <c r="DE142" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF142" t="n">
         <v>1.75</v>
@@ -67629,7 +67629,7 @@
         <v>1.36</v>
       </c>
       <c r="DE145" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF145" t="n">
         <v>1.38</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71330,7 +71330,7 @@
         <v>65</v>
       </c>
       <c r="DD153" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE153" t="n">
         <v>1.54</v>
@@ -74122,7 +74122,7 @@
         <v>56</v>
       </c>
       <c r="DD159" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE159" t="n">
         <v>1</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -75053,7 +75053,7 @@
         <v>1.54</v>
       </c>
       <c r="DE161" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF161" t="n">
         <v>1.56</v>
@@ -77805,7 +77805,7 @@
         <v>0.54</v>
       </c>
       <c r="DE167" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF167" t="n">
         <v>0.4</v>
@@ -79618,7 +79618,7 @@
         <v>60</v>
       </c>
       <c r="DD171" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE171" t="n">
         <v>1.86</v>
@@ -80522,7 +80522,7 @@
         <v>67</v>
       </c>
       <c r="DD173" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE173" t="n">
         <v>1.43</v>
@@ -82389,7 +82389,7 @@
         <v>1.5</v>
       </c>
       <c r="DE177" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF177" t="n">
         <v>1.4</v>
@@ -82850,7 +82850,7 @@
         <v>59</v>
       </c>
       <c r="DD178" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE178" t="n">
         <v>1.14</v>
@@ -83325,7 +83325,7 @@
         <v>0.57</v>
       </c>
       <c r="DE179" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF179" t="n">
         <v>0.64</v>
@@ -83789,7 +83789,7 @@
         <v>1.38</v>
       </c>
       <c r="DE180" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF180" t="n">
         <v>1.5</v>
@@ -86114,7 +86114,7 @@
         <v>73</v>
       </c>
       <c r="DD185" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE185" t="n">
         <v>1.62</v>
@@ -89809,7 +89809,7 @@
         <v>1.5</v>
       </c>
       <c r="DE193" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF193" t="n">
         <v>1.36</v>
@@ -90750,7 +90750,7 @@
         <v>67</v>
       </c>
       <c r="DD195" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DE195" t="n">
         <v>0.79</v>
@@ -92593,7 +92593,7 @@
         <v>1.5</v>
       </c>
       <c r="DE199" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF199" t="n">
         <v>1.5</v>
@@ -92623,7 +92623,7 @@
         <v>3.07</v>
       </c>
       <c r="DO199" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP199" t="b">
         <v>1</v>
@@ -95317,7 +95317,7 @@
         <v>2.85</v>
       </c>
       <c r="DE205" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DF205" t="n">
         <v>2.83</v>
@@ -96242,7 +96242,7 @@
         <v>63</v>
       </c>
       <c r="DD207" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE207" t="n">
         <v>1.62</v>
@@ -100994,6 +100994,902 @@
       <c r="EJ217" t="inlineStr"/>
       <c r="EK217" t="inlineStr"/>
       <c r="EL217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>28</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>46087.82291666666</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>7</v>
+      </c>
+      <c r="K218" t="n">
+        <v>3</v>
+      </c>
+      <c r="L218" t="n">
+        <v>10</v>
+      </c>
+      <c r="M218" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>10</v>
+      </c>
+      <c r="R218" t="n">
+        <v>5</v>
+      </c>
+      <c r="S218" t="n">
+        <v>11</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>21</v>
+      </c>
+      <c r="V218" t="n">
+        <v>5</v>
+      </c>
+      <c r="W218" t="n">
+        <v>9</v>
+      </c>
+      <c r="X218" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>Stade du Tivoli</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>Avenue de Saint-Maur-des-Fossés, La Louvière</t>
+        </is>
+      </c>
+      <c r="AC218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT218" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV218" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW218" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX218" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY218" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ218" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA218" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB218" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM218" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR218" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS218" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU218" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV218" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX218" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY218" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ218" t="n">
+        <v>19</v>
+      </c>
+      <c r="DA218" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB218" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC218" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD218" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DE218" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DF218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG218" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH218" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DI218" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DJ218" t="n">
+        <v>81</v>
+      </c>
+      <c r="DK218" t="n">
+        <v>46</v>
+      </c>
+      <c r="DL218" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM218" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN218" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DO218" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV218" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW218" t="inlineStr"/>
+      <c r="DX218" t="inlineStr"/>
+      <c r="DY218" t="inlineStr"/>
+      <c r="DZ218" t="inlineStr"/>
+      <c r="EA218" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EB218" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EC218" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED218" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE218" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EF218" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EG218" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH218" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EI218" t="inlineStr"/>
+      <c r="EJ218" t="inlineStr"/>
+      <c r="EK218" t="inlineStr"/>
+      <c r="EL218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>28</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>46088.625</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>9</v>
+      </c>
+      <c r="K219" t="n">
+        <v>7</v>
+      </c>
+      <c r="L219" t="n">
+        <v>16</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>4</v>
+      </c>
+      <c r="R219" t="n">
+        <v>1</v>
+      </c>
+      <c r="S219" t="n">
+        <v>17</v>
+      </c>
+      <c r="T219" t="n">
+        <v>8</v>
+      </c>
+      <c r="U219" t="n">
+        <v>21</v>
+      </c>
+      <c r="V219" t="n">
+        <v>9</v>
+      </c>
+      <c r="W219" t="n">
+        <v>13</v>
+      </c>
+      <c r="X219" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>King Power at Den Dreef Stadion</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>Kardinaal Mercierlaan 46, Heverlee</t>
+        </is>
+      </c>
+      <c r="AC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>534</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV219" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW219" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX219" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY219" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ219" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CA219" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB219" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP219" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR219" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS219" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU219" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV219" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX219" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY219" t="n">
+        <v>22</v>
+      </c>
+      <c r="CZ219" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA219" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB219" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC219" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD219" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE219" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DF219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH219" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DI219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ219" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK219" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL219" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM219" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN219" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DO219" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP219" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV219" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW219" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="DX219" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DY219" t="inlineStr"/>
+      <c r="DZ219" t="inlineStr"/>
+      <c r="EA219" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EB219" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EC219" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="ED219" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EE219" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="EF219" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EG219" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EH219" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EI219" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EJ219" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EK219" t="inlineStr"/>
+      <c r="EL219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL219" headerRowCount="1">
-  <autoFilter ref="A1:EL219"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL225" headerRowCount="1">
+  <autoFilter ref="A1:EL225"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL219"/>
+  <dimension ref="A1:EL225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2238,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         <v>1.07</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4562,10 +4562,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE9" t="n">
         <v>1.14</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE13" t="n">
         <v>0.86</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7797,7 +7797,7 @@
         <v>0.57</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE18" t="n">
         <v>0.79</v>
@@ -9227,7 +9227,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9666,10 +9666,10 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10133,7 +10133,7 @@
         <v>1.5</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10586,7 +10586,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE21" t="n">
         <v>1.43</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11061,7 +11061,7 @@
         <v>1.07</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11997,7 +11997,7 @@
         <v>1.21</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12933,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13386,7 +13386,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE27" t="n">
         <v>1.79</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14294,10 +14294,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14758,10 +14758,10 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15206,7 +15206,7 @@
         <v>25</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE31" t="n">
         <v>0.86</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16183,7 +16183,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16609,7 +16609,7 @@
         <v>1.21</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF34" t="n">
         <v>2</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17062,7 +17062,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE35" t="n">
         <v>1.86</v>
@@ -17095,7 +17095,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17529,7 +17529,7 @@
         <v>1.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF36" t="n">
         <v>2</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -18462,7 +18462,7 @@
         <v>50</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE38" t="n">
         <v>1</v>
@@ -18495,7 +18495,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18967,7 +18967,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20359,7 +20359,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20798,7 +20798,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE43" t="n">
         <v>1.79</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21257,7 +21257,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21710,10 +21710,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22641,7 +22641,7 @@
         <v>1.21</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF47" t="n">
         <v>1.33</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23094,7 +23094,7 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE48" t="n">
         <v>1</v>
@@ -23127,7 +23127,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23542,7 +23542,7 @@
         <v>34</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE49" t="n">
         <v>1.43</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24921,7 +24921,7 @@
         <v>0.57</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -24951,7 +24951,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25393,7 +25393,7 @@
         <v>2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25846,7 +25846,7 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE54" t="n">
         <v>1.21</v>
@@ -25879,7 +25879,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26305,7 +26305,7 @@
         <v>1.36</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26754,7 +26754,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE56" t="n">
         <v>0.79</v>
@@ -26787,7 +26787,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27731,7 +27731,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29085,7 +29085,7 @@
         <v>1.5</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29546,7 +29546,7 @@
         <v>59</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE62" t="n">
         <v>1.86</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30005,7 +30005,7 @@
         <v>1.5</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF63" t="n">
         <v>2.33</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE65" t="n">
         <v>1.21</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31365,7 +31365,7 @@
         <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31834,7 +31834,7 @@
         <v>63</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE67" t="n">
         <v>0.93</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32766,7 +32766,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE69" t="n">
         <v>1.21</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33214,10 +33214,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF70" t="n">
         <v>2.25</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34129,7 +34129,7 @@
         <v>1.21</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF72" t="n">
         <v>1.25</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34582,7 +34582,7 @@
         <v>38</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE73" t="n">
         <v>0.86</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35054,10 +35054,10 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -35087,7 +35087,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36457,7 +36457,7 @@
         <v>1.5</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36921,7 +36921,7 @@
         <v>2</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37814,7 +37814,7 @@
         <v>68</v>
       </c>
       <c r="DD80" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE80" t="n">
         <v>1.43</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39654,10 +39654,10 @@
         <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40121,7 +40121,7 @@
         <v>0.57</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF85" t="n">
         <v>0.8</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40566,10 +40566,10 @@
         <v>30</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF86" t="n">
         <v>0.4</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41014,10 +41014,10 @@
         <v>65</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF87" t="n">
         <v>1.8</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41486,7 +41486,7 @@
         <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE88" t="n">
         <v>1.14</v>
@@ -41519,7 +41519,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42389,7 +42389,7 @@
         <v>1.21</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42891,7 +42891,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43770,10 +43770,10 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44723,7 +44723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45618,7 +45618,7 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE97" t="n">
         <v>1.86</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46065,7 +46065,7 @@
         <v>1.21</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46534,7 +46534,7 @@
         <v>50</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE99" t="n">
         <v>1.43</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46990,7 +46990,7 @@
         <v>72</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE100" t="n">
         <v>0.79</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47457,7 +47457,7 @@
         <v>2</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF101" t="n">
         <v>1.83</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47913,7 +47913,7 @@
         <v>1.5</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF102" t="n">
         <v>1.67</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48391,7 +48391,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48806,7 +48806,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE104" t="n">
         <v>0.93</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49281,7 +49281,7 @@
         <v>1.07</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49726,7 +49726,7 @@
         <v>50</v>
       </c>
       <c r="DD106" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE106" t="n">
         <v>0.79</v>
@@ -49759,7 +49759,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50231,7 +50231,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50687,7 +50687,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52022,10 +52022,10 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52478,10 +52478,10 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF112" t="n">
         <v>2.17</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -53830,10 +53830,10 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF115" t="n">
         <v>3</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54319,7 +54319,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -54742,10 +54742,10 @@
         <v>84</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF117" t="n">
         <v>2.67</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55209,7 +55209,7 @@
         <v>1.36</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56121,7 +56121,7 @@
         <v>1.07</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56591,7 +56591,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57033,7 +57033,7 @@
         <v>1.5</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57494,7 +57494,7 @@
         <v>50</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE123" t="n">
         <v>1.21</v>
@@ -57527,7 +57527,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57950,10 +57950,10 @@
         <v>57</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF124" t="n">
         <v>1.43</v>
@@ -57983,7 +57983,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58870,7 +58870,7 @@
         <v>64</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE126" t="n">
         <v>0.93</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60254,7 +60254,7 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE129" t="n">
         <v>1.86</v>
@@ -60287,7 +60287,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61193,7 +61193,7 @@
         <v>0.57</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF131" t="n">
         <v>0.75</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61650,7 +61650,7 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE132" t="n">
         <v>1.14</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62098,7 +62098,7 @@
         <v>69</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE133" t="n">
         <v>1.79</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62557,7 +62557,7 @@
         <v>1.5</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF134" t="n">
         <v>1.25</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63013,7 +63013,7 @@
         <v>1.5</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63453,7 +63453,7 @@
         <v>1.5</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF136" t="n">
         <v>1.38</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -63955,7 +63955,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -64869,7 +64869,7 @@
         <v>0.57</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF139" t="n">
         <v>0.67</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65330,7 +65330,7 @@
         <v>57</v>
       </c>
       <c r="DD140" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE140" t="n">
         <v>0.86</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66258,7 +66258,7 @@
         <v>69</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE142" t="n">
         <v>0.93</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66690,7 +66690,7 @@
         <v>53</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE143" t="n">
         <v>1.79</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68093,7 +68093,7 @@
         <v>1.21</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF146" t="n">
         <v>1.44</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68554,10 +68554,10 @@
         <v>50</v>
       </c>
       <c r="DD147" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF147" t="n">
         <v>0.44</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69490,7 +69490,7 @@
         <v>77</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE149" t="n">
         <v>0.79</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69946,7 +69946,7 @@
         <v>59</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE150" t="n">
         <v>1.14</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70402,10 +70402,10 @@
         <v>78</v>
       </c>
       <c r="DD151" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF151" t="n">
         <v>2.11</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70861,7 +70861,7 @@
         <v>1.5</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF152" t="n">
         <v>1.56</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71333,7 +71333,7 @@
         <v>1</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF153" t="n">
         <v>1</v>
@@ -71363,7 +71363,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73197,7 +73197,7 @@
         <v>2</v>
       </c>
       <c r="DE157" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF157" t="n">
         <v>2.3</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75050,7 +75050,7 @@
         <v>78</v>
       </c>
       <c r="DD161" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE161" t="n">
         <v>1.21</v>
@@ -75083,7 +75083,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75506,7 +75506,7 @@
         <v>58</v>
       </c>
       <c r="DD162" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE162" t="n">
         <v>0.86</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -75970,10 +75970,10 @@
         <v>79</v>
       </c>
       <c r="DD163" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE163" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF163" t="n">
         <v>1.33</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76429,7 +76429,7 @@
         <v>1.5</v>
       </c>
       <c r="DE164" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF164" t="n">
         <v>1.7</v>
@@ -76459,7 +76459,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76874,10 +76874,10 @@
         <v>79</v>
       </c>
       <c r="DD165" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE165" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF165" t="n">
         <v>2.78</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77338,10 +77338,10 @@
         <v>68</v>
       </c>
       <c r="DD166" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE166" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF166" t="n">
         <v>1.7</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77802,7 +77802,7 @@
         <v>59</v>
       </c>
       <c r="DD167" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE167" t="n">
         <v>0.93</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78261,7 +78261,7 @@
         <v>1.21</v>
       </c>
       <c r="DE168" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF168" t="n">
         <v>1.4</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -78722,7 +78722,7 @@
         <v>65</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE169" t="n">
         <v>1</v>
@@ -78755,7 +78755,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80074,7 +80074,7 @@
         <v>71</v>
       </c>
       <c r="DD172" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE172" t="n">
         <v>0.79</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -80981,7 +80981,7 @@
         <v>1.5</v>
       </c>
       <c r="DE174" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF174" t="n">
         <v>1.64</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81453,7 +81453,7 @@
         <v>1.36</v>
       </c>
       <c r="DE175" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF175" t="n">
         <v>1.2</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82883,7 +82883,7 @@
         <v>2.66</v>
       </c>
       <c r="DO178" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP178" t="b">
         <v>1</v>
@@ -83355,7 +83355,7 @@
         <v>2.71</v>
       </c>
       <c r="DO179" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -83786,7 +83786,7 @@
         <v>71</v>
       </c>
       <c r="DD180" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE180" t="n">
         <v>1.21</v>
@@ -83819,7 +83819,7 @@
         <v>3.02</v>
       </c>
       <c r="DO180" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP180" t="b">
         <v>1</v>
@@ -84234,10 +84234,10 @@
         <v>87</v>
       </c>
       <c r="DD181" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE181" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF181" t="n">
         <v>2.27</v>
@@ -84267,7 +84267,7 @@
         <v>3.01</v>
       </c>
       <c r="DO181" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP181" t="b">
         <v>1</v>
@@ -84709,7 +84709,7 @@
         <v>1.21</v>
       </c>
       <c r="DE182" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF182" t="n">
         <v>1.09</v>
@@ -84739,7 +84739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO182" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -85170,10 +85170,10 @@
         <v>69</v>
       </c>
       <c r="DD183" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE183" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF183" t="n">
         <v>0.64</v>
@@ -85203,7 +85203,7 @@
         <v>2.77</v>
       </c>
       <c r="DO183" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP183" t="b">
         <v>1</v>
@@ -85642,7 +85642,7 @@
         <v>77</v>
       </c>
       <c r="DD184" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE184" t="n">
         <v>1.79</v>
@@ -85675,7 +85675,7 @@
         <v>3.71</v>
       </c>
       <c r="DO184" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP184" t="b">
         <v>1</v>
@@ -86117,7 +86117,7 @@
         <v>1</v>
       </c>
       <c r="DE185" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF185" t="n">
         <v>0.91</v>
@@ -86147,7 +86147,7 @@
         <v>2.75</v>
       </c>
       <c r="DO185" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -86619,7 +86619,7 @@
         <v>3.37</v>
       </c>
       <c r="DO186" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP186" t="b">
         <v>1</v>
@@ -87042,7 +87042,7 @@
         <v>69</v>
       </c>
       <c r="DD187" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE187" t="n">
         <v>0.79</v>
@@ -87075,7 +87075,7 @@
         <v>2.78</v>
       </c>
       <c r="DO187" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP187" t="b">
         <v>1</v>
@@ -87501,7 +87501,7 @@
         <v>1.21</v>
       </c>
       <c r="DE188" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF188" t="n">
         <v>1.55</v>
@@ -87531,7 +87531,7 @@
         <v>2.76</v>
       </c>
       <c r="DO188" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP188" t="b">
         <v>1</v>
@@ -87954,7 +87954,7 @@
         <v>69</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE189" t="n">
         <v>1</v>
@@ -87987,7 +87987,7 @@
         <v>3.03</v>
       </c>
       <c r="DO189" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -88429,7 +88429,7 @@
         <v>1.36</v>
       </c>
       <c r="DE190" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF190" t="n">
         <v>1.18</v>
@@ -88459,7 +88459,7 @@
         <v>3.51</v>
       </c>
       <c r="DO190" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP190" t="b">
         <v>1</v>
@@ -88870,7 +88870,7 @@
         <v>73</v>
       </c>
       <c r="DD191" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE191" t="n">
         <v>0.86</v>
@@ -88903,7 +88903,7 @@
         <v>2.93</v>
       </c>
       <c r="DO191" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP191" t="b">
         <v>1</v>
@@ -89342,10 +89342,10 @@
         <v>64</v>
       </c>
       <c r="DD192" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE192" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF192" t="n">
         <v>2.27</v>
@@ -89375,7 +89375,7 @@
         <v>2.89</v>
       </c>
       <c r="DO192" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP192" t="b">
         <v>1</v>
@@ -89839,7 +89839,7 @@
         <v>2.48</v>
       </c>
       <c r="DO193" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP193" t="b">
         <v>1</v>
@@ -90281,7 +90281,7 @@
         <v>1.5</v>
       </c>
       <c r="DE194" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF194" t="n">
         <v>1.5</v>
@@ -90311,7 +90311,7 @@
         <v>2.87</v>
       </c>
       <c r="DO194" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP194" t="b">
         <v>1</v>
@@ -90783,7 +90783,7 @@
         <v>2.81</v>
       </c>
       <c r="DO195" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP195" t="b">
         <v>1</v>
@@ -91239,7 +91239,7 @@
         <v>2.88</v>
       </c>
       <c r="DO196" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP196" t="b">
         <v>1</v>
@@ -91695,7 +91695,7 @@
         <v>2.98</v>
       </c>
       <c r="DO197" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP197" t="b">
         <v>1</v>
@@ -92167,7 +92167,7 @@
         <v>3.27</v>
       </c>
       <c r="DO198" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP198" t="b">
         <v>1</v>
@@ -93087,7 +93087,7 @@
         <v>2.89</v>
       </c>
       <c r="DO200" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP200" t="b">
         <v>0</v>
@@ -93518,7 +93518,7 @@
         <v>79</v>
       </c>
       <c r="DD201" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DE201" t="n">
         <v>0.79</v>
@@ -93551,7 +93551,7 @@
         <v>2.94</v>
       </c>
       <c r="DO201" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP201" t="b">
         <v>1</v>
@@ -93974,10 +93974,10 @@
         <v>79</v>
       </c>
       <c r="DD202" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DE202" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DF202" t="n">
         <v>1.67</v>
@@ -94007,7 +94007,7 @@
         <v>3.06</v>
       </c>
       <c r="DO202" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP202" t="b">
         <v>1</v>
@@ -94402,7 +94402,7 @@
         <v>63</v>
       </c>
       <c r="DD203" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DE203" t="n">
         <v>1.86</v>
@@ -94435,7 +94435,7 @@
         <v>2.78</v>
       </c>
       <c r="DO203" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP203" t="b">
         <v>1</v>
@@ -94866,7 +94866,7 @@
         <v>63</v>
       </c>
       <c r="DD204" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DE204" t="n">
         <v>1</v>
@@ -94899,7 +94899,7 @@
         <v>3.39</v>
       </c>
       <c r="DO204" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP204" t="b">
         <v>1</v>
@@ -95314,7 +95314,7 @@
         <v>79</v>
       </c>
       <c r="DD205" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE205" t="n">
         <v>0.93</v>
@@ -95347,7 +95347,7 @@
         <v>3.12</v>
       </c>
       <c r="DO205" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP205" t="b">
         <v>1</v>
@@ -95789,7 +95789,7 @@
         <v>1.36</v>
       </c>
       <c r="DE206" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DF206" t="n">
         <v>1.33</v>
@@ -95819,7 +95819,7 @@
         <v>2.97</v>
       </c>
       <c r="DO206" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP206" t="b">
         <v>1</v>
@@ -96245,7 +96245,7 @@
         <v>1.07</v>
       </c>
       <c r="DE207" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF207" t="n">
         <v>1.17</v>
@@ -96275,7 +96275,7 @@
         <v>2.5</v>
       </c>
       <c r="DO207" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP207" t="b">
         <v>1</v>
@@ -96714,10 +96714,10 @@
         <v>58</v>
       </c>
       <c r="DD208" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE208" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DF208" t="n">
         <v>1.5</v>
@@ -96747,7 +96747,7 @@
         <v>2.94</v>
       </c>
       <c r="DO208" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP208" t="b">
         <v>1</v>
@@ -97181,7 +97181,7 @@
         <v>1.5</v>
       </c>
       <c r="DE209" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF209" t="n">
         <v>1.42</v>
@@ -97211,7 +97211,7 @@
         <v>3.1</v>
       </c>
       <c r="DO209" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP209" t="b">
         <v>1</v>
@@ -97683,7 +97683,7 @@
         <v>2.31</v>
       </c>
       <c r="DO210" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP210" t="b">
         <v>1</v>
@@ -98139,7 +98139,7 @@
         <v>2.57</v>
       </c>
       <c r="DO211" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP211" t="b">
         <v>1</v>
@@ -98595,7 +98595,7 @@
         <v>3</v>
       </c>
       <c r="DO212" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP212" t="b">
         <v>1</v>
@@ -99051,7 +99051,7 @@
         <v>3.27</v>
       </c>
       <c r="DO213" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP213" t="b">
         <v>1</v>
@@ -99523,7 +99523,7 @@
         <v>3.4</v>
       </c>
       <c r="DO214" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP214" t="b">
         <v>1</v>
@@ -99979,7 +99979,7 @@
         <v>3.37</v>
       </c>
       <c r="DO215" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP215" t="b">
         <v>0</v>
@@ -100451,7 +100451,7 @@
         <v>3.3</v>
       </c>
       <c r="DO216" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP216" t="b">
         <v>1</v>
@@ -100923,7 +100923,7 @@
         <v>2.87</v>
       </c>
       <c r="DO217" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP217" t="b">
         <v>0</v>
@@ -101475,10 +101475,10 @@
         <v>9</v>
       </c>
       <c r="K219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L219" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -101496,13 +101496,13 @@
         <v>4</v>
       </c>
       <c r="R219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S219" t="n">
         <v>17</v>
       </c>
       <c r="T219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U219" t="n">
         <v>21</v>
@@ -101623,28 +101623,28 @@
         <v>-1</v>
       </c>
       <c r="BG219" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH219" t="n">
         <v>1</v>
       </c>
       <c r="BI219" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BJ219" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK219" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL219" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM219" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BN219" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO219" t="n">
         <v>0</v>
@@ -101683,10 +101683,10 @@
         <v>2.04</v>
       </c>
       <c r="CA219" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="CB219" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="CC219" t="n">
         <v>0</v>
@@ -101719,10 +101719,10 @@
         <v>1</v>
       </c>
       <c r="CM219" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN219" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CO219" t="n">
         <v>0</v>
@@ -101734,7 +101734,7 @@
         <v>1</v>
       </c>
       <c r="CR219" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS219" t="n">
         <v>19</v>
@@ -101826,70 +101826,2798 @@
       <c r="DV219" t="b">
         <v>0</v>
       </c>
-      <c r="DW219" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="DX219" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
+      <c r="DW219" t="inlineStr"/>
+      <c r="DX219" t="inlineStr"/>
       <c r="DY219" t="inlineStr"/>
       <c r="DZ219" t="inlineStr"/>
       <c r="EA219" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EB219" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EC219" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED219" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EE219" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EF219" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EG219" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH219" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EI219" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EJ219" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EK219" t="inlineStr"/>
       <c r="EL219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>28</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>46088.71875</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2</v>
+      </c>
+      <c r="I220" t="n">
+        <v>4</v>
+      </c>
+      <c r="J220" t="n">
+        <v>5</v>
+      </c>
+      <c r="K220" t="n">
+        <v>13</v>
+      </c>
+      <c r="L220" t="n">
+        <v>18</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>5</v>
+      </c>
+      <c r="R220" t="n">
+        <v>7</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="n">
+        <v>15</v>
+      </c>
+      <c r="U220" t="n">
+        <v>15</v>
+      </c>
+      <c r="V220" t="n">
+        <v>22</v>
+      </c>
+      <c r="W220" t="n">
+        <v>9</v>
+      </c>
+      <c r="X220" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT220" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV220" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW220" t="n">
+        <v>83</v>
+      </c>
+      <c r="BX220" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY220" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ220" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA220" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CB220" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="CC220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN220" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR220" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS220" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU220" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV220" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX220" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY220" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ220" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA220" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB220" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC220" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD220" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE220" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DF220" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DG220" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DH220" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DJ220" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK220" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN220" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO220" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP220" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ220" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR220" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS220" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT220" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU220" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV220" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW220" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="DX220" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY220" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DZ220" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EA220" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="EB220" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC220" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED220" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="EE220" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EF220" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG220" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH220" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI220" t="inlineStr"/>
+      <c r="EJ220" t="inlineStr"/>
+      <c r="EK220" t="inlineStr"/>
+      <c r="EL220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>28</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>46088.82291666666</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>5</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>6</v>
+      </c>
+      <c r="M221" t="n">
+        <v>3</v>
+      </c>
+      <c r="N221" t="n">
+        <v>2</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>4</v>
+      </c>
+      <c r="R221" t="n">
+        <v>3</v>
+      </c>
+      <c r="S221" t="n">
+        <v>8</v>
+      </c>
+      <c r="T221" t="n">
+        <v>2</v>
+      </c>
+      <c r="U221" t="n">
+        <v>12</v>
+      </c>
+      <c r="V221" t="n">
+        <v>5</v>
+      </c>
+      <c r="W221" t="n">
+        <v>9</v>
+      </c>
+      <c r="X221" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV221" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW221" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX221" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY221" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ221" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA221" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB221" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR221" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS221" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU221" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV221" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX221" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY221" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ221" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA221" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB221" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC221" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD221" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DE221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF221" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DG221" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DH221" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DI221" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DJ221" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK221" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL221" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DM221" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN221" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="DO221" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS221" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT221" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU221" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW221" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="DX221" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DY221" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="DZ221" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EA221" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EB221" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EC221" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="ED221" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE221" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EF221" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="EG221" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH221" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EI221" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EJ221" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK221" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EL221" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>28</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>46089.52083333334</v>
+      </c>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" t="n">
+        <v>4</v>
+      </c>
+      <c r="J222" t="n">
+        <v>11</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" t="n">
+        <v>13</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" t="n">
+        <v>3</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>9</v>
+      </c>
+      <c r="R222" t="n">
+        <v>5</v>
+      </c>
+      <c r="S222" t="n">
+        <v>15</v>
+      </c>
+      <c r="T222" t="n">
+        <v>8</v>
+      </c>
+      <c r="U222" t="n">
+        <v>24</v>
+      </c>
+      <c r="V222" t="n">
+        <v>13</v>
+      </c>
+      <c r="W222" t="n">
+        <v>7</v>
+      </c>
+      <c r="X222" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ222" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV222" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW222" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX222" t="n">
+        <v>133</v>
+      </c>
+      <c r="BY222" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ222" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CA222" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CB222" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="CC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP222" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR222" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS222" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU222" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV222" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX222" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY222" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ222" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA222" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB222" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC222" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD222" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DE222" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF222" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DG222" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DH222" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DI222" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DJ222" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK222" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL222" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DM222" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN222" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DO222" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP222" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ222" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR222" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS222" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT222" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU222" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV222" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW222" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DX222" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY222" t="inlineStr"/>
+      <c r="DZ222" t="inlineStr"/>
+      <c r="EA222" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EB222" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC222" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="ED222" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EE222" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="EF222" t="inlineStr">
+        <is>
+          <t>6.81</t>
+        </is>
+      </c>
+      <c r="EG222" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EH222" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EI222" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ222" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EK222" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EL222" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>28</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>46089.625</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" t="n">
+        <v>4</v>
+      </c>
+      <c r="J223" t="n">
+        <v>3</v>
+      </c>
+      <c r="K223" t="n">
+        <v>5</v>
+      </c>
+      <c r="L223" t="n">
+        <v>8</v>
+      </c>
+      <c r="M223" t="n">
+        <v>2</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>5</v>
+      </c>
+      <c r="R223" t="n">
+        <v>3</v>
+      </c>
+      <c r="S223" t="n">
+        <v>8</v>
+      </c>
+      <c r="T223" t="n">
+        <v>5</v>
+      </c>
+      <c r="U223" t="n">
+        <v>13</v>
+      </c>
+      <c r="V223" t="n">
+        <v>8</v>
+      </c>
+      <c r="W223" t="n">
+        <v>9</v>
+      </c>
+      <c r="X223" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV223" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW223" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX223" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY223" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ223" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA223" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB223" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR223" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS223" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU223" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV223" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW223" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX223" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY223" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ223" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA223" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB223" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC223" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD223" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE223" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF223" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DG223" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DH223" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI223" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ223" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK223" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL223" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM223" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN223" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO223" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP223" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ223" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR223" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS223" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT223" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU223" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV223" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW223" t="inlineStr"/>
+      <c r="DX223" t="inlineStr"/>
+      <c r="DY223" t="inlineStr"/>
+      <c r="DZ223" t="inlineStr"/>
+      <c r="EA223" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EB223" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EC223" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="ED223" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE223" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EF223" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EG223" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH223" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EI223" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EJ223" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK223" t="inlineStr"/>
+      <c r="EL223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>28</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>46089.72916666666</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" t="n">
+        <v>2</v>
+      </c>
+      <c r="L224" t="n">
+        <v>5</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>5</v>
+      </c>
+      <c r="R224" t="n">
+        <v>4</v>
+      </c>
+      <c r="S224" t="n">
+        <v>14</v>
+      </c>
+      <c r="T224" t="n">
+        <v>5</v>
+      </c>
+      <c r="U224" t="n">
+        <v>19</v>
+      </c>
+      <c r="V224" t="n">
+        <v>9</v>
+      </c>
+      <c r="W224" t="n">
+        <v>10</v>
+      </c>
+      <c r="X224" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>Regenboogstadion</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>Zuiderlaan 17, Waregem</t>
+        </is>
+      </c>
+      <c r="AC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>31</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV224" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW224" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX224" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY224" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ224" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CA224" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB224" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR224" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS224" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU224" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV224" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX224" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY224" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ224" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA224" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB224" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC224" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD224" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF224" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG224" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH224" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI224" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ224" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK224" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL224" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM224" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DN224" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO224" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP224" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV224" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW224" t="inlineStr"/>
+      <c r="DX224" t="inlineStr"/>
+      <c r="DY224" t="inlineStr"/>
+      <c r="DZ224" t="inlineStr"/>
+      <c r="EA224" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EB224" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC224" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="ED224" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EE224" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EF224" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EG224" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH224" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EI224" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ224" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EK224" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EL224" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>28</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>46089.76041666666</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" t="n">
+        <v>3</v>
+      </c>
+      <c r="J225" t="n">
+        <v>7</v>
+      </c>
+      <c r="K225" t="n">
+        <v>5</v>
+      </c>
+      <c r="L225" t="n">
+        <v>12</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>4</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>7</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6</v>
+      </c>
+      <c r="S225" t="n">
+        <v>8</v>
+      </c>
+      <c r="T225" t="n">
+        <v>12</v>
+      </c>
+      <c r="U225" t="n">
+        <v>15</v>
+      </c>
+      <c r="V225" t="n">
+        <v>18</v>
+      </c>
+      <c r="W225" t="n">
+        <v>7</v>
+      </c>
+      <c r="X225" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA225" t="inlineStr"/>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>532</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV225" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW225" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX225" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY225" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ225" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CA225" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CB225" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="CC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI225" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ225" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP225" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ225" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR225" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS225" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT225" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU225" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV225" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW225" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX225" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY225" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ225" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA225" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB225" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC225" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD225" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DE225" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF225" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DG225" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DH225" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI225" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DJ225" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK225" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL225" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM225" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN225" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="DO225" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP225" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ225" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR225" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS225" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT225" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU225" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV225" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW225" t="inlineStr"/>
+      <c r="DX225" t="inlineStr"/>
+      <c r="DY225" t="inlineStr"/>
+      <c r="DZ225" t="inlineStr"/>
+      <c r="EA225" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB225" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC225" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="ED225" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE225" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EF225" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="EG225" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EH225" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EI225" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ225" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EK225" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EL225" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -102413,10 +102413,10 @@
         <v>9</v>
       </c>
       <c r="Y221" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z221" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -104032,7 +104032,7 @@
         <v>1</v>
       </c>
       <c r="CX224" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY224" t="n">
         <v>10</v>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL225" headerRowCount="1">
-  <autoFilter ref="A1:EL225"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL226" headerRowCount="1">
+  <autoFilter ref="A1:EL226"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL225"/>
+  <dimension ref="A1:EL226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5933,7 +5933,7 @@
         <v>1.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE13" t="n">
         <v>0.86</v>
@@ -10586,7 +10586,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE21" t="n">
         <v>1.43</v>
@@ -11533,7 +11533,7 @@
         <v>2</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -20798,7 +20798,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE43" t="n">
         <v>1.79</v>
@@ -22185,7 +22185,7 @@
         <v>1.36</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -26754,7 +26754,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE56" t="n">
         <v>0.79</v>
@@ -27701,7 +27701,7 @@
         <v>1.21</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF58" t="n">
         <v>1.67</v>
@@ -35054,7 +35054,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE74" t="n">
         <v>1.21</v>
@@ -35985,7 +35985,7 @@
         <v>1.07</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
@@ -41519,7 +41519,7 @@
         <v>2.85</v>
       </c>
       <c r="DO88" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43770,7 +43770,7 @@
         <v>60</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE93" t="n">
         <v>1.5</v>
@@ -44693,7 +44693,7 @@
         <v>0.57</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF95" t="n">
         <v>0.83</v>
@@ -49729,7 +49729,7 @@
         <v>0.57</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF106" t="n">
         <v>0.33</v>
@@ -52478,7 +52478,7 @@
         <v>77</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE112" t="n">
         <v>1.36</v>
@@ -53369,7 +53369,7 @@
         <v>1.21</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF114" t="n">
         <v>1.57</v>
@@ -60254,7 +60254,7 @@
         <v>71</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE129" t="n">
         <v>1.86</v>
@@ -63925,7 +63925,7 @@
         <v>1</v>
       </c>
       <c r="DE137" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF137" t="n">
         <v>1</v>
@@ -66258,7 +66258,7 @@
         <v>69</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE142" t="n">
         <v>0.93</v>
@@ -69493,7 +69493,7 @@
         <v>2.86</v>
       </c>
       <c r="DE149" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF149" t="n">
         <v>2.75</v>
@@ -73669,7 +73669,7 @@
         <v>1.5</v>
       </c>
       <c r="DE158" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF158" t="n">
         <v>1.5</v>
@@ -75050,7 +75050,7 @@
         <v>78</v>
       </c>
       <c r="DD161" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE161" t="n">
         <v>1.21</v>
@@ -77338,7 +77338,7 @@
         <v>68</v>
       </c>
       <c r="DD166" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE166" t="n">
         <v>1.14</v>
@@ -80077,7 +80077,7 @@
         <v>2.29</v>
       </c>
       <c r="DE172" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF172" t="n">
         <v>2.2</v>
@@ -87954,7 +87954,7 @@
         <v>69</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE189" t="n">
         <v>1</v>
@@ -93521,7 +93521,7 @@
         <v>2.21</v>
       </c>
       <c r="DE201" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF201" t="n">
         <v>2.08</v>
@@ -93974,7 +93974,7 @@
         <v>79</v>
       </c>
       <c r="DD202" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE202" t="n">
         <v>1.43</v>
@@ -98109,7 +98109,7 @@
         <v>1.5</v>
       </c>
       <c r="DE211" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF211" t="n">
         <v>1.38</v>
@@ -103602,7 +103602,7 @@
         <v>85</v>
       </c>
       <c r="DD223" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DE223" t="n">
         <v>1.5</v>
@@ -104618,6 +104618,442 @@
           <t>1.50</t>
         </is>
       </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>29</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>46094.82291666666</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>2</v>
+      </c>
+      <c r="J226" t="n">
+        <v>2</v>
+      </c>
+      <c r="K226" t="n">
+        <v>6</v>
+      </c>
+      <c r="L226" t="n">
+        <v>8</v>
+      </c>
+      <c r="M226" t="n">
+        <v>2</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>5</v>
+      </c>
+      <c r="R226" t="n">
+        <v>1</v>
+      </c>
+      <c r="S226" t="n">
+        <v>6</v>
+      </c>
+      <c r="T226" t="n">
+        <v>4</v>
+      </c>
+      <c r="U226" t="n">
+        <v>11</v>
+      </c>
+      <c r="V226" t="n">
+        <v>5</v>
+      </c>
+      <c r="W226" t="n">
+        <v>13</v>
+      </c>
+      <c r="X226" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>GHELAMCO-arena</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>Ottergemsesteenweg-Zuid 808, Gent</t>
+        </is>
+      </c>
+      <c r="AC226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>525</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV226" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW226" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX226" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY226" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ226" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA226" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB226" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CC226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN226" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP226" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR226" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS226" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU226" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV226" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX226" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY226" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ226" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA226" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB226" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC226" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD226" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE226" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF226" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG226" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DH226" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DI226" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DJ226" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK226" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL226" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN226" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO226" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP226" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ226" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR226" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS226" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT226" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU226" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV226" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW226" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DX226" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY226" t="inlineStr"/>
+      <c r="DZ226" t="inlineStr"/>
+      <c r="EA226" t="inlineStr"/>
+      <c r="EB226" t="inlineStr"/>
+      <c r="EC226" t="inlineStr"/>
+      <c r="ED226" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EE226" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EF226" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EG226" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EH226" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EI226" t="inlineStr"/>
+      <c r="EJ226" t="inlineStr"/>
+      <c r="EK226" t="inlineStr"/>
+      <c r="EL226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Belgium_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL226" headerRowCount="1">
-  <autoFilter ref="A1:EL226"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL233" headerRowCount="1">
+  <autoFilter ref="A1:EL233"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL226"/>
+  <dimension ref="A1:EL233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE2" t="n">
         <v>1.43</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP3" t="b">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         <v>1.07</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE11" t="n">
         <v>0.73</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6389,7 +6389,7 @@
         <v>1.21</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6861,7 +6861,7 @@
         <v>1.73</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE14" t="n">
         <v>0.93</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7794,10 +7794,10 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8266,10 +8266,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8730,10 +8730,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9197,7 +9197,7 @@
         <v>2.21</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9227,7 +9227,7 @@
         <v>2.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9699,7 +9699,7 @@
         <v>2.97</v>
       </c>
       <c r="DO19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10130,7 +10130,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE20" t="n">
         <v>1.5</v>
@@ -10163,7 +10163,7 @@
         <v>2.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10619,7 +10619,7 @@
         <v>3.49</v>
       </c>
       <c r="DO21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>3.54</v>
       </c>
       <c r="DO22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11563,7 +11563,7 @@
         <v>4.13</v>
       </c>
       <c r="DO23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12466,10 +12466,10 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE25" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12499,7 +12499,7 @@
         <v>1.74</v>
       </c>
       <c r="DO25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12963,7 +12963,7 @@
         <v>3</v>
       </c>
       <c r="DO26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13389,7 +13389,7 @@
         <v>1.29</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF27" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>4.47</v>
       </c>
       <c r="DO27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13838,7 +13838,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE28" t="n">
         <v>1.14</v>
@@ -13871,7 +13871,7 @@
         <v>2.39</v>
       </c>
       <c r="DO28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14294,10 +14294,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14327,7 +14327,7 @@
         <v>3.25</v>
       </c>
       <c r="DO29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14761,7 +14761,7 @@
         <v>0.57</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -14791,7 +14791,7 @@
         <v>2.46</v>
       </c>
       <c r="DO30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15209,7 +15209,7 @@
         <v>2.21</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15239,7 +15239,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15678,7 +15678,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE32" t="n">
         <v>0.93</v>
@@ -15711,7 +15711,7 @@
         <v>1.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16150,7 +16150,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE33" t="n">
         <v>1.21</v>
@@ -16183,7 +16183,7 @@
         <v>2.38</v>
       </c>
       <c r="DO33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16639,7 +16639,7 @@
         <v>2.27</v>
       </c>
       <c r="DO34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17065,7 +17065,7 @@
         <v>1.29</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF35" t="n">
         <v>0.5</v>
@@ -17095,7 +17095,7 @@
         <v>3.03</v>
       </c>
       <c r="DO35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17526,7 +17526,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE36" t="n">
         <v>1.5</v>
@@ -17559,7 +17559,7 @@
         <v>2.02</v>
       </c>
       <c r="DO36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18031,7 +18031,7 @@
         <v>3.06</v>
       </c>
       <c r="DO37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>0.57</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -18495,7 +18495,7 @@
         <v>1.86</v>
       </c>
       <c r="DO38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18934,10 +18934,10 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -18967,7 +18967,7 @@
         <v>3.08</v>
       </c>
       <c r="DO39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19398,10 +19398,10 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19431,7 +19431,7 @@
         <v>1.93</v>
       </c>
       <c r="DO40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19870,7 +19870,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE41" t="n">
         <v>0.93</v>
@@ -19903,7 +19903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20326,10 +20326,10 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20359,7 +20359,7 @@
         <v>1.86</v>
       </c>
       <c r="DO42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20801,7 +20801,7 @@
         <v>1.73</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -20831,7 +20831,7 @@
         <v>3.85</v>
       </c>
       <c r="DO43" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21257,7 +21257,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21287,7 +21287,7 @@
         <v>2.31</v>
       </c>
       <c r="DO44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21710,10 +21710,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21743,7 +21743,7 @@
         <v>4.11</v>
       </c>
       <c r="DO45" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22182,7 +22182,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE46" t="n">
         <v>0.73</v>
@@ -22215,7 +22215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22671,7 +22671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO47" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23097,7 +23097,7 @@
         <v>1.29</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF48" t="n">
         <v>0.33</v>
@@ -23127,7 +23127,7 @@
         <v>2.06</v>
       </c>
       <c r="DO48" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23575,7 +23575,7 @@
         <v>2.68</v>
       </c>
       <c r="DO49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24017,7 +24017,7 @@
         <v>1.07</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF50" t="n">
         <v>1.33</v>
@@ -24047,7 +24047,7 @@
         <v>3.08</v>
       </c>
       <c r="DO50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24462,7 +24462,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE51" t="n">
         <v>1.14</v>
@@ -24495,7 +24495,7 @@
         <v>3.03</v>
       </c>
       <c r="DO51" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE52" t="n">
         <v>1.21</v>
@@ -24951,7 +24951,7 @@
         <v>3.3</v>
       </c>
       <c r="DO52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25423,7 +25423,7 @@
         <v>4.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25879,7 +25879,7 @@
         <v>3.32</v>
       </c>
       <c r="DO54" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26302,7 +26302,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE55" t="n">
         <v>1.21</v>
@@ -26335,7 +26335,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26757,7 +26757,7 @@
         <v>1.73</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF56" t="n">
         <v>1.33</v>
@@ -26787,7 +26787,7 @@
         <v>2.62</v>
       </c>
       <c r="DO56" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27229,7 +27229,7 @@
         <v>1</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>1.33</v>
@@ -27259,7 +27259,7 @@
         <v>2.45</v>
       </c>
       <c r="DO57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27698,7 +27698,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE58" t="n">
         <v>0.73</v>
@@ -27731,7 +27731,7 @@
         <v>2.3</v>
       </c>
       <c r="DO58" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28203,7 +28203,7 @@
         <v>3.22</v>
       </c>
       <c r="DO59" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28626,7 +28626,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE60" t="n">
         <v>1.43</v>
@@ -28659,7 +28659,7 @@
         <v>3.33</v>
       </c>
       <c r="DO60" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29082,10 +29082,10 @@
         <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -29115,7 +29115,7 @@
         <v>2.51</v>
       </c>
       <c r="DO61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29549,7 +29549,7 @@
         <v>2.29</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF62" t="n">
         <v>3</v>
@@ -29579,7 +29579,7 @@
         <v>3.47</v>
       </c>
       <c r="DO62" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30002,7 +30002,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE63" t="n">
         <v>1.43</v>
@@ -30035,7 +30035,7 @@
         <v>2.74</v>
       </c>
       <c r="DO63" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -30491,7 +30491,7 @@
         <v>3.68</v>
       </c>
       <c r="DO64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30939,7 +30939,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31365,7 +31365,7 @@
         <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -31395,7 +31395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO66" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31867,7 +31867,7 @@
         <v>2.31</v>
       </c>
       <c r="DO67" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32297,7 +32297,7 @@
         <v>1.21</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF68" t="n">
         <v>1.25</v>
@@ -32327,7 +32327,7 @@
         <v>3.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32766,7 +32766,7 @@
         <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE69" t="n">
         <v>1.21</v>
@@ -32799,7 +32799,7 @@
         <v>3.99</v>
       </c>
       <c r="DO69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33247,7 +33247,7 @@
         <v>3.59</v>
       </c>
       <c r="DO70" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33670,7 +33670,7 @@
         <v>75</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE71" t="n">
         <v>1.14</v>
@@ -33703,7 +33703,7 @@
         <v>2.82</v>
       </c>
       <c r="DO71" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34126,7 +34126,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE72" t="n">
         <v>1.5</v>
@@ -34159,7 +34159,7 @@
         <v>2.56</v>
       </c>
       <c r="DO72" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34585,7 +34585,7 @@
         <v>0.57</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF73" t="n">
         <v>0.25</v>
@@ -34615,7 +34615,7 @@
         <v>1.91</v>
       </c>
       <c r="DO73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -35087,7 +35087,7 @@
         <v>3.1</v>
       </c>
       <c r="DO74" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35518,10 +35518,10 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF75" t="n">
         <v>2</v>
@@ -35551,7 +35551,7 @@
         <v>2.79</v>
       </c>
       <c r="DO75" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36015,7 +36015,7 @@
         <v>2.59</v>
       </c>
       <c r="DO76" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -36454,7 +36454,7 @@
         <v>63</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE77" t="n">
         <v>1.43</v>
@@ -36487,7 +36487,7 @@
         <v>2.96</v>
       </c>
       <c r="DO77" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36921,7 +36921,7 @@
         <v>2</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF78" t="n">
         <v>1.6</v>
@@ -36951,7 +36951,7 @@
         <v>2.79</v>
       </c>
       <c r="DO78" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37374,10 +37374,10 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF79" t="n">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>2.77</v>
       </c>
       <c r="DO79" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37847,7 +37847,7 @@
         <v>3.64</v>
       </c>
       <c r="DO80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38286,10 +38286,10 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE81" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF81" t="n">
         <v>1.5</v>
@@ -38319,7 +38319,7 @@
         <v>3.04</v>
       </c>
       <c r="DO81" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38775,7 +38775,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP82" t="b">
         <v>0</v>
@@ -39201,7 +39201,7 @@
         <v>1</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>3.36</v>
       </c>
       <c r="DO83" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39654,7 +39654,7 @@
         <v>88</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE84" t="n">
         <v>1.21</v>
@@ -39687,7 +39687,7 @@
         <v>3.64</v>
       </c>
       <c r="DO84" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40118,7 +40118,7 @@
         <v>90</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE85" t="n">
         <v>1.36</v>
@@ -40151,7 +40151,7 @@
         <v>3.48</v>
       </c>
       <c r="DO85" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40599,7 +40599,7 @@
         <v>2.27</v>
       </c>
       <c r="DO86" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41017,7 +41017,7 @@
         <v>2.21</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF87" t="n">
         <v>1.8</v>
@@ -41047,7 +41047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO87" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41975,7 +41975,7 @@
         <v>2.4</v>
       </c>
       <c r="DO89" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42386,10 +42386,10 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -42419,7 +42419,7 @@
         <v>2.63</v>
       </c>
       <c r="DO90" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42858,10 +42858,10 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF91" t="n">
         <v>1.8</v>
@@ -42891,7 +42891,7 @@
         <v>2.98</v>
       </c>
       <c r="DO91" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43306,10 +43306,10 @@
         <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE92" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF92" t="n">
         <v>1.6</v>
@@ -43339,7 +43339,7 @@
         <v>2.52</v>
       </c>
       <c r="DO92" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43773,7 +43773,7 @@
         <v>1.73</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -43803,7 +43803,7 @@
         <v>2.33</v>
       </c>
       <c r="DO93" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44226,10 +44226,10 @@
         <v>75</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF94" t="n">
         <v>1.6</v>
@@ -44259,7 +44259,7 @@
         <v>3.41</v>
       </c>
       <c r="DO94" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44690,7 +44690,7 @@
         <v>90</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE95" t="n">
         <v>0.73</v>
@@ -44723,7 +44723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO95" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45146,10 +45146,10 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF96" t="n">
         <v>1.4</v>
@@ -45179,7 +45179,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45618,10 +45618,10 @@
         <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF97" t="n">
         <v>3</v>
@@ -45651,7 +45651,7 @@
         <v>3.73</v>
       </c>
       <c r="DO97" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46095,7 +46095,7 @@
         <v>2.74</v>
       </c>
       <c r="DO98" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46567,7 +46567,7 @@
         <v>2.93</v>
       </c>
       <c r="DO99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46993,7 +46993,7 @@
         <v>2.29</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF100" t="n">
         <v>2.6</v>
@@ -47023,7 +47023,7 @@
         <v>3.03</v>
       </c>
       <c r="DO100" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47487,7 +47487,7 @@
         <v>3.35</v>
       </c>
       <c r="DO101" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47910,7 +47910,7 @@
         <v>83</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE102" t="n">
         <v>1.36</v>
@@ -47943,7 +47943,7 @@
         <v>3.74</v>
       </c>
       <c r="DO102" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48391,7 +48391,7 @@
         <v>2.95</v>
       </c>
       <c r="DO103" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48839,7 +48839,7 @@
         <v>2.72</v>
       </c>
       <c r="DO104" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49311,7 +49311,7 @@
         <v>2.7</v>
       </c>
       <c r="DO105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49759,7 +49759,7 @@
         <v>2.55</v>
       </c>
       <c r="DO106" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50198,10 +50198,10 @@
         <v>84</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE107" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF107" t="n">
         <v>0.86</v>
@@ -50231,7 +50231,7 @@
         <v>2.88</v>
       </c>
       <c r="DO107" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50654,7 +50654,7 @@
         <v>75</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE108" t="n">
         <v>1.21</v>
@@ -50687,7 +50687,7 @@
         <v>2.81</v>
       </c>
       <c r="DO108" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51094,10 +51094,10 @@
         <v>84</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF109" t="n">
         <v>1.33</v>
@@ -51127,7 +51127,7 @@
         <v>2.51</v>
       </c>
       <c r="DO109" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51569,7 +51569,7 @@
         <v>2</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF110" t="n">
         <v>2</v>
@@ -51599,7 +51599,7 @@
         <v>3.79</v>
       </c>
       <c r="DO110" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52025,7 +52025,7 @@
         <v>2.21</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF111" t="n">
         <v>1.86</v>
@@ -52055,7 +52055,7 @@
         <v>2.64</v>
       </c>
       <c r="DO111" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52511,7 +52511,7 @@
         <v>3.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52926,7 +52926,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE113" t="n">
         <v>1.43</v>
@@ -52959,7 +52959,7 @@
         <v>2.94</v>
       </c>
       <c r="DO113" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53399,7 +53399,7 @@
         <v>2.75</v>
       </c>
       <c r="DO114" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP114" t="b">
         <v>0</v>
@@ -53830,7 +53830,7 @@
         <v>59</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE115" t="n">
         <v>1.43</v>
@@ -53863,7 +53863,7 @@
         <v>3.55</v>
       </c>
       <c r="DO115" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54286,7 +54286,7 @@
         <v>79</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE116" t="n">
         <v>1.14</v>
@@ -54319,7 +54319,7 @@
         <v>3.36</v>
       </c>
       <c r="DO116" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -54775,7 +54775,7 @@
         <v>3.27</v>
       </c>
       <c r="DO117" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55206,7 +55206,7 @@
         <v>86</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE118" t="n">
         <v>1.5</v>
@@ -55239,7 +55239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO118" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55662,10 +55662,10 @@
         <v>86</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF119" t="n">
         <v>1.57</v>
@@ -55695,7 +55695,7 @@
         <v>2.73</v>
       </c>
       <c r="DO119" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56121,7 +56121,7 @@
         <v>1.07</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF120" t="n">
         <v>1.71</v>
@@ -56151,7 +56151,7 @@
         <v>2.57</v>
       </c>
       <c r="DO120" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56561,7 +56561,7 @@
         <v>1</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF121" t="n">
         <v>1.14</v>
@@ -56591,7 +56591,7 @@
         <v>2.98</v>
       </c>
       <c r="DO121" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57030,10 +57030,10 @@
         <v>57</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF122" t="n">
         <v>1.43</v>
@@ -57063,7 +57063,7 @@
         <v>2.12</v>
       </c>
       <c r="DO122" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57527,7 +57527,7 @@
         <v>2.79</v>
       </c>
       <c r="DO123" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57983,7 +57983,7 @@
         <v>2.84</v>
       </c>
       <c r="DO124" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58398,10 +58398,10 @@
         <v>72</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF125" t="n">
         <v>1.57</v>
@@ -58431,7 +58431,7 @@
         <v>2.23</v>
       </c>
       <c r="DO125" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP125" t="b">
         <v>0</v>
@@ -58903,7 +58903,7 @@
         <v>2.88</v>
       </c>
       <c r="DO126" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59318,10 +59318,10 @@
         <v>86</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE127" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF127" t="n">
         <v>1.14</v>
@@ -59351,7 +59351,7 @@
         <v>3.2</v>
       </c>
       <c r="DO127" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59815,7 +59815,7 @@
         <v>3.59</v>
       </c>
       <c r="DO128" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60257,7 +60257,7 @@
         <v>1.73</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -60287,7 +60287,7 @@
         <v>3.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60721,7 +60721,7 @@
         <v>1.07</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF130" t="n">
         <v>1.5</v>
@@ -60751,7 +60751,7 @@
         <v>2.39</v>
       </c>
       <c r="DO130" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61190,10 +61190,10 @@
         <v>75</v>
       </c>
       <c r="DD131" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF131" t="n">
         <v>0.75</v>
@@ -61223,7 +61223,7 @@
         <v>2.47</v>
       </c>
       <c r="DO131" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61650,7 +61650,7 @@
         <v>67</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE132" t="n">
         <v>1.14</v>
@@ -61683,7 +61683,7 @@
         <v>3.48</v>
       </c>
       <c r="DO132" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62101,7 +62101,7 @@
         <v>2.21</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF133" t="n">
         <v>2</v>
@@ -62131,7 +62131,7 @@
         <v>3.45</v>
       </c>
       <c r="DO133" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62554,7 +62554,7 @@
         <v>69</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE134" t="n">
         <v>1.21</v>
@@ -62587,7 +62587,7 @@
         <v>2.58</v>
       </c>
       <c r="DO134" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63010,10 +63010,10 @@
         <v>59</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF135" t="n">
         <v>1.38</v>
@@ -63043,7 +63043,7 @@
         <v>3.39</v>
       </c>
       <c r="DO135" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         <v>82</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE136" t="n">
         <v>1.36</v>
@@ -63483,7 +63483,7 @@
         <v>3.23</v>
       </c>
       <c r="DO136" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -63955,7 +63955,7 @@
         <v>2.81</v>
       </c>
       <c r="DO137" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64397,7 +64397,7 @@
         <v>1.21</v>
       </c>
       <c r="DE138" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF138" t="n">
         <v>1.5</v>
@@ -64427,7 +64427,7 @@
         <v>2.81</v>
       </c>
       <c r="DO138" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -64866,7 +64866,7 @@
         <v>88</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE139" t="n">
         <v>1.5</v>
@@ -64899,7 +64899,7 @@
         <v>2.93</v>
       </c>
       <c r="DO139" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65333,7 +65333,7 @@
         <v>1.29</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF140" t="n">
         <v>1.38</v>
@@ -65363,7 +65363,7 @@
         <v>2.22</v>
       </c>
       <c r="DO140" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -65789,7 +65789,7 @@
         <v>2</v>
       </c>
       <c r="DE141" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF141" t="n">
         <v>2.22</v>
@@ -65819,7 +65819,7 @@
         <v>3.38</v>
       </c>
       <c r="DO141" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66291,7 +66291,7 @@
         <v>2.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66693,7 +66693,7 @@
         <v>0.57</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF143" t="n">
         <v>0.5</v>
@@ -66723,7 +66723,7 @@
         <v>2.92</v>
       </c>
       <c r="DO143" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67154,7 +67154,7 @@
         <v>66</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE144" t="n">
         <v>1.43</v>
@@ -67187,7 +67187,7 @@
         <v>2.94</v>
       </c>
       <c r="DO144" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67626,7 +67626,7 @@
         <v>82</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE145" t="n">
         <v>1.21</v>
@@ -67659,7 +67659,7 @@
         <v>3.67</v>
       </c>
       <c r="DO145" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68090,7 +68090,7 @@
         <v>84</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE146" t="n">
         <v>1.36</v>
@@ -68123,7 +68123,7 @@
         <v>3.08</v>
       </c>
       <c r="DO146" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68557,7 +68557,7 @@
         <v>0.57</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF147" t="n">
         <v>0.44</v>
@@ -68587,7 +68587,7 @@
         <v>1.99</v>
       </c>
       <c r="DO147" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69026,10 +69026,10 @@
         <v>67</v>
       </c>
       <c r="DD148" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF148" t="n">
         <v>1.56</v>
@@ -69059,7 +69059,7 @@
         <v>2.8</v>
       </c>
       <c r="DO148" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69490,7 +69490,7 @@
         <v>77</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE149" t="n">
         <v>0.73</v>
@@ -69523,7 +69523,7 @@
         <v>3.36</v>
       </c>
       <c r="DO149" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -69979,7 +69979,7 @@
         <v>3.38</v>
       </c>
       <c r="DO150" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70435,7 +70435,7 @@
         <v>3.03</v>
       </c>
       <c r="DO151" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -70858,10 +70858,10 @@
         <v>64</v>
       </c>
       <c r="DD152" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF152" t="n">
         <v>1.56</v>
@@ -70891,7 +70891,7 @@
         <v>3.03</v>
       </c>
       <c r="DO152" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71363,7 +71363,7 @@
         <v>2.92</v>
       </c>
       <c r="DO153" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71786,10 +71786,10 @@
         <v>80</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF154" t="n">
         <v>1.33</v>
@@ -71819,7 +71819,7 @@
         <v>3.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72250,7 +72250,7 @@
         <v>80</v>
       </c>
       <c r="DD155" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE155" t="n">
         <v>1.43</v>
@@ -72283,7 +72283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO155" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72725,7 +72725,7 @@
         <v>1.21</v>
       </c>
       <c r="DE156" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF156" t="n">
         <v>1.33</v>
@@ -72755,7 +72755,7 @@
         <v>2.96</v>
       </c>
       <c r="DO156" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73227,7 +73227,7 @@
         <v>3.17</v>
       </c>
       <c r="DO157" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73666,7 +73666,7 @@
         <v>80</v>
       </c>
       <c r="DD158" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE158" t="n">
         <v>0.73</v>
@@ -73699,7 +73699,7 @@
         <v>2.86</v>
       </c>
       <c r="DO158" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -74125,7 +74125,7 @@
         <v>1.07</v>
       </c>
       <c r="DE159" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF159" t="n">
         <v>1.33</v>
@@ -74155,7 +74155,7 @@
         <v>2.6</v>
       </c>
       <c r="DO159" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -74578,10 +74578,10 @@
         <v>67</v>
       </c>
       <c r="DD160" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF160" t="n">
         <v>1.44</v>
@@ -74611,7 +74611,7 @@
         <v>2.5</v>
       </c>
       <c r="DO160" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75083,7 +75083,7 @@
         <v>3.22</v>
       </c>
       <c r="DO161" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75509,7 +75509,7 @@
         <v>2.29</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF162" t="n">
         <v>2.44</v>
@@ -75539,7 +75539,7 @@
         <v>2.95</v>
       </c>
       <c r="DO162" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -76003,7 +76003,7 @@
         <v>2.99</v>
       </c>
       <c r="DO163" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76426,7 +76426,7 @@
         <v>74</v>
       </c>
       <c r="DD164" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE164" t="n">
         <v>1.43</v>
@@ -76459,7 +76459,7 @@
         <v>3.26</v>
       </c>
       <c r="DO164" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76874,7 +76874,7 @@
         <v>79</v>
       </c>
       <c r="DD165" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE165" t="n">
         <v>1.5</v>
@@ -76907,7 +76907,7 @@
         <v>3.25</v>
       </c>
       <c r="DO165" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77341,7 +77341,7 @@
         <v>1.73</v>
       </c>
       <c r="DE166" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF166" t="n">
         <v>1.7</v>
@@ -77371,7 +77371,7 @@
         <v>3.11</v>
       </c>
       <c r="DO166" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77835,7 +77835,7 @@
         <v>2.24</v>
       </c>
       <c r="DO167" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78258,10 +78258,10 @@
         <v>70</v>
       </c>
       <c r="DD168" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE168" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF168" t="n">
         <v>1.4</v>
@@ -78291,7 +78291,7 @@
         <v>2.28</v>
       </c>
       <c r="DO168" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -78725,7 +78725,7 @@
         <v>2.21</v>
       </c>
       <c r="DE169" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF169" t="n">
         <v>2.2</v>
@@ -78755,7 +78755,7 @@
         <v>3.02</v>
       </c>
       <c r="DO169" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79195,7 +79195,7 @@
         <v>2.74</v>
       </c>
       <c r="DO170" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -79621,7 +79621,7 @@
         <v>1.07</v>
       </c>
       <c r="DE171" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF171" t="n">
         <v>1.3</v>
@@ -79651,7 +79651,7 @@
         <v>2.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80107,7 +80107,7 @@
         <v>3.24</v>
       </c>
       <c r="DO172" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80555,7 +80555,7 @@
         <v>3.14</v>
       </c>
       <c r="DO173" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP173" t="b">
         <v>0</v>
@@ -80978,7 +80978,7 @@
         <v>86</v>
       </c>
       <c r="DD174" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE174" t="n">
         <v>1.21</v>
@@ -81011,7 +81011,7 @@
         <v>2.83</v>
       </c>
       <c r="DO174" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81450,7 +81450,7 @@
         <v>80</v>
       </c>
       <c r="DD175" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE175" t="n">
         <v>1.43</v>
@@ -81483,7 +81483,7 @@
         <v>3.43</v>
       </c>
       <c r="DO175" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81917,7 +81917,7 @@
         <v>2</v>
       </c>
       <c r="DE176" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF176" t="n">
         <v>2.09</v>
@@ -81947,7 +81947,7 @@
         <v>3.2</v>
       </c>
       <c r="DO176" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -82386,7 +82386,7 @@
         <v>70</v>
       </c>
       <c r="DD177" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE177" t="n">
         <v>1.21</v>
@@ -82419,7 +82419,7 @@
         <v>2.92</v>
       </c>
       <c r="DO177" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -82883,7 +82883,7 @@
         <v>2.66</v>
       </c>
       <c r="DO178" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP178" t="b">
         <v>1</v>
@@ -83322,7 +83322,7 @@
         <v>85</v>
       </c>
       <c r="DD179" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE179" t="n">
         <v>0.93</v>
@@ -83355,7 +83355,7 @@
         <v>2.71</v>
       </c>
       <c r="DO179" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -83819,7 +83819,7 @@
         <v>3.02</v>
       </c>
       <c r="DO180" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP180" t="b">
         <v>1</v>
@@ -84267,7 +84267,7 @@
         <v>3.01</v>
       </c>
       <c r="DO181" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP181" t="b">
         <v>1</v>
@@ -84709,7 +84709,7 @@
         <v>1.21</v>
       </c>
       <c r="DE182" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF182" t="n">
         <v>1.09</v>
@@ -84739,7 +84739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO182" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -85203,7 +85203,7 @@
         <v>2.77</v>
       </c>
       <c r="DO183" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP183" t="b">
         <v>1</v>
@@ -85642,10 +85642,10 @@
         <v>77</v>
       </c>
       <c r="DD184" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE184" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF184" t="n">
         <v>2.8</v>
@@ -85675,7 +85675,7 @@
         <v>3.71</v>
       </c>
       <c r="DO184" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP184" t="b">
         <v>1</v>
@@ -86147,7 +86147,7 @@
         <v>2.75</v>
       </c>
       <c r="DO185" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -86586,10 +86586,10 @@
         <v>73</v>
       </c>
       <c r="DD186" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE186" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF186" t="n">
         <v>1.55</v>
@@ -86619,7 +86619,7 @@
         <v>3.37</v>
       </c>
       <c r="DO186" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP186" t="b">
         <v>1</v>
@@ -87045,7 +87045,7 @@
         <v>1.29</v>
       </c>
       <c r="DE187" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF187" t="n">
         <v>1.36</v>
@@ -87075,7 +87075,7 @@
         <v>2.78</v>
       </c>
       <c r="DO187" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP187" t="b">
         <v>1</v>
@@ -87498,7 +87498,7 @@
         <v>78</v>
       </c>
       <c r="DD188" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE188" t="n">
         <v>1.43</v>
@@ -87531,7 +87531,7 @@
         <v>2.76</v>
       </c>
       <c r="DO188" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP188" t="b">
         <v>1</v>
@@ -87957,7 +87957,7 @@
         <v>1.73</v>
       </c>
       <c r="DE189" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF189" t="n">
         <v>1.82</v>
@@ -87987,7 +87987,7 @@
         <v>3.03</v>
       </c>
       <c r="DO189" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -88426,10 +88426,10 @@
         <v>78</v>
       </c>
       <c r="DD190" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE190" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF190" t="n">
         <v>1.18</v>
@@ -88459,7 +88459,7 @@
         <v>3.51</v>
       </c>
       <c r="DO190" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP190" t="b">
         <v>1</v>
@@ -88870,10 +88870,10 @@
         <v>73</v>
       </c>
       <c r="DD191" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE191" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF191" t="n">
         <v>2.82</v>
@@ -88903,7 +88903,7 @@
         <v>2.93</v>
       </c>
       <c r="DO191" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP191" t="b">
         <v>1</v>
@@ -89345,7 +89345,7 @@
         <v>2.29</v>
       </c>
       <c r="DE192" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF192" t="n">
         <v>2.27</v>
@@ -89375,7 +89375,7 @@
         <v>2.89</v>
       </c>
       <c r="DO192" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP192" t="b">
         <v>1</v>
@@ -89806,7 +89806,7 @@
         <v>69</v>
       </c>
       <c r="DD193" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE193" t="n">
         <v>0.93</v>
@@ -89839,7 +89839,7 @@
         <v>2.48</v>
       </c>
       <c r="DO193" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP193" t="b">
         <v>1</v>
@@ -90278,7 +90278,7 @@
         <v>75</v>
       </c>
       <c r="DD194" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE194" t="n">
         <v>1.36</v>
@@ -90311,7 +90311,7 @@
         <v>2.87</v>
       </c>
       <c r="DO194" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP194" t="b">
         <v>1</v>
@@ -90753,7 +90753,7 @@
         <v>1</v>
       </c>
       <c r="DE195" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF195" t="n">
         <v>0.92</v>
@@ -90783,7 +90783,7 @@
         <v>2.81</v>
       </c>
       <c r="DO195" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP195" t="b">
         <v>1</v>
@@ -91206,7 +91206,7 @@
         <v>75</v>
       </c>
       <c r="DD196" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE196" t="n">
         <v>1.14</v>
@@ -91239,7 +91239,7 @@
         <v>2.88</v>
       </c>
       <c r="DO196" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP196" t="b">
         <v>1</v>
@@ -91695,7 +91695,7 @@
         <v>2.98</v>
       </c>
       <c r="DO197" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP197" t="b">
         <v>1</v>
@@ -92134,10 +92134,10 @@
         <v>88</v>
       </c>
       <c r="DD198" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE198" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF198" t="n">
         <v>0.58</v>
@@ -92167,7 +92167,7 @@
         <v>3.27</v>
       </c>
       <c r="DO198" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP198" t="b">
         <v>1</v>
@@ -92590,7 +92590,7 @@
         <v>83</v>
       </c>
       <c r="DD199" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE199" t="n">
         <v>1.21</v>
@@ -92623,7 +92623,7 @@
         <v>3.07</v>
       </c>
       <c r="DO199" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP199" t="b">
         <v>1</v>
@@ -93057,7 +93057,7 @@
         <v>2</v>
       </c>
       <c r="DE200" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF200" t="n">
         <v>2</v>
@@ -93087,7 +93087,7 @@
         <v>2.89</v>
       </c>
       <c r="DO200" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP200" t="b">
         <v>0</v>
@@ -93551,7 +93551,7 @@
         <v>2.94</v>
       </c>
       <c r="DO201" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP201" t="b">
         <v>1</v>
@@ -94007,7 +94007,7 @@
         <v>3.06</v>
       </c>
       <c r="DO202" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP202" t="b">
         <v>1</v>
@@ -94405,7 +94405,7 @@
         <v>0.57</v>
       </c>
       <c r="DE203" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF203" t="n">
         <v>0.58</v>
@@ -94435,7 +94435,7 @@
         <v>2.78</v>
       </c>
       <c r="DO203" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP203" t="b">
         <v>1</v>
@@ -94869,7 +94869,7 @@
         <v>2.29</v>
       </c>
       <c r="DE204" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF204" t="n">
         <v>2.33</v>
@@ -94899,7 +94899,7 @@
         <v>3.39</v>
       </c>
       <c r="DO204" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP204" t="b">
         <v>1</v>
@@ -95314,7 +95314,7 @@
         <v>79</v>
       </c>
       <c r="DD205" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE205" t="n">
         <v>0.93</v>
@@ -95347,7 +95347,7 @@
         <v>3.12</v>
       </c>
       <c r="DO205" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP205" t="b">
         <v>1</v>
@@ -95786,10 +95786,10 @@
         <v>75</v>
       </c>
       <c r="DD206" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE206" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF206" t="n">
         <v>1.33</v>
@@ -95819,7 +95819,7 @@
         <v>2.97</v>
       </c>
       <c r="DO206" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP206" t="b">
         <v>1</v>
@@ -96275,7 +96275,7 @@
         <v>2.5</v>
       </c>
       <c r="DO207" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP207" t="b">
         <v>1</v>
@@ -96717,7 +96717,7 @@
         <v>1.29</v>
       </c>
       <c r="DE208" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF208" t="n">
         <v>1.5</v>
@@ -96747,7 +96747,7 @@
         <v>2.94</v>
       </c>
       <c r="DO208" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP208" t="b">
         <v>1</v>
@@ -97178,7 +97178,7 @@
         <v>83</v>
       </c>
       <c r="DD209" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE209" t="n">
         <v>1.21</v>
@@ -97211,7 +97211,7 @@
         <v>3.1</v>
       </c>
       <c r="DO209" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP209" t="b">
         <v>1</v>
@@ -97653,7 +97653,7 @@
         <v>1.21</v>
       </c>
       <c r="DE210" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF210" t="n">
         <v>1.23</v>
@@ -97683,7 +97683,7 @@
         <v>2.31</v>
       </c>
       <c r="DO210" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP210" t="b">
         <v>1</v>
@@ -98106,7 +98106,7 @@
         <v>77</v>
       </c>
       <c r="DD211" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DE211" t="n">
         <v>0.73</v>
@@ -98139,7 +98139,7 @@
         <v>2.57</v>
       </c>
       <c r="DO211" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP211" t="b">
         <v>1</v>
@@ -98562,10 +98562,10 @@
         <v>77</v>
       </c>
       <c r="DD212" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE212" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DF212" t="n">
         <v>1.38</v>
@@ -98595,7 +98595,7 @@
         <v>3</v>
       </c>
       <c r="DO212" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP212" t="b">
         <v>1</v>
@@ -99021,7 +99021,7 @@
         <v>2</v>
       </c>
       <c r="DE213" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF213" t="n">
         <v>1.92</v>
@@ -99051,7 +99051,7 @@
         <v>3.27</v>
       </c>
       <c r="DO213" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP213" t="b">
         <v>1</v>
@@ -99490,7 +99490,7 @@
         <v>77</v>
       </c>
       <c r="DD214" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE214" t="n">
         <v>1.14</v>
@@ -99523,7 +99523,7 @@
         <v>3.4</v>
       </c>
       <c r="DO214" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP214" t="b">
         <v>1</v>
@@ -99946,7 +99946,7 @@
         <v>74</v>
       </c>
       <c r="DD215" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE215" t="n">
         <v>1.43</v>
@@ -99979,7 +99979,7 @@
         <v>3.37</v>
       </c>
       <c r="DO215" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP215" t="b">
         <v>0</v>
@@ -100418,10 +100418,10 @@
         <v>77</v>
       </c>
       <c r="DD216" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE216" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DF216" t="n">
         <v>1.31</v>
@@ -100451,7 +100451,7 @@
         <v>3.3</v>
       </c>
       <c r="DO216" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP216" t="b">
         <v>1</v>
@@ -100890,10 +100890,10 @@
         <v>81</v>
       </c>
       <c r="DD217" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DE217" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DF217" t="n">
         <v>0.54</v>
@@ -100923,7 +100923,7 @@
         <v>2.87</v>
       </c>
       <c r="DO217" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP217" t="b">
         <v>0</v>
@@ -101363,7 +101363,7 @@
         <v>2.36</v>
       </c>
       <c r="DO218" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP218" t="b">
         <v>0</v>
@@ -101803,7 +101803,7 @@
         <v>3.14</v>
       </c>
       <c r="DO219" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP219" t="b">
         <v>1</v>
@@ -102243,7 +102243,7 @@
         <v>2.58</v>
       </c>
       <c r="DO220" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP220" t="b">
         <v>1</v>
@@ -102666,7 +102666,7 @@
         <v>85</v>
       </c>
       <c r="DD221" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE221" t="n">
         <v>1.36</v>
@@ -102699,7 +102699,7 @@
         <v>3.52</v>
       </c>
       <c r="DO221" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP221" t="b">
         <v>1</v>
@@ -103141,7 +103141,7 @@
         <v>2.29</v>
       </c>
       <c r="DE222" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DF222" t="n">
         <v>2.38</v>
@@ -103171,7 +103171,7 @@
         <v>3.5</v>
       </c>
       <c r="DO222" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP222" t="b">
         <v>1</v>
@@ -103635,7 +103635,7 @@
         <v>2.87</v>
       </c>
       <c r="DO223" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP223" t="b">
         <v>1</v>
@@ -104053,7 +104053,7 @@
         <v>1.29</v>
       </c>
       <c r="DE224" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF224" t="n">
         <v>1.38</v>
@@ -104083,7 +104083,7 @@
         <v>2.54</v>
       </c>
       <c r="DO224" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP224" t="b">
         <v>1</v>
@@ -104531,7 +104531,7 @@
         <v>3.13</v>
       </c>
       <c r="DO225" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP225" t="b">
         <v>1</v>
@@ -105054,6 +105054,3286 @@
       <c r="EJ226" t="inlineStr"/>
       <c r="EK226" t="inlineStr"/>
       <c r="EL226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>29</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>46095.625</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>2</v>
+      </c>
+      <c r="I227" t="n">
+        <v>2</v>
+      </c>
+      <c r="J227" t="n">
+        <v>10</v>
+      </c>
+      <c r="K227" t="n">
+        <v>3</v>
+      </c>
+      <c r="L227" t="n">
+        <v>13</v>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>5</v>
+      </c>
+      <c r="R227" t="n">
+        <v>5</v>
+      </c>
+      <c r="S227" t="n">
+        <v>14</v>
+      </c>
+      <c r="T227" t="n">
+        <v>5</v>
+      </c>
+      <c r="U227" t="n">
+        <v>19</v>
+      </c>
+      <c r="V227" t="n">
+        <v>10</v>
+      </c>
+      <c r="W227" t="n">
+        <v>6</v>
+      </c>
+      <c r="X227" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>Stade du Pays de Charleroi</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>Boulevard Zoé Drion 19, Charleroi</t>
+        </is>
+      </c>
+      <c r="AC227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>690</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV227" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW227" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX227" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY227" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ227" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA227" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB227" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI227" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ227" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP227" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ227" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR227" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS227" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT227" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU227" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV227" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW227" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX227" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY227" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ227" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA227" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB227" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC227" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD227" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE227" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF227" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DG227" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH227" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI227" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ227" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK227" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL227" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM227" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN227" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO227" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP227" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ227" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR227" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS227" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT227" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU227" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV227" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW227" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="DX227" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="DY227" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DZ227" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EA227" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EB227" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC227" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="ED227" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EE227" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="EF227" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="EG227" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EH227" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EI227" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EJ227" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EK227" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EL227" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>29</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>46095.71875</v>
+      </c>
+      <c r="G228" t="n">
+        <v>2</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>2</v>
+      </c>
+      <c r="J228" t="n">
+        <v>5</v>
+      </c>
+      <c r="K228" t="n">
+        <v>5</v>
+      </c>
+      <c r="L228" t="n">
+        <v>10</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>3</v>
+      </c>
+      <c r="R228" t="n">
+        <v>1</v>
+      </c>
+      <c r="S228" t="n">
+        <v>6</v>
+      </c>
+      <c r="T228" t="n">
+        <v>4</v>
+      </c>
+      <c r="U228" t="n">
+        <v>9</v>
+      </c>
+      <c r="V228" t="n">
+        <v>5</v>
+      </c>
+      <c r="W228" t="n">
+        <v>9</v>
+      </c>
+      <c r="X228" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>Stade Joseph Mariën</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>Chaussée de Bruxelles 223, Forest, Brussels</t>
+        </is>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>2572</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV228" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW228" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX228" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY228" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ228" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA228" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB228" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM228" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR228" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS228" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU228" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV228" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX228" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY228" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ228" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA228" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB228" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC228" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD228" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DE228" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF228" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DG228" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DH228" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DI228" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="DJ228" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK228" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL228" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM228" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN228" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DO228" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP228" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ228" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR228" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS228" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT228" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU228" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV228" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW228" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="DX228" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DY228" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DZ228" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EA228" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EB228" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EC228" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="ED228" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EE228" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="EF228" t="inlineStr">
+        <is>
+          <t>12.20</t>
+        </is>
+      </c>
+      <c r="EG228" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EH228" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI228" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ228" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EK228" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL228" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>29</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>46095.82291666666</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" t="n">
+        <v>11</v>
+      </c>
+      <c r="K229" t="n">
+        <v>2</v>
+      </c>
+      <c r="L229" t="n">
+        <v>13</v>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>3</v>
+      </c>
+      <c r="R229" t="n">
+        <v>3</v>
+      </c>
+      <c r="S229" t="n">
+        <v>11</v>
+      </c>
+      <c r="T229" t="n">
+        <v>3</v>
+      </c>
+      <c r="U229" t="n">
+        <v>14</v>
+      </c>
+      <c r="V229" t="n">
+        <v>6</v>
+      </c>
+      <c r="W229" t="n">
+        <v>10</v>
+      </c>
+      <c r="X229" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>Het Kuipje</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>De Merodedreef 189, Westerlo</t>
+        </is>
+      </c>
+      <c r="AC229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT229" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV229" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW229" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX229" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY229" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ229" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA229" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB229" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR229" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS229" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU229" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV229" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX229" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY229" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ229" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA229" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB229" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC229" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD229" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE229" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DF229" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG229" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DH229" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI229" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DJ229" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK229" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL229" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM229" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DN229" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="DO229" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP229" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ229" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR229" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS229" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT229" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU229" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV229" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW229" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DX229" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DY229" t="inlineStr"/>
+      <c r="DZ229" t="inlineStr"/>
+      <c r="EA229" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EB229" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EC229" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="ED229" t="inlineStr">
+        <is>
+          <t>5.46</t>
+        </is>
+      </c>
+      <c r="EE229" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="EF229" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG229" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EH229" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EI229" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EJ229" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EK229" t="inlineStr"/>
+      <c r="EL229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>29</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>46096.52083333334</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>5</v>
+      </c>
+      <c r="K230" t="n">
+        <v>8</v>
+      </c>
+      <c r="L230" t="n">
+        <v>13</v>
+      </c>
+      <c r="M230" t="n">
+        <v>2</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>4</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1</v>
+      </c>
+      <c r="S230" t="n">
+        <v>9</v>
+      </c>
+      <c r="T230" t="n">
+        <v>7</v>
+      </c>
+      <c r="U230" t="n">
+        <v>13</v>
+      </c>
+      <c r="V230" t="n">
+        <v>8</v>
+      </c>
+      <c r="W230" t="n">
+        <v>9</v>
+      </c>
+      <c r="X230" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>Luminus Arena</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>Stadionplein 4, Waterschei, Genk</t>
+        </is>
+      </c>
+      <c r="AC230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV230" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW230" t="n">
+        <v>87</v>
+      </c>
+      <c r="BX230" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY230" t="n">
+        <v>120</v>
+      </c>
+      <c r="BZ230" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA230" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB230" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR230" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS230" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU230" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV230" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX230" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY230" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ230" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA230" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB230" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC230" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD230" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DE230" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DF230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG230" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI230" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DJ230" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK230" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL230" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM230" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN230" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="DO230" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP230" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV230" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW230" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DX230" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="DY230" t="inlineStr"/>
+      <c r="DZ230" t="inlineStr"/>
+      <c r="EA230" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EB230" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EC230" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="ED230" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EE230" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EF230" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EG230" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH230" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EI230" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ230" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EK230" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EL230" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>29</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>46096.625</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="n">
+        <v>2</v>
+      </c>
+      <c r="J231" t="n">
+        <v>5</v>
+      </c>
+      <c r="K231" t="n">
+        <v>3</v>
+      </c>
+      <c r="L231" t="n">
+        <v>8</v>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>2</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6</v>
+      </c>
+      <c r="S231" t="n">
+        <v>7</v>
+      </c>
+      <c r="T231" t="n">
+        <v>6</v>
+      </c>
+      <c r="U231" t="n">
+        <v>9</v>
+      </c>
+      <c r="V231" t="n">
+        <v>12</v>
+      </c>
+      <c r="W231" t="n">
+        <v>11</v>
+      </c>
+      <c r="X231" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>Bosuilstadion</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>Oude Bosuilbaan 54a, Deurne</t>
+        </is>
+      </c>
+      <c r="AC231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV231" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW231" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX231" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY231" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ231" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CA231" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB231" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP231" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR231" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS231" t="n">
+        <v>35</v>
+      </c>
+      <c r="CT231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU231" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV231" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX231" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY231" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ231" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA231" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB231" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC231" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD231" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DE231" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DF231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH231" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI231" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ231" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK231" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL231" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM231" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DN231" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DO231" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP231" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ231" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR231" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS231" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT231" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU231" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV231" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW231" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="DX231" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DY231" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="DZ231" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EA231" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="EB231" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EC231" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED231" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EE231" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EF231" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EG231" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH231" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI231" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EJ231" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EK231" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL231" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>29</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>46096.72916666666</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1</v>
+      </c>
+      <c r="J232" t="n">
+        <v>5</v>
+      </c>
+      <c r="K232" t="n">
+        <v>4</v>
+      </c>
+      <c r="L232" t="n">
+        <v>9</v>
+      </c>
+      <c r="M232" t="n">
+        <v>2</v>
+      </c>
+      <c r="N232" t="n">
+        <v>7</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>5</v>
+      </c>
+      <c r="R232" t="n">
+        <v>4</v>
+      </c>
+      <c r="S232" t="n">
+        <v>8</v>
+      </c>
+      <c r="T232" t="n">
+        <v>13</v>
+      </c>
+      <c r="U232" t="n">
+        <v>13</v>
+      </c>
+      <c r="V232" t="n">
+        <v>17</v>
+      </c>
+      <c r="W232" t="n">
+        <v>8</v>
+      </c>
+      <c r="X232" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>AFAS-stadion Achter de Kazerne</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>Kleine Nieuwedijk 53, Malines</t>
+        </is>
+      </c>
+      <c r="AC232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR232" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT232" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV232" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW232" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX232" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY232" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ232" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CA232" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB232" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR232" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS232" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU232" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV232" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX232" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY232" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ232" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA232" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB232" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC232" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD232" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE232" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DF232" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG232" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH232" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI232" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ232" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK232" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL232" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM232" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN232" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO232" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP232" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV232" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW232" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="DX232" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="DY232" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DZ232" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EA232" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EB232" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC232" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="ED232" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EE232" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EF232" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EG232" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EH232" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI232" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EJ232" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EK232" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EL232" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Belgium_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>29</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>46096.76041666666</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>3</v>
+      </c>
+      <c r="I233" t="n">
+        <v>4</v>
+      </c>
+      <c r="J233" t="n">
+        <v>5</v>
+      </c>
+      <c r="K233" t="n">
+        <v>7</v>
+      </c>
+      <c r="L233" t="n">
+        <v>12</v>
+      </c>
+      <c r="M233" t="n">
+        <v>2</v>
+      </c>
+      <c r="N233" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>10</v>
+      </c>
+      <c r="R233" t="n">
+        <v>5</v>
+      </c>
+      <c r="S233" t="n">
+        <v>15</v>
+      </c>
+      <c r="T233" t="n">
+        <v>10</v>
+      </c>
+      <c r="U233" t="n">
+        <v>25</v>
+      </c>
+      <c r="V233" t="n">
+        <v>15</v>
+      </c>
+      <c r="W233" t="n">
+        <v>8</v>
+      </c>
+      <c r="X233" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>Jan Breydelstadion</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>Olympialaan 74, Brugge</t>
+        </is>
+      </c>
+      <c r="AC233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>669434</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR233" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS233" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV233" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW233" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX233" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY233" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ233" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CA233" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB233" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="CC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM233" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR233" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS233" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU233" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV233" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW233" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX233" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY233" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ233" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA233" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB233" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC233" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD233" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DE233" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF233" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DG233" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH233" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI233" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DJ233" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK233" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL233" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM233" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN233" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DO233" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP233" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ233" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR233" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS233" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT233" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU233" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV233" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW233" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="DX233" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DY233" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DZ233" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EA233" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EB233" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EC233" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED233" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EE233" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EF233" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EG233" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EH233" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EI233" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ233" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EK233" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EL233" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
